--- a/Test_Output/GPIO/TestPlan/GPIO_TestPlan_1.xlsx
+++ b/Test_Output/GPIO/TestPlan/GPIO_TestPlan_1.xlsx
@@ -4,10 +4,11 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Meta_data_sheet" sheetId="1" state="veryHidden" r:id="rId1"/>
+    <sheet name="TestPlan" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,13 +46,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,420 +444,436 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Hidden_Test_Case_Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Hidden_Test_Description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Hidden_Remarks</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Hidden_Test_Steps_Procedure</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Hidden_Impacted_Registers</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Hidden_Validation_Acceptance_Criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>gpio_reg_wr_rd_test</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Test performs two phases over CNT=49 registers listed in addr_array[] (MIZAR_GPIO_GP0_GPIO_8..MIZAR_GPIO_GP0_GPIO_39, MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, MIZAR_GPIO_GP0_INTR1_INTR_EN1, MIZAR_GPIO_GP0_INTR1_INTR_STS1, MIZAR_GPIO_GP0_INTR2_INTR_EN1, MIZAR_GPIO_GP0_INTR2_INTR_STS1, MIZAR_GPIO_GPIO_IO_CTRL_GROUP1..4, MIZAR_GPIO_GPIO_DOUT_GROUP1..4, MIZAR_GPIO_GPIO_DIN_GROUP1..4). Phase 1 (chk_rst_val): for i=0..CNT-1, addr=addr_array[i]; if skip_rst_array[i]==1 continue; if read_mask_array[i]==0 continue; data_rd=read_reg(addr); data=(data_rd &amp; 0xfffffffe); if data==default_value_array[i] pass else def_fail_cnt++. Phase 2 (chk_rd_wr): for each j in {0xffffffff,0xaaaaaaaa,0x55555555,0xf5f5f5f5,0xA5A5A5A5,0xffff0000} set data_wr; Write loop: for i=0..CNT-1 if skip_array[i]==1 continue; if write_mask_array[i]==0 continue; write_reg(addr_array[i], (data_wr &amp; write_mask_array[i])); Readback loop: for i=0..CNT-1 if skip_array[i]==1 continue; if write_mask_array[i]==0 continue; if read_mask_array[i]==0 continue; data_rd=(read_reg(addr_array[i]) &amp; read_mask_array[i]); wr_n=(write_mask_array[i] ^ 0xffffffff); exp_val=((data_wr &amp; read_mask_array[i] &amp; write_mask_array[i]) | (wr_n &amp; read_mask_array[i] &amp; default_value_array[i])); if data_rd==exp_val pass else wr_fail_cnt++. test_case() calls chk_rst_val(); chk_rd_wr(); if(def_fail_cnt&gt;0 || wr_fail_cnt&gt;0) finish(1) else finish(0).</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>skip_array[] skips VRRW or otherwise restricted registers for write; skip_rst_array[] skips default-value checks for specific group registers. Note: when reading default values the DIN bit may become 1 if not driven; forcing zero on DIN can drive bit-level selection high, causing read mismatch with expected default.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>["test_case(): call chk_rst_val().","chk_rst_val(): for(i=0;i&lt;CNT;i++){ addr=addr_array[i]; if(skip_rst_array[i]==1) continue; if(read_mask_array[i]==0x00000000) continue; data_rd=read_reg(addr); data=(data_rd &amp; 0xfffffffe); if(data==default_value_array[i]) { } else { def_fail_cnt++; printf failure; } }","Return to test_case(): call chk_rd_wr().","chk_rd_wr(): define chk_val[6]={0xffffffff,0xaaaaaaaa,0x55555555,0xf5f5f5f5,0xA5A5A5A5,0xffff0000}; For each j in 0..5: data_wr=chk_val[j].","Write loop: for(i=0;i&lt;CNT;i++){ addr=addr_array[i]; if(skip_array[i]==1) continue; if(write_mask_array[i]==0x00000000) continue; write_reg(addr,(data_wr &amp; write_mask_array[i])); }","Readback loop: for(i=0;i&lt;CNT;i++){ addr=addr_array[i]; if(skip_array[i]==1) continue; if(write_mask_array[i]==0x00000000) continue; if(read_mask_array[i]==0x00000000) continue; data_rd=(read_reg(addr) &amp; read_mask_array[i]); wr_n=(write_mask_array[i] ^ 0xffffffff); exp_val=((data_wr &amp; read_mask_array[i] &amp; write_mask_array[i]) | (wr_n &amp; read_mask_array[i] &amp; default_value_array[i])); if(data_rd==exp_val){ } else { wr_fail_cnt++; printf failure; } }","Return to test_case(): if(def_fail_cnt&gt;0 || wr_fail_cnt&gt;0) finish(1); else finish(0)."]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>MIZAR_GPIO_GP0_GPIO_8, MIZAR_GPIO_GP0_GPIO_9, MIZAR_GPIO_GP0_GPIO_10, MIZAR_GPIO_GP0_GPIO_11, MIZAR_GPIO_GP0_GPIO_12, MIZAR_GPIO_GP0_GPIO_13, MIZAR_GPIO_GP0_GPIO_14, MIZAR_GPIO_GP0_GPIO_15, MIZAR_GPIO_GP0_GPIO_16, MIZAR_GPIO_GP0_GPIO_17, MIZAR_GPIO_GP0_GPIO_18, MIZAR_GPIO_GP0_GPIO_19, MIZAR_GPIO_GP0_GPIO_20, MIZAR_GPIO_GP0_GPIO_21, MIZAR_GPIO_GP0_GPIO_22, MIZAR_GPIO_GP0_GPIO_23, MIZAR_GPIO_GP0_GPIO_24, MIZAR_GPIO_GP0_GPIO_25, MIZAR_GPIO_GP0_GPIO_26, MIZAR_GPIO_GP0_GPIO_27, MIZAR_GPIO_GP0_GPIO_28, MIZAR_GPIO_GP0_GPIO_29, MIZAR_GPIO_GP0_GPIO_30, MIZAR_GPIO_GP0_GPIO_31, MIZAR_GPIO_GP0_GPIO_32, MIZAR_GPIO_GP0_GPIO_33, MIZAR_GPIO_GP0_GPIO_34, MIZAR_GPIO_GP0_GPIO_35, MIZAR_GPIO_GP0_GPIO_36, MIZAR_GPIO_GP0_GPIO_37, MIZAR_GPIO_GP0_GPIO_38, MIZAR_GPIO_GP0_GPIO_39, MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, MIZAR_GPIO_GP0_INTR1_INTR_EN1, MIZAR_GPIO_GP0_INTR1_INTR_STS1, MIZAR_GPIO_GP0_INTR2_INTR_EN1, MIZAR_GPIO_GP0_INTR2_INTR_STS1, MIZAR_GPIO_GPIO_IO_CTRL_GROUP1, MIZAR_GPIO_GPIO_IO_CTRL_GROUP2, MIZAR_GPIO_GPIO_IO_CTRL_GROUP3, MIZAR_GPIO_GPIO_IO_CTRL_GROUP4, MIZAR_GPIO_GPIO_DOUT_GROUP1, MIZAR_GPIO_GPIO_DOUT_GROUP2, MIZAR_GPIO_GPIO_DOUT_GROUP3, MIZAR_GPIO_GPIO_DOUT_GROUP4, MIZAR_GPIO_GPIO_DIN_GROUP1, MIZAR_GPIO_GPIO_DIN_GROUP2, MIZAR_GPIO_GPIO_DIN_GROUP3, MIZAR_GPIO_GPIO_DIN_GROUP4</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PASS if def_fail_cnt==0 and wr_fail_cnt==0 at end of test_case(); else FAIL. Default check uses (read_reg(addr) &amp; 0xfffffffe) == default_value_array[i]. Write/read check expects data_rd == ((data_wr &amp; read_mask &amp; write_mask) | ((~write_mask) &amp; read_mask &amp; default_value)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>test_gpio_negedge_intr_en</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Negative-edge interrupt enable test. test_case(): test_err=0; optionally GIC_EnableIRQ(87) or GIC_EnableIRQ(88) under GPIO0/GPIO1. Enable sysreg interrupt: write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR or LSS_SYSREG_INTR_EN1_GPIO1_INTR). Drive all high: write_reg(0xA0243ffc,0xffffffff). Configure pins 8..39: for i=0..31 addr1=MIZAR_GPIO_GP0_GPIO_8+(i4); write_reg(addr1,(1&lt;&lt;20)|(1&lt;&lt;18)|(1&lt;&lt;16)); wait_on(10). For each i=0..31: wr_val=(1&lt;&lt;i); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, wr_val); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, wr_val); wait_on(10); int_pend=1; write_reg(0xA0243ffc,0xffffffff); wait_on(30); write_reg(0xA0243ffc, ~wr_val); bounded wait: timeout=5000; while(int_pend &amp;&amp; timeout--) wait_on(10); if(timeout==0){ printf timeout; test_err++; }. finish(test_err). Default_IRQHandler(): local_wr=(1&lt;&lt;i); int_pend=0; write_reg(0xA0243ffc,0xffffffff); raddr=MIZAR_GPIO_GP0_GPIO_8+(i4); rdata=read_reg(raddr); if((rdata &amp; 0x1)!=0) test_err++; if((rdata &amp; 0x2)!=0x0){ rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if((rdata_grp &amp; local_wr)==0) test_err++; raddr2=MIZAR_GPIO_GP0_GPIO_8+(i4); write_reg(raddr2,(1&lt;&lt;20)|(1&lt;&lt;16)); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, local_wr); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if(rdata_grp!=0x0) test_err++; write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR or _GPIO1_INTR); GIC_ClearIRQ(87 or 88); } else { test_err++; }</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>The test uses a pad drive at address 0xA0243ffc to synthesize a falling edge per selected bit. A bounded loop with timeout=5000 and wait_on(10) prevents indefinite hang if no interrupt arrives.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>["test_case(): test_err=0.","#ifdef GPIO0: GIC_EnableIRQ(87); #endif; #ifdef GPIO1: GIC_EnableIRQ(88); #endif.","#ifdef GPIO0: write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR); #endif.","#ifdef GPIO1: write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO1_INTR); #endif.","write_reg(0xA0243ffc, 0xffffffff);","for(i=0;i&lt;32;i++){ addr1=MIZAR_GPIO_GP0_GPIO_8+(i4); write_reg(addr1, (1u&lt;&lt;20)|(1u&lt;&lt;18)|(1u&lt;&lt;16)); wait_on(10); }","for(i=0;i&lt;32;i++){ wr_val=(1u&lt;&lt;i); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, wr_val); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, wr_val); wait_on(10); int_pend=1; write_reg(0xA0243ffc, 0xffffffff); wait_on(30); write_reg(0xA0243ffc, ~wr_val); unsigned int timeout=5000; while(int_pend &amp;&amp; timeout--){ wait_on(10);} if(timeout==0){ printf timeout; test_err++; } }","finish(test_err);","Default_IRQHandler(): local_wr=(1u&lt;&lt;i); int_pend=0; write_reg(0xA0243ffc, 0xffffffff); raddr=MIZAR_GPIO_GP0_GPIO_8+(i4); rdata=read_reg(raddr); if((rdata &amp; 0x1)!=0){ test_err++; } if((rdata &amp; 0x2)!=0x0){ rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if((rdata_grp &amp; local_wr)==0){ test_err++; } raddr2=MIZAR_GPIO_GP0_GPIO_8+(i4); write_reg(raddr2, (1u&lt;&lt;20)|(1u&lt;&lt;16)); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, local_wr); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if(rdata_grp!=0x0){ test_err++; } #ifdef GPIO0: write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); GIC_ClearIRQ(87); #endif; #ifdef GPIO1: write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO1_INTR); GIC_ClearIRQ(88); #endif; } else { test_err++; }"]</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>MIZAR_LSS_SYSREG_INTR_EN1, MIZAR_LSS_SYSREG_RAW_STCR1, MIZAR_GPIO_GP0_GPIO_8, MIZAR_GPIO_GP0_INTR1_INTR_EN1, MIZAR_GPIO_GP0_INTR1_INTR_STS1, MIZAR_GPIO_GPIO_INTR_RAW_STCLR1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Per pin: timeout loop must exit by ISR clearing int_pend; in ISR, (rdata &amp; 0x1)==0 (DIN low) and raw bit set ((rdata &amp; 0x2)!=0); group status read MIZAR_GPIO_GP0_INTR1_INTR_STS1 must have the active bit set and become 0 after clearing per-pin and RAW_STCLR1. Sysreg raw clear write is issued; GIC pending IRQ cleared. test_err must remain 0 for PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>test_gpio_pedge_all_pads_en</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Positive-edge all‑pads enable test. test_case(): optionally GIC_EnableIRQ(87/88); enable sysreg interrupt via write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR or _GPIO1_INTR). For i=0..31: write_reg(MIZAR_GPIO_GP0_GPIO_8+(i4), 0x00020000) to set PEIE (bit17). wait_on(10). Set input mode: write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP1..4, 0x000000FF). wait_on(10). Enable group: write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF). For each i=0..31: write_reg(0xA0243ffc,0x00000000); wait_on(10); int_pend=1; write_reg(0xA0243ffc,0xFFFFFFFF); int timeout=2000; while(int_pend==1 &amp;&amp; --timeout&gt;0){ wait_on(10);} if(timeout==0){ printf timeout; test_err++; break;} write_reg(0xA0243ffc,0x00000000); wait_on(10). finish(test_err). Default_IRQHandler(): wr_val=(1&lt;&lt;i); int_pend=0; rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0x00000000); if((rdata_grp &amp; 0xffffffff)!=0) OK else { printf error; test_err++; }. For j=0..31: write_reg(MIZAR_GPIO_GP0_GPIO_8+(j4),0x00010000) to set ICLR; wait_on(2); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if(rdata_grp==0x0) OK else { test_err++; }. Clear sysreg raw: write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR or _GPIO1_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if(rdata &amp; bit)!=0 then test_err++; Re‑enable: write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF); GIC_ClearIRQ(87 or 88).</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>External pad drive at 0xA0243ffc is toggled low‑to‑high to generate a rising edge. The wait loop uses timeout=2000 and wait_on(10) per iteration to bound execution time.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>["test_case(): #ifdef GPIO0: GIC_EnableIRQ(87); #endif; #ifdef GPIO1: GIC_EnableIRQ(88); #endif; test_err=0.","#ifdef GPIO0: write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR); #endif; #ifdef GPIO1: write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO1_INTR); #endif.","for(i=0;i&lt;32;i++){ write_reg(MIZAR_GPIO_GP0_GPIO_8+(i4), 0x00020000); }","wait_on(10);","write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP1, 0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP2, 0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP3, 0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP4, 0x000000FF);","wait_on(10);","write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF);","for(i=0;i&lt;32;i++){ write_reg(0xA0243ffc, 0x00000000); wait_on(10); int_pend=1; write_reg(0xA0243ffc, 0xFFFFFFFF); int timeout=2000; while((int_pend==1) &amp;&amp; (--timeout&gt;0)){ wait_on(10);} if(timeout==0){ printf timeout; test_err++; break;} write_reg(0xA0243ffc, 0x00000000); wait_on(10); }","finish(test_err);","Default_IRQHandler(): wr_val=(1&lt;&lt;i); int_pend=0; rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0x00000000); if((rdata_grp &amp; 0xffffffff)!=0){ } else { printf error; test_err++; } for(j=0;j&lt;32;j++){ write_reg(MIZAR_GPIO_GP0_GPIO_8+(j4), 0x00010000);} wait_on(2); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if(rdata_grp==0x0){ } else { test_err++; } #ifdef GPIO0: write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO0_INTR)!=0){ test_err++; } #endif; #ifdef GPIO1: write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO1_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO1_INTR)!=0){ test_err++; } #endif; write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF); #ifdef GPIO0: GIC_ClearIRQ(87); #endif; #ifdef GPIO1: GIC_ClearIRQ(88); #endif;"]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MIZAR_LSS_SYSREG_INTR_EN1, MIZAR_LSS_SYSREG_RAW_STCR1, MIZAR_GPIO_GP0_GPIO_8, MIZAR_GPIO_GP0_INTR1_INTR_EN1, MIZAR_GPIO_GP0_INTR1_INTR_STS1, MIZAR_GPIO_GPIO_IO_CTRL_GROUP1, MIZAR_GPIO_GPIO_IO_CTRL_GROUP2, MIZAR_GPIO_GPIO_IO_CTRL_GROUP3, MIZAR_GPIO_GPIO_IO_CTRL_GROUP4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>For each pin: loop must complete without timeout (int_pend cleared in ISR). In ISR: MIZAR_GPIO_GP0_INTR1_INTR_STS1 must be non‑zero on entry; after clearing per‑pin ICLR (write 0x00010000 to each pin reg) the group status must read 0x0. System raw status in MIZAR_LSS_SYSREG_RAW_STCR1 must be cleared (readback with relevant bit 0). test_err must remain 0 to PASS.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="120" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="120" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="120" customWidth="1" min="10" max="10"/>
-    <col width="120" customWidth="1" min="11" max="11"/>
-    <col width="120" customWidth="1" min="12" max="12"/>
-    <col width="120" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
-    <col width="29" customWidth="1" min="15" max="15"/>
-    <col width="120" customWidth="1" min="16" max="16"/>
-    <col width="120" customWidth="1" min="17" max="17"/>
-    <col width="120" customWidth="1" min="18" max="18"/>
-    <col width="120" customWidth="1" min="19" max="19"/>
-    <col width="120" customWidth="1" min="20" max="20"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="10" max="10"/>
+    <col width="80" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="12" max="12"/>
+    <col width="80" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Index</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>SS / Module</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Test Case Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Test Description</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Memory Start Offset</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Memory End Offset</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Test Steps / Procedure</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Impacted Registers</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Validation / Acceptance Criteria</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Code Generation (Required / Not)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Hidden_Test_Case_Name</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Hidden_Test_Description</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Hidden_Remarks</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Hidden_Test_Steps_Procedure</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Hidden_Impacted_Registers</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Hidden_Validation_Acceptance_Criteria</t>
-        </is>
-      </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" ht="180" customHeight="1">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>GPIO</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>AHB 32-bit register interface</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>gpio_reg_wr_rd_test</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Validates 32-bit register access by checking reset defaults and verifying masked write-and-read behavior across per-pin GPIO control and group control/status registers.</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Certain registers are intentionally skipped for specific operations based on predefined skip lists. Reading input status without a driven source may report a high level, and forcing a low input level can affect bit-level selection, leading to mismatches if not accounted for.</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>["Entry: invoke the test entry function.","Reset-defaults phase: iterate all targeted per-pin control and group registers; for each readable register not marked to be skipped, read the value and compare the result (with the least significant input bit excluded) to the documented reset default.","Write phase: for each of six data patterns, iterate all targeted registers; for writable registers not marked to be skipped, write the pattern masked by the register’s writable-bit mask.","Readback/compare phase: for each register written in the previous step that is also readable, read the value masked by the readable-bit mask and compare against an expected value derived from the written pattern for writable bits and the reset default for non‑writable bits.","Completion: declare pass only if no default-value mismatches and no write/read mismatches were detected; otherwise declare fail."]</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>GPIO_33, GPIO_34, GPIO_35, GPIO_36, GPIO_37, GPIO_38, GPIO_39, GPIO_INTR_RAW_STCLR1, INTR1_INTR_EN1, INTR1_INTR_STS1, INTR2_INTR_EN1, INTR2_INTR_STS1, GPIO_IO_CTRL_GROUP1, GPIO_IO_CTRL_GROUP2, GPIO_IO_CTRL_GROUP3, GPIO_IO_CTRL_GROUP4, GPIO_DOUT_GROUP1, GPIO_DOUT_GROUP2, GPIO_DOUT_GROUP3, GPIO_DOUT_GROUP4, GPIO_DIN_GROUP1, GPIO_DIN_GROUP2, GPIO_DIN_GROUP3, GPIO_DIN_GROUP4</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>["No reset-default mismatches are observed for any readable register that is not skipped.","For each data pattern, the readback of each readable and writable register matches the expected value defined by writable-bit and readable-bit masks combined with the reset default for non‑writable bits.","Overall result is pass only if both the reset‑default and write‑read checks report zero errors."]</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>gpio_reg_wr_rd_test</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Test performs two phases over CNT=49 registers listed in addr_array[] (MIZAR_GPIO_GP0_GPIO_8..MIZAR_GPIO_GP0_GPIO_39, MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, MIZAR_GPIO_GP0_INTR1_INTR_EN1, MIZAR_GPIO_GP0_INTR1_INTR_STS1, MIZAR_GPIO_GP0_INTR2_INTR_EN1, MIZAR_GPIO_GP0_INTR2_INTR_STS1, MIZAR_GPIO_GPIO_IO_CTRL_GROUP1..4, MIZAR_GPIO_GPIO_DOUT_GROUP1..4, MIZAR_GPIO_GPIO_DIN_GROUP1..4). Phase 1 (chk_rst_val): for i=0..CNT-1, addr=addr_array[i]; if skip_rst_array[i]==1 continue; if read_mask_array[i]==0 continue; data_rd=read_reg(addr); data=(data_rd &amp; 0xfffffffe); if data==default_value_array[i] pass else def_fail_cnt++. Phase 2 (chk_rd_wr): for each j in {0xffffffff,0xaaaaaaaa,0x55555555,0xf5f5f5f5,0xA5A5A5A5,0xffff0000} set data_wr; Write loop: for i=0..CNT-1 if skip_array[i]==1 continue; if write_mask_array[i]==0 continue; write_reg(addr_array[i], (data_wr &amp; write_mask_array[i])); Readback loop: for i=0..CNT-1 if skip_array[i]==1 continue; if write_mask_array[i]==0 continue; if read_mask_array[i]==0 continue; data_rd=(read_reg(addr_array[i]) &amp; read_mask_array[i]); wr_n=(write_mask_array[i] ^ 0xffffffff); exp_val=((data_wr &amp; read_mask_array[i] &amp; write_mask_array[i]) | (wr_n &amp; read_mask_array[i] &amp; default_value_array[i])); if data_rd==exp_val pass else wr_fail_cnt++. test_case() calls chk_rst_val(); chk_rd_wr(); if(def_fail_cnt&gt;0 || wr_fail_cnt&gt;0) finish(1) else finish(0).</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>skip_array[] skips VRRW or otherwise restricted registers for write; skip_rst_array[] skips default-value checks for specific group registers. Note: when reading default values the DIN bit may become 1 if not driven; forcing zero on DIN can drive bit-level selection high, causing read mismatch with expected default.</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>["test_case(): call chk_rst_val().","chk_rst_val(): for(i=0;i&lt;CNT;i++){ addr=addr_array[i]; if(skip_rst_array[i]==1) continue; if(read_mask_array[i]==0x00000000) continue; data_rd=read_reg(addr); data=(data_rd &amp; 0xfffffffe); if(data==default_value_array[i]) { } else { def_fail_cnt++; printf failure; } }","Return to test_case(): call chk_rd_wr().","chk_rd_wr(): define chk_val[6]={0xffffffff,0xaaaaaaaa,0x55555555,0xf5f5f5f5,0xA5A5A5A5,0xffff0000}; For each j in 0..5: data_wr=chk_val[j].","Write loop: for(i=0;i&lt;CNT;i++){ addr=addr_array[i]; if(skip_array[i]==1) continue; if(write_mask_array[i]==0x00000000) continue; write_reg(addr,(data_wr &amp; write_mask_array[i])); }","Readback loop: for(i=0;i&lt;CNT;i++){ addr=addr_array[i]; if(skip_array[i]==1) continue; if(write_mask_array[i]==0x00000000) continue; if(read_mask_array[i]==0x00000000) continue; data_rd=(read_reg(addr) &amp; read_mask_array[i]); wr_n=(write_mask_array[i] ^ 0xffffffff); exp_val=((data_wr &amp; read_mask_array[i] &amp; write_mask_array[i]) | (wr_n &amp; read_mask_array[i] &amp; default_value_array[i])); if(data_rd==exp_val){ } else { wr_fail_cnt++; printf failure; } }","Return to test_case(): if(def_fail_cnt&gt;0 || wr_fail_cnt&gt;0) finish(1); else finish(0)."]</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>MIZAR_GPIO_GP0_GPIO_8, MIZAR_GPIO_GP0_GPIO_9, MIZAR_GPIO_GP0_GPIO_10, MIZAR_GPIO_GP0_GPIO_11, MIZAR_GPIO_GP0_GPIO_12, MIZAR_GPIO_GP0_GPIO_13, MIZAR_GPIO_GP0_GPIO_14, MIZAR_GPIO_GP0_GPIO_15, MIZAR_GPIO_GP0_GPIO_16, MIZAR_GPIO_GP0_GPIO_17, MIZAR_GPIO_GP0_GPIO_18, MIZAR_GPIO_GP0_GPIO_19, MIZAR_GPIO_GP0_GPIO_20, MIZAR_GPIO_GP0_GPIO_21, MIZAR_GPIO_GP0_GPIO_22, MIZAR_GPIO_GP0_GPIO_23, MIZAR_GPIO_GP0_GPIO_24, MIZAR_GPIO_GP0_GPIO_25, MIZAR_GPIO_GP0_GPIO_26, MIZAR_GPIO_GP0_GPIO_27, MIZAR_GPIO_GP0_GPIO_28, MIZAR_GPIO_GP0_GPIO_29, MIZAR_GPIO_GP0_GPIO_30, MIZAR_GPIO_GP0_GPIO_31, MIZAR_GPIO_GP0_GPIO_32, MIZAR_GPIO_GP0_GPIO_33, MIZAR_GPIO_GP0_GPIO_34, MIZAR_GPIO_GP0_GPIO_35, MIZAR_GPIO_GP0_GPIO_36, MIZAR_GPIO_GP0_GPIO_37, MIZAR_GPIO_GP0_GPIO_38, MIZAR_GPIO_GP0_GPIO_39, MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, MIZAR_GPIO_GP0_INTR1_INTR_EN1, MIZAR_GPIO_GP0_INTR1_INTR_STS1, MIZAR_GPIO_GP0_INTR2_INTR_EN1, MIZAR_GPIO_GP0_INTR2_INTR_STS1, MIZAR_GPIO_GPIO_IO_CTRL_GROUP1, MIZAR_GPIO_GPIO_IO_CTRL_GROUP2, MIZAR_GPIO_GPIO_IO_CTRL_GROUP3, MIZAR_GPIO_GPIO_IO_CTRL_GROUP4, MIZAR_GPIO_GPIO_DOUT_GROUP1, MIZAR_GPIO_GPIO_DOUT_GROUP2, MIZAR_GPIO_GPIO_DOUT_GROUP3, MIZAR_GPIO_GPIO_DOUT_GROUP4, MIZAR_GPIO_GPIO_DIN_GROUP1, MIZAR_GPIO_GPIO_DIN_GROUP2, MIZAR_GPIO_GPIO_DIN_GROUP3, MIZAR_GPIO_GPIO_DIN_GROUP4</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>PASS if def_fail_cnt==0 and wr_fail_cnt==0 at end of test_case(); else FAIL. Default check uses (read_reg(addr) &amp; 0xfffffffe) == default_value_array[i]. Write/read check expects data_rd == ((data_wr &amp; read_mask &amp; write_mask) | ((~write_mask) &amp; read_mask &amp; default_value)).</t>
-        </is>
-      </c>
+      <c r="N2" s="4" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" ht="270" customHeight="1">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>GPIO</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>interrupts can be generated based on positive edge or negative edge or level high or level low detection at GPIO input</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>test_gpio_negedge_intr_en</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Configures GPIO inputs for falling-edge detection per pin, generates a single falling edge per pad, services the interrupt, verifies per‑pin and group status, clears the status sources, and checks that the system interrupt is cleared.</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Interrupt</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>0xA0243ffc</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>0xA0243ffc</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>A known pad drive level is applied before and after generating each edge. The wait for completion is bounded with a timeout to avoid indefinite blocking.</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>["Enable the interrupt line in the interrupt controller for the selected GPIO instance.","Enable the system interrupt output for the selected GPIO instance.","Drive the external pad control register to a known high level to establish a baseline.","For each pin in the target range, configure the per‑pin control to input mode with falling‑edge detection and clear any latched per‑pin raw status. Insert a brief wait.","For each pin: clear the corresponding bit in the raw status clear register, enable only that pin in the group interrupt enable register, then arm the completion flag.","Generate a single falling edge on the selected pin via the external pad control register (high to low), with a short delay between transitions.","Wait for the ISR to clear the completion flag, with a bounded timeout to prevent hang. On timeout, record an error and continue to the next pin.","In the interrupt service routine: restore the external pad drive to high, read the per‑pin control/status register for the active pin and check input level is low after the falling edge.","Still in the ISR: confirm the group interrupt status reflects the active pin, clear the per‑pin raw status and the group raw status clear register, and verify the group status is cleared.","Clear the system interrupt source and the interrupt controller pending state to complete service."]</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>GPIO_INTR_RAW_STCLR1, INTR1_INTR_EN1, INTR1_INTR_STS1</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>["For each pin, the interrupt is observed before the timeout expires.","During service, the per‑pin input level is low immediately after the falling edge.","The group interrupt status reflects the active pin when the interrupt occurs and is fully cleared after per‑pin and group raw clears.","The system interrupt source is cleared during service.","Overall result is pass if no timeouts or status verification failures occur."]</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>test_gpio_negedge_intr_en</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Negative-edge interrupt enable test. test_case(): test_err=0; optionally GIC_EnableIRQ(87) or GIC_EnableIRQ(88) under GPIO0/GPIO1. Enable sysreg interrupt: write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR or LSS_SYSREG_INTR_EN1_GPIO1_INTR). Drive all high: write_reg(0xA0243ffc,0xffffffff). Configure pins 8..39: for i=0..31 addr1=MIZAR_GPIO_GP0_GPIO_8+(i4); write_reg(addr1,(1&lt;&lt;20)|(1&lt;&lt;18)|(1&lt;&lt;16)); wait_on(10). For each i=0..31: wr_val=(1&lt;&lt;i); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, wr_val); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, wr_val); wait_on(10); int_pend=1; write_reg(0xA0243ffc,0xffffffff); wait_on(30); write_reg(0xA0243ffc, ~wr_val); bounded wait: timeout=5000; while(int_pend &amp;&amp; timeout--) wait_on(10); if(timeout==0){ printf timeout; test_err++; }. finish(test_err). Default_IRQHandler(): local_wr=(1&lt;&lt;i); int_pend=0; write_reg(0xA0243ffc,0xffffffff); raddr=MIZAR_GPIO_GP0_GPIO_8+(i4); rdata=read_reg(raddr); if((rdata &amp; 0x1)!=0) test_err++; if((rdata &amp; 0x2)!=0x0){ rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if((rdata_grp &amp; local_wr)==0) test_err++; raddr2=MIZAR_GPIO_GP0_GPIO_8+(i4); write_reg(raddr2,(1&lt;&lt;20)|(1&lt;&lt;16)); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, local_wr); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if(rdata_grp!=0x0) test_err++; write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR or _GPIO1_INTR); GIC_ClearIRQ(87 or 88); } else { test_err++; }</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>The test uses a pad drive at address 0xA0243ffc to synthesize a falling edge per selected bit. A bounded loop with timeout=5000 and wait_on(10) prevents indefinite hang if no interrupt arrives.</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>["test_case(): test_err=0.","#ifdef GPIO0: GIC_EnableIRQ(87); #endif; #ifdef GPIO1: GIC_EnableIRQ(88); #endif.","#ifdef GPIO0: write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR); #endif.","#ifdef GPIO1: write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO1_INTR); #endif.","write_reg(0xA0243ffc, 0xffffffff);","for(i=0;i&lt;32;i++){ addr1=MIZAR_GPIO_GP0_GPIO_8+(i4); write_reg(addr1, (1u&lt;&lt;20)|(1u&lt;&lt;18)|(1u&lt;&lt;16)); wait_on(10); }","for(i=0;i&lt;32;i++){ wr_val=(1u&lt;&lt;i); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, wr_val); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, wr_val); wait_on(10); int_pend=1; write_reg(0xA0243ffc, 0xffffffff); wait_on(30); write_reg(0xA0243ffc, ~wr_val); unsigned int timeout=5000; while(int_pend &amp;&amp; timeout--){ wait_on(10);} if(timeout==0){ printf timeout; test_err++; } }","finish(test_err);","Default_IRQHandler(): local_wr=(1u&lt;&lt;i); int_pend=0; write_reg(0xA0243ffc, 0xffffffff); raddr=MIZAR_GPIO_GP0_GPIO_8+(i4); rdata=read_reg(raddr); if((rdata &amp; 0x1)!=0){ test_err++; } if((rdata &amp; 0x2)!=0x0){ rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if((rdata_grp &amp; local_wr)==0){ test_err++; } raddr2=MIZAR_GPIO_GP0_GPIO_8+(i4); write_reg(raddr2, (1u&lt;&lt;20)|(1u&lt;&lt;16)); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, local_wr); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if(rdata_grp!=0x0){ test_err++; } #ifdef GPIO0: write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); GIC_ClearIRQ(87); #endif; #ifdef GPIO1: write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO1_INTR); GIC_ClearIRQ(88); #endif; } else { test_err++; }"]</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>MIZAR_LSS_SYSREG_INTR_EN1, MIZAR_LSS_SYSREG_RAW_STCR1, MIZAR_GPIO_GP0_GPIO_8, MIZAR_GPIO_GP0_INTR1_INTR_EN1, MIZAR_GPIO_GP0_INTR1_INTR_STS1, MIZAR_GPIO_GPIO_INTR_RAW_STCLR1</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Per pin: timeout loop must exit by ISR clearing int_pend; in ISR, (rdata &amp; 0x1)==0 (DIN low) and raw bit set ((rdata &amp; 0x2)!=0); group status read MIZAR_GPIO_GP0_INTR1_INTR_STS1 must have the active bit set and become 0 after clearing per-pin and RAW_STCLR1. Sysreg raw clear write is issued; GIC pending IRQ cleared. test_err must remain 0 for PASS.</t>
-        </is>
-      </c>
+      <c r="N3" s="4" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" ht="210" customHeight="1">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>GPIO</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>interrupts can be generated based on positive edge or negative edge or level high or level low detection at GPIO input</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>test_gpio_pedge_all_pads_en</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Enables rising‑edge detection for all targeted GPIO inputs, asserts a single rising edge per pad using an external drive register, services the interrupt by masking, clearing per‑pin raw status, and verifying group status clears, then re‑enables the group interrupt for the next iteration.</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Interrupt</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>0xA0243ffc</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>0xA0243ffc</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Per‑pin edge detection is configured before enabling the group interrupt. An external pad control register is used to generate known low‑to‑high transitions. A bounded wait prevents indefinite stalls if an interrupt is not observed.</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>["Enable the interrupt line in the interrupt controller for the selected GPIO instance.","Enable the system interrupt output for the selected GPIO instance.","For each target pin, program the per‑pin control to enable rising‑edge detection.","Set the group I/O control registers so the pins operate as inputs.","Enable all bits in the group interrupt enable register.","For each pin: drive the external pad control register low, arm the completion flag, then drive the external pad control register high to create a single rising edge.","Wait for the ISR to clear the completion flag with a bounded timeout; on timeout, flag an error and stop further iterations.","Optionally drive the external pad control register low to prepare for the next iteration.","In the ISR: read the group interrupt status, mask the group interrupt, clear per‑pin raw status for all pins, and verify the group interrupt status clears to zero.","Clear the system interrupt source, verify the system status is cleared, re‑enable the group interrupt, and clear the pending state in the interrupt controller."]</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>INTR1_INTR_EN1, INTR1_INTR_STS1, GPIO_IO_CTRL_GROUP1, GPIO_IO_CTRL_GROUP2, GPIO_IO_CTRL_GROUP3, GPIO_IO_CTRL_GROUP4</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>["For each pin, the interrupt occurs before the timeout expires.","Group interrupt status is non‑zero on entry to the ISR and becomes zero after clearing per‑pin raw status.","The system interrupt status is cleared during service.","Overall result is pass if no timeouts and no status verification failures occur."]</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>test_gpio_pedge_all_pads_en</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Positive-edge all‑pads enable test. test_case(): optionally GIC_EnableIRQ(87/88); enable sysreg interrupt via write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR or _GPIO1_INTR). For i=0..31: write_reg(MIZAR_GPIO_GP0_GPIO_8+(i4), 0x00020000) to set PEIE (bit17). wait_on(10). Set input mode: write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP1..4, 0x000000FF). wait_on(10). Enable group: write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF). For each i=0..31: write_reg(0xA0243ffc,0x00000000); wait_on(10); int_pend=1; write_reg(0xA0243ffc,0xFFFFFFFF); int timeout=2000; while(int_pend==1 &amp;&amp; --timeout&gt;0){ wait_on(10);} if(timeout==0){ printf timeout; test_err++; break;} write_reg(0xA0243ffc,0x00000000); wait_on(10). finish(test_err). Default_IRQHandler(): wr_val=(1&lt;&lt;i); int_pend=0; rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0x00000000); if((rdata_grp &amp; 0xffffffff)!=0) OK else { printf error; test_err++; }. For j=0..31: write_reg(MIZAR_GPIO_GP0_GPIO_8+(j4),0x00010000) to set ICLR; wait_on(2); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if(rdata_grp==0x0) OK else { test_err++; }. Clear sysreg raw: write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR or _GPIO1_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if(rdata &amp; bit)!=0 then test_err++; Re‑enable: write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF); GIC_ClearIRQ(87 or 88).</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>External pad drive at 0xA0243ffc is toggled low‑to‑high to generate a rising edge. The wait loop uses timeout=2000 and wait_on(10) per iteration to bound execution time.</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>["test_case(): #ifdef GPIO0: GIC_EnableIRQ(87); #endif; #ifdef GPIO1: GIC_EnableIRQ(88); #endif; test_err=0.","#ifdef GPIO0: write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR); #endif; #ifdef GPIO1: write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO1_INTR); #endif.","for(i=0;i&lt;32;i++){ write_reg(MIZAR_GPIO_GP0_GPIO_8+(i4), 0x00020000); }","wait_on(10);","write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP1, 0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP2, 0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP3, 0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP4, 0x000000FF);","wait_on(10);","write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF);","for(i=0;i&lt;32;i++){ write_reg(0xA0243ffc, 0x00000000); wait_on(10); int_pend=1; write_reg(0xA0243ffc, 0xFFFFFFFF); int timeout=2000; while((int_pend==1) &amp;&amp; (--timeout&gt;0)){ wait_on(10);} if(timeout==0){ printf timeout; test_err++; break;} write_reg(0xA0243ffc, 0x00000000); wait_on(10); }","finish(test_err);","Default_IRQHandler(): wr_val=(1&lt;&lt;i); int_pend=0; rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0x00000000); if((rdata_grp &amp; 0xffffffff)!=0){ } else { printf error; test_err++; } for(j=0;j&lt;32;j++){ write_reg(MIZAR_GPIO_GP0_GPIO_8+(j4), 0x00010000);} wait_on(2); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if(rdata_grp==0x0){ } else { test_err++; } #ifdef GPIO0: write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO0_INTR)!=0){ test_err++; } #endif; #ifdef GPIO1: write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO1_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO1_INTR)!=0){ test_err++; } #endif; write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF); #ifdef GPIO0: GIC_ClearIRQ(87); #endif; #ifdef GPIO1: GIC_ClearIRQ(88); #endif;"]</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>MIZAR_LSS_SYSREG_INTR_EN1, MIZAR_LSS_SYSREG_RAW_STCR1, MIZAR_GPIO_GP0_GPIO_8, MIZAR_GPIO_GP0_INTR1_INTR_EN1, MIZAR_GPIO_GP0_INTR1_INTR_STS1, MIZAR_GPIO_GPIO_IO_CTRL_GROUP1, MIZAR_GPIO_GPIO_IO_CTRL_GROUP2, MIZAR_GPIO_GPIO_IO_CTRL_GROUP3, MIZAR_GPIO_GPIO_IO_CTRL_GROUP4</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>For each pin: loop must complete without timeout (int_pend cleared in ISR). In ISR: MIZAR_GPIO_GP0_INTR1_INTR_STS1 must be non‑zero on entry; after clearing per‑pin ICLR (write 0x00010000 to each pin reg) the group status must read 0x0. System raw status in MIZAR_LSS_SYSREG_RAW_STCR1 must be cleared (readback with relevant bit 0). test_err must remain 0 to PASS.</t>
-        </is>
-      </c>
+      <c r="N4" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Test_Output/GPIO/TestPlan/GPIO_TestPlan_1.xlsx
+++ b/Test_Output/GPIO/TestPlan/GPIO_TestPlan_1.xlsx
@@ -444,138 +444,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Hidden_Test_Case_Name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Hidden_Test_Description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Hidden_Remarks</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Hidden_Test_Steps_Procedure</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Hidden_Impacted_Registers</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Hidden_Validation_Acceptance_Criteria</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>gpio_reg_wr_rd_test</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Test performs two phases over CNT=49 registers listed in addr_array[] (MIZAR_GPIO_GP0_GPIO_8..MIZAR_GPIO_GP0_GPIO_39, MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, MIZAR_GPIO_GP0_INTR1_INTR_EN1, MIZAR_GPIO_GP0_INTR1_INTR_STS1, MIZAR_GPIO_GP0_INTR2_INTR_EN1, MIZAR_GPIO_GP0_INTR2_INTR_STS1, MIZAR_GPIO_GPIO_IO_CTRL_GROUP1..4, MIZAR_GPIO_GPIO_DOUT_GROUP1..4, MIZAR_GPIO_GPIO_DIN_GROUP1..4). Phase 1 (chk_rst_val): for i=0..CNT-1, addr=addr_array[i]; if skip_rst_array[i]==1 continue; if read_mask_array[i]==0 continue; data_rd=read_reg(addr); data=(data_rd &amp; 0xfffffffe); if data==default_value_array[i] pass else def_fail_cnt++. Phase 2 (chk_rd_wr): for each j in {0xffffffff,0xaaaaaaaa,0x55555555,0xf5f5f5f5,0xA5A5A5A5,0xffff0000} set data_wr; Write loop: for i=0..CNT-1 if skip_array[i]==1 continue; if write_mask_array[i]==0 continue; write_reg(addr_array[i], (data_wr &amp; write_mask_array[i])); Readback loop: for i=0..CNT-1 if skip_array[i]==1 continue; if write_mask_array[i]==0 continue; if read_mask_array[i]==0 continue; data_rd=(read_reg(addr_array[i]) &amp; read_mask_array[i]); wr_n=(write_mask_array[i] ^ 0xffffffff); exp_val=((data_wr &amp; read_mask_array[i] &amp; write_mask_array[i]) | (wr_n &amp; read_mask_array[i] &amp; default_value_array[i])); if data_rd==exp_val pass else wr_fail_cnt++. test_case() calls chk_rst_val(); chk_rd_wr(); if(def_fail_cnt&gt;0 || wr_fail_cnt&gt;0) finish(1) else finish(0).</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>skip_array[] skips VRRW or otherwise restricted registers for write; skip_rst_array[] skips default-value checks for specific group registers. Note: when reading default values the DIN bit may become 1 if not driven; forcing zero on DIN can drive bit-level selection high, causing read mismatch with expected default.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>["test_case(): call chk_rst_val().","chk_rst_val(): for(i=0;i&lt;CNT;i++){ addr=addr_array[i]; if(skip_rst_array[i]==1) continue; if(read_mask_array[i]==0x00000000) continue; data_rd=read_reg(addr); data=(data_rd &amp; 0xfffffffe); if(data==default_value_array[i]) { } else { def_fail_cnt++; printf failure; } }","Return to test_case(): call chk_rd_wr().","chk_rd_wr(): define chk_val[6]={0xffffffff,0xaaaaaaaa,0x55555555,0xf5f5f5f5,0xA5A5A5A5,0xffff0000}; For each j in 0..5: data_wr=chk_val[j].","Write loop: for(i=0;i&lt;CNT;i++){ addr=addr_array[i]; if(skip_array[i]==1) continue; if(write_mask_array[i]==0x00000000) continue; write_reg(addr,(data_wr &amp; write_mask_array[i])); }","Readback loop: for(i=0;i&lt;CNT;i++){ addr=addr_array[i]; if(skip_array[i]==1) continue; if(write_mask_array[i]==0x00000000) continue; if(read_mask_array[i]==0x00000000) continue; data_rd=(read_reg(addr) &amp; read_mask_array[i]); wr_n=(write_mask_array[i] ^ 0xffffffff); exp_val=((data_wr &amp; read_mask_array[i] &amp; write_mask_array[i]) | (wr_n &amp; read_mask_array[i] &amp; default_value_array[i])); if(data_rd==exp_val){ } else { wr_fail_cnt++; printf failure; } }","Return to test_case(): if(def_fail_cnt&gt;0 || wr_fail_cnt&gt;0) finish(1); else finish(0)."]</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>MIZAR_GPIO_GP0_GPIO_8, MIZAR_GPIO_GP0_GPIO_9, MIZAR_GPIO_GP0_GPIO_10, MIZAR_GPIO_GP0_GPIO_11, MIZAR_GPIO_GP0_GPIO_12, MIZAR_GPIO_GP0_GPIO_13, MIZAR_GPIO_GP0_GPIO_14, MIZAR_GPIO_GP0_GPIO_15, MIZAR_GPIO_GP0_GPIO_16, MIZAR_GPIO_GP0_GPIO_17, MIZAR_GPIO_GP0_GPIO_18, MIZAR_GPIO_GP0_GPIO_19, MIZAR_GPIO_GP0_GPIO_20, MIZAR_GPIO_GP0_GPIO_21, MIZAR_GPIO_GP0_GPIO_22, MIZAR_GPIO_GP0_GPIO_23, MIZAR_GPIO_GP0_GPIO_24, MIZAR_GPIO_GP0_GPIO_25, MIZAR_GPIO_GP0_GPIO_26, MIZAR_GPIO_GP0_GPIO_27, MIZAR_GPIO_GP0_GPIO_28, MIZAR_GPIO_GP0_GPIO_29, MIZAR_GPIO_GP0_GPIO_30, MIZAR_GPIO_GP0_GPIO_31, MIZAR_GPIO_GP0_GPIO_32, MIZAR_GPIO_GP0_GPIO_33, MIZAR_GPIO_GP0_GPIO_34, MIZAR_GPIO_GP0_GPIO_35, MIZAR_GPIO_GP0_GPIO_36, MIZAR_GPIO_GP0_GPIO_37, MIZAR_GPIO_GP0_GPIO_38, MIZAR_GPIO_GP0_GPIO_39, MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, MIZAR_GPIO_GP0_INTR1_INTR_EN1, MIZAR_GPIO_GP0_INTR1_INTR_STS1, MIZAR_GPIO_GP0_INTR2_INTR_EN1, MIZAR_GPIO_GP0_INTR2_INTR_STS1, MIZAR_GPIO_GPIO_IO_CTRL_GROUP1, MIZAR_GPIO_GPIO_IO_CTRL_GROUP2, MIZAR_GPIO_GPIO_IO_CTRL_GROUP3, MIZAR_GPIO_GPIO_IO_CTRL_GROUP4, MIZAR_GPIO_GPIO_DOUT_GROUP1, MIZAR_GPIO_GPIO_DOUT_GROUP2, MIZAR_GPIO_GPIO_DOUT_GROUP3, MIZAR_GPIO_GPIO_DOUT_GROUP4, MIZAR_GPIO_GPIO_DIN_GROUP1, MIZAR_GPIO_GPIO_DIN_GROUP2, MIZAR_GPIO_GPIO_DIN_GROUP3, MIZAR_GPIO_GPIO_DIN_GROUP4</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>PASS if def_fail_cnt==0 and wr_fail_cnt==0 at end of test_case(); else FAIL. Default check uses (read_reg(addr) &amp; 0xfffffffe) == default_value_array[i]. Write/read check expects data_rd == ((data_wr &amp; read_mask &amp; write_mask) | ((~write_mask) &amp; read_mask &amp; default_value)).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>test_gpio_negedge_intr_en</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Negative-edge interrupt enable test. test_case(): test_err=0; optionally GIC_EnableIRQ(87) or GIC_EnableIRQ(88) under GPIO0/GPIO1. Enable sysreg interrupt: write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR or LSS_SYSREG_INTR_EN1_GPIO1_INTR). Drive all high: write_reg(0xA0243ffc,0xffffffff). Configure pins 8..39: for i=0..31 addr1=MIZAR_GPIO_GP0_GPIO_8+(i4); write_reg(addr1,(1&lt;&lt;20)|(1&lt;&lt;18)|(1&lt;&lt;16)); wait_on(10). For each i=0..31: wr_val=(1&lt;&lt;i); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, wr_val); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, wr_val); wait_on(10); int_pend=1; write_reg(0xA0243ffc,0xffffffff); wait_on(30); write_reg(0xA0243ffc, ~wr_val); bounded wait: timeout=5000; while(int_pend &amp;&amp; timeout--) wait_on(10); if(timeout==0){ printf timeout; test_err++; }. finish(test_err). Default_IRQHandler(): local_wr=(1&lt;&lt;i); int_pend=0; write_reg(0xA0243ffc,0xffffffff); raddr=MIZAR_GPIO_GP0_GPIO_8+(i4); rdata=read_reg(raddr); if((rdata &amp; 0x1)!=0) test_err++; if((rdata &amp; 0x2)!=0x0){ rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if((rdata_grp &amp; local_wr)==0) test_err++; raddr2=MIZAR_GPIO_GP0_GPIO_8+(i4); write_reg(raddr2,(1&lt;&lt;20)|(1&lt;&lt;16)); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, local_wr); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if(rdata_grp!=0x0) test_err++; write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR or _GPIO1_INTR); GIC_ClearIRQ(87 or 88); } else { test_err++; }</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>The test uses a pad drive at address 0xA0243ffc to synthesize a falling edge per selected bit. A bounded loop with timeout=5000 and wait_on(10) prevents indefinite hang if no interrupt arrives.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>["test_case(): test_err=0.","#ifdef GPIO0: GIC_EnableIRQ(87); #endif; #ifdef GPIO1: GIC_EnableIRQ(88); #endif.","#ifdef GPIO0: write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR); #endif.","#ifdef GPIO1: write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO1_INTR); #endif.","write_reg(0xA0243ffc, 0xffffffff);","for(i=0;i&lt;32;i++){ addr1=MIZAR_GPIO_GP0_GPIO_8+(i4); write_reg(addr1, (1u&lt;&lt;20)|(1u&lt;&lt;18)|(1u&lt;&lt;16)); wait_on(10); }","for(i=0;i&lt;32;i++){ wr_val=(1u&lt;&lt;i); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, wr_val); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, wr_val); wait_on(10); int_pend=1; write_reg(0xA0243ffc, 0xffffffff); wait_on(30); write_reg(0xA0243ffc, ~wr_val); unsigned int timeout=5000; while(int_pend &amp;&amp; timeout--){ wait_on(10);} if(timeout==0){ printf timeout; test_err++; } }","finish(test_err);","Default_IRQHandler(): local_wr=(1u&lt;&lt;i); int_pend=0; write_reg(0xA0243ffc, 0xffffffff); raddr=MIZAR_GPIO_GP0_GPIO_8+(i4); rdata=read_reg(raddr); if((rdata &amp; 0x1)!=0){ test_err++; } if((rdata &amp; 0x2)!=0x0){ rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if((rdata_grp &amp; local_wr)==0){ test_err++; } raddr2=MIZAR_GPIO_GP0_GPIO_8+(i4); write_reg(raddr2, (1u&lt;&lt;20)|(1u&lt;&lt;16)); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, local_wr); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if(rdata_grp!=0x0){ test_err++; } #ifdef GPIO0: write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); GIC_ClearIRQ(87); #endif; #ifdef GPIO1: write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO1_INTR); GIC_ClearIRQ(88); #endif; } else { test_err++; }"]</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>MIZAR_LSS_SYSREG_INTR_EN1, MIZAR_LSS_SYSREG_RAW_STCR1, MIZAR_GPIO_GP0_GPIO_8, MIZAR_GPIO_GP0_INTR1_INTR_EN1, MIZAR_GPIO_GP0_INTR1_INTR_STS1, MIZAR_GPIO_GPIO_INTR_RAW_STCLR1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Per pin: timeout loop must exit by ISR clearing int_pend; in ISR, (rdata &amp; 0x1)==0 (DIN low) and raw bit set ((rdata &amp; 0x2)!=0); group status read MIZAR_GPIO_GP0_INTR1_INTR_STS1 must have the active bit set and become 0 after clearing per-pin and RAW_STCLR1. Sysreg raw clear write is issued; GIC pending IRQ cleared. test_err must remain 0 for PASS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>test_gpio_pedge_all_pads_en</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Positive-edge all‑pads enable test. test_case(): optionally GIC_EnableIRQ(87/88); enable sysreg interrupt via write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR or _GPIO1_INTR). For i=0..31: write_reg(MIZAR_GPIO_GP0_GPIO_8+(i4), 0x00020000) to set PEIE (bit17). wait_on(10). Set input mode: write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP1..4, 0x000000FF). wait_on(10). Enable group: write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF). For each i=0..31: write_reg(0xA0243ffc,0x00000000); wait_on(10); int_pend=1; write_reg(0xA0243ffc,0xFFFFFFFF); int timeout=2000; while(int_pend==1 &amp;&amp; --timeout&gt;0){ wait_on(10);} if(timeout==0){ printf timeout; test_err++; break;} write_reg(0xA0243ffc,0x00000000); wait_on(10). finish(test_err). Default_IRQHandler(): wr_val=(1&lt;&lt;i); int_pend=0; rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0x00000000); if((rdata_grp &amp; 0xffffffff)!=0) OK else { printf error; test_err++; }. For j=0..31: write_reg(MIZAR_GPIO_GP0_GPIO_8+(j4),0x00010000) to set ICLR; wait_on(2); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if(rdata_grp==0x0) OK else { test_err++; }. Clear sysreg raw: write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR or _GPIO1_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if(rdata &amp; bit)!=0 then test_err++; Re‑enable: write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF); GIC_ClearIRQ(87 or 88).</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>External pad drive at 0xA0243ffc is toggled low‑to‑high to generate a rising edge. The wait loop uses timeout=2000 and wait_on(10) per iteration to bound execution time.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>["test_case(): #ifdef GPIO0: GIC_EnableIRQ(87); #endif; #ifdef GPIO1: GIC_EnableIRQ(88); #endif; test_err=0.","#ifdef GPIO0: write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR); #endif; #ifdef GPIO1: write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO1_INTR); #endif.","for(i=0;i&lt;32;i++){ write_reg(MIZAR_GPIO_GP0_GPIO_8+(i4), 0x00020000); }","wait_on(10);","write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP1, 0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP2, 0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP3, 0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP4, 0x000000FF);","wait_on(10);","write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF);","for(i=0;i&lt;32;i++){ write_reg(0xA0243ffc, 0x00000000); wait_on(10); int_pend=1; write_reg(0xA0243ffc, 0xFFFFFFFF); int timeout=2000; while((int_pend==1) &amp;&amp; (--timeout&gt;0)){ wait_on(10);} if(timeout==0){ printf timeout; test_err++; break;} write_reg(0xA0243ffc, 0x00000000); wait_on(10); }","finish(test_err);","Default_IRQHandler(): wr_val=(1&lt;&lt;i); int_pend=0; rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0x00000000); if((rdata_grp &amp; 0xffffffff)!=0){ } else { printf error; test_err++; } for(j=0;j&lt;32;j++){ write_reg(MIZAR_GPIO_GP0_GPIO_8+(j4), 0x00010000);} wait_on(2); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if(rdata_grp==0x0){ } else { test_err++; } #ifdef GPIO0: write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO0_INTR)!=0){ test_err++; } #endif; #ifdef GPIO1: write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO1_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO1_INTR)!=0){ test_err++; } #endif; write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF); #ifdef GPIO0: GIC_ClearIRQ(87); #endif; #ifdef GPIO1: GIC_ClearIRQ(88); #endif;"]</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MIZAR_LSS_SYSREG_INTR_EN1, MIZAR_LSS_SYSREG_RAW_STCR1, MIZAR_GPIO_GP0_GPIO_8, MIZAR_GPIO_GP0_INTR1_INTR_EN1, MIZAR_GPIO_GP0_INTR1_INTR_STS1, MIZAR_GPIO_GPIO_IO_CTRL_GROUP1, MIZAR_GPIO_GPIO_IO_CTRL_GROUP2, MIZAR_GPIO_GPIO_IO_CTRL_GROUP3, MIZAR_GPIO_GPIO_IO_CTRL_GROUP4</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>For each pin: loop must complete without timeout (int_pend cleared in ISR). In ISR: MIZAR_GPIO_GP0_INTR1_INTR_STS1 must be non‑zero on entry; after clearing per‑pin ICLR (write 0x00010000 to each pin reg) the group status must read 0x0. System raw status in MIZAR_LSS_SYSREG_RAW_STCR1 must be cleared (readback with relevant bit 0). test_err must remain 0 to PASS.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Test_Output/GPIO/TestPlan/GPIO_TestPlan_1.xlsx
+++ b/Test_Output/GPIO/TestPlan/GPIO_TestPlan_1.xlsx
@@ -4,11 +4,11 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Meta_data_sheet" sheetId="1" state="veryHidden" r:id="rId1"/>
-    <sheet name="TestPlan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TestPlan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Meta_data_sheet" sheetId="2" state="veryHidden" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -64,7 +64,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -78,6 +78,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -444,9 +447,296 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="10" max="10"/>
+    <col width="80" customWidth="1" min="11" max="11"/>
+    <col width="80" customWidth="1" min="12" max="12"/>
+    <col width="80" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>SS / Module</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Test Case Name</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Test Description</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Mode</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Memory Start Offset</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Memory End Offset</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Test Steps / Procedure</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Impacted Registers</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Validation / Acceptance Criteria</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Code Generation (Required / Not)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="180" customHeight="1">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>GPIO</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>AHB 32-bit register interface</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>gpio_reg_wr_rd_test</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Validates 32-bit register access by checking reset defaults and verifying masked write-and-read behavior across per-pin GPIO control and group control/status registers.</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Certain registers are intentionally skipped for specific operations based on predefined skip lists. Reading input status without a driven source may report a high level, and forcing a low input level can affect bit-level selection, leading to mismatches if not accounted for.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>["Entry: invoke the test entry function.","Reset-defaults phase: iterate all targeted per-pin control and group registers; for each readable register not marked to be skipped, read the value and compare the result (with the least significant input bit excluded) to the documented reset default.","Write phase: for each of six data patterns, iterate all targeted registers; for writable registers not marked to be skipped, write the pattern masked by the register’s writable-bit mask.","Readback/compare phase: for each register written in the previous step that is also readable, read the value masked by the readable-bit mask and compare against an expected value derived from the written pattern for writable bits and the reset default for non‑writable bits.","Completion: declare pass only if no default-value mismatches and no write/read mismatches were detected; otherwise declare fail."]</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>GPIO_33, GPIO_34, GPIO_35, GPIO_36, GPIO_37, GPIO_38, GPIO_39, GPIO_INTR_RAW_STCLR1, INTR1_INTR_EN1, INTR1_INTR_STS1, INTR2_INTR_EN1, INTR2_INTR_STS1, GPIO_IO_CTRL_GROUP1, GPIO_IO_CTRL_GROUP2, GPIO_IO_CTRL_GROUP3, GPIO_IO_CTRL_GROUP4, GPIO_DOUT_GROUP1, GPIO_DOUT_GROUP2, GPIO_DOUT_GROUP3, GPIO_DOUT_GROUP4, GPIO_DIN_GROUP1, GPIO_DIN_GROUP2, GPIO_DIN_GROUP3, GPIO_DIN_GROUP4</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>["No reset-default mismatches are observed for any readable register that is not skipped.","For each data pattern, the readback of each readable and writable register matches the expected value defined by writable-bit and readable-bit masks combined with the reset default for non‑writable bits.","Overall result is pass only if both the reset‑default and write‑read checks report zero errors."]</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="255" customHeight="1">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>GPIO</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>interrupts can be generated based on positive edge or negative edge or level high or level low detection at GPIO input</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>test_gpio_negedge_intr_en</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Configures GPIO inputs for falling-edge detection per pin, generates a single falling edge per pad, services the interrupt, verifies per‑pin and group status, clears the status sources, and checks that the system interrupt is cleared.</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Interrupt</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>0xA0243ffc</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>0xA0243ffc</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>A known pad drive level is applied before and after generating each edge. The wait for completion is bounded with a timeout to avoid indefinite blocking.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>["Enable the interrupt line in the interrupt controller for the selected GPIO instance.","Enable the system interrupt output for the selected GPIO instance.","Drive the external pad control register to a known high level to establish a baseline.","For each pin in the target range, configure the per‑pin control to input mode with falling‑edge detection and clear any latched per‑pin raw status. Insert a brief wait.","For each pin: clear the corresponding bit in the raw status clear register, enable only that pin in the group interrupt enable register, then arm the completion flag.","Generate a single falling edge on the selected pin via the external pad control register (high to low), with a short delay between transitions.","Wait for the ISR to clear the completion flag, with a bounded timeout to prevent hang. On timeout, record an error and continue to the next pin.","In the interrupt service routine: restore the external pad drive to high, read the per‑pin control/status register for the active pin and check input level is low after the falling edge.","Still in the ISR: confirm the group interrupt status reflects the active pin, clear the per‑pin raw status and the group raw status clear register, and verify the group status is cleared.","Clear the system interrupt source and the interrupt controller pending state to complete service."]</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>GPIO_INTR_RAW_STCLR1, INTR1_INTR_EN1, INTR1_INTR_STS1</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>["For each pin, the interrupt is observed before the timeout expires.","During service, the per‑pin input level is low immediately after the falling edge.","The group interrupt status reflects the active pin when the interrupt occurs and is fully cleared after per‑pin and group raw clears.","The system interrupt source is cleared during service.","Overall result is pass if no timeouts or status verification failures occur."]</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="210" customHeight="1">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>GPIO</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>interrupts can be generated based on positive edge or negative edge or level high or level low detection at GPIO input</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>test_gpio_pedge_all_pads_en</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Enables rising‑edge detection for all targeted GPIO inputs, asserts a single rising edge per pad using an external drive register, services the interrupt by masking, clearing per‑pin raw status, and verifying group status clears, then re‑enables the group interrupt for the next iteration.</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Interrupt</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>0xA0243ffc</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>0xA0243ffc</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Per‑pin edge detection is configured before enabling the group interrupt. An external pad control register is used to generate known low‑to‑high transitions. A bounded wait prevents indefinite stalls if an interrupt is not observed.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>["Enable the interrupt line in the interrupt controller for the selected GPIO instance.","Enable the system interrupt output for the selected GPIO instance.","For each target pin, program the per‑pin control to enable rising‑edge detection.","Set the group I/O control registers so the pins operate as inputs.","Enable all bits in the group interrupt enable register.","For each pin: drive the external pad control register low, arm the completion flag, then drive the external pad control register high to create a single rising edge.","Wait for the ISR to clear the completion flag with a bounded timeout; on timeout, flag an error and stop further iterations.","Optionally drive the external pad control register low to prepare for the next iteration.","In the ISR: read the group interrupt status, mask the group interrupt, clear per‑pin raw status for all pins, and verify the group interrupt status clears to zero.","Clear the system interrupt source, verify the system status is cleared, re‑enable the group interrupt, and clear the pending state in the interrupt controller."]</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>INTR1_INTR_EN1, INTR1_INTR_STS1, GPIO_IO_CTRL_GROUP1, GPIO_IO_CTRL_GROUP2, GPIO_IO_CTRL_GROUP3, GPIO_IO_CTRL_GROUP4</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>["For each pin, the interrupt occurs before the timeout expires.","Group interrupt status is non‑zero on entry to the ISR and becomes zero after clearing per‑pin raw status.","The system interrupt status is cleared during service.","Overall result is pass if no timeouts and no status verification failures occur."]</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="n"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -457,296 +747,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="80" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="80" customWidth="1" min="10" max="10"/>
-    <col width="80" customWidth="1" min="11" max="11"/>
-    <col width="80" customWidth="1" min="12" max="12"/>
-    <col width="80" customWidth="1" min="13" max="13"/>
-    <col width="36" customWidth="1" min="14" max="14"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Index</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>SS / Module</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Test Case Name</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Test Description</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Mode</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Memory Start Offset</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Memory End Offset</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>Test Steps / Procedure</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>Impacted Registers</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>Validation / Acceptance Criteria</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>Code Generation (Required / Not)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="180" customHeight="1">
-      <c r="A2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>GPIO</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>AHB 32-bit register interface</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>gpio_reg_wr_rd_test</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>Validates 32-bit register access by checking reset defaults and verifying masked write-and-read behavior across per-pin GPIO control and group control/status registers.</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>Certain registers are intentionally skipped for specific operations based on predefined skip lists. Reading input status without a driven source may report a high level, and forcing a low input level can affect bit-level selection, leading to mismatches if not accounted for.</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>["Entry: invoke the test entry function.","Reset-defaults phase: iterate all targeted per-pin control and group registers; for each readable register not marked to be skipped, read the value and compare the result (with the least significant input bit excluded) to the documented reset default.","Write phase: for each of six data patterns, iterate all targeted registers; for writable registers not marked to be skipped, write the pattern masked by the register’s writable-bit mask.","Readback/compare phase: for each register written in the previous step that is also readable, read the value masked by the readable-bit mask and compare against an expected value derived from the written pattern for writable bits and the reset default for non‑writable bits.","Completion: declare pass only if no default-value mismatches and no write/read mismatches were detected; otherwise declare fail."]</t>
-        </is>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>GPIO_33, GPIO_34, GPIO_35, GPIO_36, GPIO_37, GPIO_38, GPIO_39, GPIO_INTR_RAW_STCLR1, INTR1_INTR_EN1, INTR1_INTR_STS1, INTR2_INTR_EN1, INTR2_INTR_STS1, GPIO_IO_CTRL_GROUP1, GPIO_IO_CTRL_GROUP2, GPIO_IO_CTRL_GROUP3, GPIO_IO_CTRL_GROUP4, GPIO_DOUT_GROUP1, GPIO_DOUT_GROUP2, GPIO_DOUT_GROUP3, GPIO_DOUT_GROUP4, GPIO_DIN_GROUP1, GPIO_DIN_GROUP2, GPIO_DIN_GROUP3, GPIO_DIN_GROUP4</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>["No reset-default mismatches are observed for any readable register that is not skipped.","For each data pattern, the readback of each readable and writable register matches the expected value defined by writable-bit and readable-bit masks combined with the reset default for non‑writable bits.","Overall result is pass only if both the reset‑default and write‑read checks report zero errors."]</t>
-        </is>
-      </c>
-      <c r="N2" s="4" t="n"/>
-    </row>
-    <row r="3" ht="270" customHeight="1">
-      <c r="A3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>GPIO</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>interrupts can be generated based on positive edge or negative edge or level high or level low detection at GPIO input</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>test_gpio_negedge_intr_en</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Configures GPIO inputs for falling-edge detection per pin, generates a single falling edge per pad, services the interrupt, verifies per‑pin and group status, clears the status sources, and checks that the system interrupt is cleared.</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Interrupt</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>0xA0243ffc</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>0xA0243ffc</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>A known pad drive level is applied before and after generating each edge. The wait for completion is bounded with a timeout to avoid indefinite blocking.</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>["Enable the interrupt line in the interrupt controller for the selected GPIO instance.","Enable the system interrupt output for the selected GPIO instance.","Drive the external pad control register to a known high level to establish a baseline.","For each pin in the target range, configure the per‑pin control to input mode with falling‑edge detection and clear any latched per‑pin raw status. Insert a brief wait.","For each pin: clear the corresponding bit in the raw status clear register, enable only that pin in the group interrupt enable register, then arm the completion flag.","Generate a single falling edge on the selected pin via the external pad control register (high to low), with a short delay between transitions.","Wait for the ISR to clear the completion flag, with a bounded timeout to prevent hang. On timeout, record an error and continue to the next pin.","In the interrupt service routine: restore the external pad drive to high, read the per‑pin control/status register for the active pin and check input level is low after the falling edge.","Still in the ISR: confirm the group interrupt status reflects the active pin, clear the per‑pin raw status and the group raw status clear register, and verify the group status is cleared.","Clear the system interrupt source and the interrupt controller pending state to complete service."]</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>GPIO_INTR_RAW_STCLR1, INTR1_INTR_EN1, INTR1_INTR_STS1</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>["For each pin, the interrupt is observed before the timeout expires.","During service, the per‑pin input level is low immediately after the falling edge.","The group interrupt status reflects the active pin when the interrupt occurs and is fully cleared after per‑pin and group raw clears.","The system interrupt source is cleared during service.","Overall result is pass if no timeouts or status verification failures occur."]</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="n"/>
-    </row>
-    <row r="4" ht="210" customHeight="1">
-      <c r="A4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>GPIO</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>interrupts can be generated based on positive edge or negative edge or level high or level low detection at GPIO input</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>test_gpio_pedge_all_pads_en</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Enables rising‑edge detection for all targeted GPIO inputs, asserts a single rising edge per pad using an external drive register, services the interrupt by masking, clearing per‑pin raw status, and verifying group status clears, then re‑enables the group interrupt for the next iteration.</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Interrupt</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>0xA0243ffc</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>0xA0243ffc</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>Per‑pin edge detection is configured before enabling the group interrupt. An external pad control register is used to generate known low‑to‑high transitions. A bounded wait prevents indefinite stalls if an interrupt is not observed.</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>["Enable the interrupt line in the interrupt controller for the selected GPIO instance.","Enable the system interrupt output for the selected GPIO instance.","For each target pin, program the per‑pin control to enable rising‑edge detection.","Set the group I/O control registers so the pins operate as inputs.","Enable all bits in the group interrupt enable register.","For each pin: drive the external pad control register low, arm the completion flag, then drive the external pad control register high to create a single rising edge.","Wait for the ISR to clear the completion flag with a bounded timeout; on timeout, flag an error and stop further iterations.","Optionally drive the external pad control register low to prepare for the next iteration.","In the ISR: read the group interrupt status, mask the group interrupt, clear per‑pin raw status for all pins, and verify the group interrupt status clears to zero.","Clear the system interrupt source, verify the system status is cleared, re‑enable the group interrupt, and clear the pending state in the interrupt controller."]</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>INTR1_INTR_EN1, INTR1_INTR_STS1, GPIO_IO_CTRL_GROUP1, GPIO_IO_CTRL_GROUP2, GPIO_IO_CTRL_GROUP3, GPIO_IO_CTRL_GROUP4</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>["For each pin, the interrupt occurs before the timeout expires.","Group interrupt status is non‑zero on entry to the ISR and becomes zero after clearing per‑pin raw status.","The system interrupt status is cleared during service.","Overall result is pass if no timeouts and no status verification failures occur."]</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="n"/>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Test_Output/GPIO/TestPlan/GPIO_TestPlan_1.xlsx
+++ b/Test_Output/GPIO/TestPlan/GPIO_TestPlan_1.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="GPIO_TestCases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="GPIO_TestPlan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Hidden_Details" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -49,9 +51,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,26 +427,26 @@
   <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="100" customWidth="1" min="3" max="3"/>
+    <col width="82" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="100" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="82" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="100" customWidth="1" min="10" max="10"/>
-    <col width="100" customWidth="1" min="11" max="11"/>
-    <col width="100" customWidth="1" min="12" max="12"/>
-    <col width="100" customWidth="1" min="13" max="13"/>
+    <col width="82" customWidth="1" min="10" max="10"/>
+    <col width="82" customWidth="1" min="11" max="11"/>
+    <col width="82" customWidth="1" min="12" max="12"/>
+    <col width="82" customWidth="1" min="13" max="13"/>
     <col width="34" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
-    <col width="100" customWidth="1" min="16" max="16"/>
-    <col width="100" customWidth="1" min="17" max="17"/>
-    <col width="100" customWidth="1" min="18" max="18"/>
-    <col width="100" customWidth="1" min="19" max="19"/>
-    <col width="100" customWidth="1" min="20" max="20"/>
+    <col width="82" customWidth="1" min="16" max="16"/>
+    <col width="82" customWidth="1" min="17" max="17"/>
+    <col width="82" customWidth="1" min="18" max="18"/>
+    <col width="82" customWidth="1" min="19" max="19"/>
+    <col width="82" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -555,7 +562,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Supports AHB 32-bit for the programming of CSR.</t>
+          <t>Independent control register for each GPIO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -565,7 +572,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Verifies default reset values and masked write/read behavior across GPIO per-pin control registers and group registers using successive patterns; flags mismatches and reports pass/fail.</t>
+          <t>Verify that per-GPIO control and group registers power-on default values match the specification and that masked write/read operations behave correctly across the defined GPIO register set.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -590,37 +597,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Reading DIN may become 1 if not driven; forcing zero at the pad can affect bit-level selector and cause mismatches when checking defaults.</t>
+          <t>Certain registers are intentionally skipped: VRRW-type and those marked non-readable/non-writable; default-read masks clear bit0; known caveat noted for DIN behavior affecting default reads.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Entry and setup:
-1) Entry point: test_case().
-2) Invoke the default-value check sequence, then the write/read check sequence. End with a final result based on failure counters.
-Default value check (in-order operations):
-3) For each index i from 0 to CNT-1, compute the per-address target from the test vector and proceed only if the default-skip flag for this index is 0.
-4) If the corresponding read mask is all-zero, skip this index; otherwise perform READ of the target register, then mask the read value per the test vector rule (LSB excluded), and compare to the expected default from the test vector.
-5) On mismatch, increment the default-failure counter.
-Write then read-back check for each data pattern:
-6) For each of the 6 data patterns, set the current write value.
-7) For each index i from 0 to CNT-1: if the write-skip flag is 1, continue; if the write-mask for this index is all-zero, continue; otherwise perform WRITE to the target register with (write_value AND the per-index write mask).
-8) For each index i from 0 to CNT-1 (read-back phase): if the write-skip flag is 1, continue; if the write mask is all-zero, continue; if the read mask is all-zero, continue; otherwise perform READ of the target register and mask with the per-index read mask. Compute the expected read value as the combination of the written bits (within the mask) and the preserved default bits (outside the mask) according to the per-index masks.
-9) If the read value does not match the expected value, increment the write/read-failure counter.
-Completion:
-10) If either failure counter is non-zero, report failure; otherwise report success.</t>
+          <t>["Entry point begins the test and first performs a default reset-value verification over the configured list of GPIO-related registers.", "Iterate through the configured register list; for any entry flagged to skip default checking, continue without accessing the register.", "For entries not skipped and marked as readable, read the register and apply a mask that clears bit 0, then compare the result to the documented default value for that register.", "Record a failure if any masked default-value comparison does not match the expected default.", "Proceed to masked write/read verification using a fixed sequence of six data patterns applied to the same configured register list.", "For each data pattern, iterate over the register list: if an entry is flagged to skip or has a zero write mask, do not write; otherwise, write the data pattern masked by the register’s write mask.", "After completing writes for the current pattern, iterate again over the register list: skip entries with zero write or zero read masks; for others, read the register value and mask it with the register’s read mask.", "For each read, compute the expected value as: (written_data AND read_mask AND write_mask) OR ((bitwise NOT of write_mask) AND read_mask AND the register’s default value).", "Compare the masked read value with the computed expected value and record a failure on any mismatch.", "Conclude the test and report pass if no default-value or write/read mismatches were recorded; otherwise report fail."]</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>GPIO_GP0_GPIO_8, GPIO_GP0_GPIO_9, GPIO_GP0_GPIO_10, GPIO_GP0_GPIO_11, GPIO_GP0_GPIO_12, GPIO_GP0_GPIO_13, GPIO_GP0_GPIO_14, GPIO_GP0_GPIO_15, GPIO_GP0_GPIO_16, GPIO_GP0_GPIO_17, GPIO_GP0_GPIO_18, GPIO_GP0_GPIO_19, GPIO_GP0_GPIO_20, GPIO_GP0_GPIO_21, GPIO_GP0_GPIO_22, GPIO_GP0_GPIO_23, GPIO_GP0_GPIO_24, GPIO_GP0_GPIO_25, GPIO_GP0_GPIO_26, GPIO_GP0_GPIO_27, GPIO_GP0_GPIO_28, GPIO_GP0_GPIO_29, GPIO_GP0_GPIO_30, GPIO_GP0_GPIO_31, GPIO_GP0_GPIO_32, GPIO_GP0_GPIO_33, GPIO_GP0_GPIO_34, GPIO_35, GPIO_36, GPIO_37, GPIO_38, GPIO_39, GPIO_INTR_RAW_STCLR1, INTR1_INTR_EN1, INTR1_INTR_STS1, INTR2_INTR_EN1, INTR2_INTR_STS1, GPIO_IO_CTRL_GROUP1, GPIO_IO_CTRL_GROUP2, GPIO_IO_CTRL_GROUP3, GPIO_IO_CTRL_GROUP4, GPIO_DOUT_GROUP1, GPIO_DOUT_GROUP2, GPIO_DOUT_GROUP3, GPIO_DOUT_GROUP4, GPIO_DIN_GROUP1, GPIO_DIN_GROUP2, GPIO_DIN_GROUP3, GPIO_DIN_GROUP4</t>
+          <t>MIZAR_GPIO_GP0_GPIO_8,MIZAR_GPIO_GP0_GPIO_9,MIZAR_GPIO_GP0_GPIO_10,MIZAR_GPIO_GP0_GPIO_11,MIZAR_GPIO_GP0_GPIO_12,MIZAR_GPIO_GP0_GPIO_13,MIZAR_GPIO_GP0_GPIO_14,MIZAR_GPIO_GP0_GPIO_15,MIZAR_GPIO_GP0_GPIO_16,MIZAR_GPIO_GP0_GPIO_17,MIZAR_GPIO_GP0_GPIO_18,MIZAR_GPIO_GP0_GPIO_19,MIZAR_GPIO_GP0_GPIO_20,MIZAR_GPIO_GP0_GPIO_21,MIZAR_GPIO_GP0_GPIO_22,MIZAR_GPIO_GP0_GPIO_23,MIZAR_GPIO_GP0_GPIO_24,MIZAR_GPIO_GP0_GPIO_25,MIZAR_GPIO_GP0_GPIO_26,MIZAR_GPIO_GP0_GPIO_27,MIZAR_GPIO_GP0_GPIO_28,MIZAR_GPIO_GP0_GPIO_29,MIZAR_GPIO_GP0_GPIO_30,MIZAR_GPIO_GP0_GPIO_31,MIZAR_GPIO_GP0_GPIO_32,MIZAR_GPIO_GP0_GPIO_33,MIZAR_GPIO_GP0_GPIO_34,MIZAR_GPIO_GP0_GPIO_35,MIZAR_GPIO_GP0_GPIO_36,MIZAR_GPIO_GP0_GPIO_37,MIZAR_GPIO_GP0_GPIO_38,MIZAR_GPIO_GP0_GPIO_39,MIZAR_GPIO_GPIO_INTR_RAW_STCLR1,MIZAR_GPIO_GP0_INTR1_INTR_EN1,MIZAR_GPIO_GP0_INTR1_INTR_STS1,MIZAR_GPIO_GP0_INTR2_INTR_EN1,MIZAR_GPIO_GP0_INTR2_INTR_STS1,MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,MIZAR_GPIO_GPIO_IO_CTRL_GROUP2,MIZAR_GPIO_GPIO_IO_CTRL_GROUP3,MIZAR_GPIO_GPIO_IO_CTRL_GROUP4,MIZAR_GPIO_GPIO_DOUT_GROUP1,MIZAR_GPIO_GPIO_DOUT_GROUP2,MIZAR_GPIO_GPIO_DOUT_GROUP3,MIZAR_GPIO_GPIO_DOUT_GROUP4,MIZAR_GPIO_GPIO_DIN_GROUP1,MIZAR_GPIO_GPIO_DIN_GROUP2,MIZAR_GPIO_GPIO_DIN_GROUP3,MIZAR_GPIO_GPIO_DIN_GROUP4</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Pass conditions:
-- For every readable index in the default-value phase, the read value (with the LSB masked as in the test) equals the expected default for that index.
-- For every index qualifying for write/read-back, the masked read value matches the expected value derived from the write value within the writable/readable mask while preserving default state outside the writable mask. Final result is pass when both default-failure and write/read-failure counters are zero.</t>
+          <t>["Default reset-value check passes only if, for every non-skipped readable register, (read_value AND 0xFFFFFFFE) equals the documented default value.", "Write/read check passes only if, for every non-skipped entry and for each test pattern, the masked read value equals: (written_data AND read_mask AND write_mask) OR ((bitwise NOT of write_mask) AND read_mask AND default_value).", "Overall test status is PASS when no default or write/read mismatches are recorded; otherwise FAIL."]</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -631,29 +623,27 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Checks default values and masked write/read on GPIO-related CSRs using arrays: addr_array[], default_value_array[], read_mask_array[], write_mask_array[], skip_array[], skip_rst_array[]. Runs chk_rst_val() then chk_rd_wr(). finish(0) on success else finish(1).</t>
+          <t>program.c invokes chk_rst_val() then chk_rd_wr(), and finishes with pass/fail based on def_fail_cnt and wr_fail_cnt. chk_rst_val() loops i=0..CNT-1 using addr=addr_array[i] (macros like MIZAR_GPIO_GP0_GPIO_8..GPIO_39, group regs, intr regs). It skips entries where skip_rst_array[i]==1 or read_mask_array[i]==0, reads via read_reg(addr), masks data_rd with 0xFFFFFFFE, and compares to default_value_array[i]. chk_rd_wr() tries six patterns (0xFFFFFFFF,0xAAAAAAAA,0x55555555,0xF5F5F5F5,0xA5A5A5A5,0xFFFF0000). For each i: if skip_array[i]==1 or write_mask_array[i]==0, it skips; else it write_reg(addr,(data_wr &amp; write_mask_array[i])). Then it reads back masked by read_mask_array[i], computes wr_n=(write_mask_array[i]^0xFFFFFFFF), and expected=((data_wr &amp; read_mask_array[i] &amp; write_mask_array[i]) | (wr_n &amp; read_mask_array[i] &amp; default_value_array[i])). Mismatch increments wr_fail_cnt. finish(1) if any failures, else finish(0).</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>when reading default values the din value is becoming 1 automatically if we don't force any value,but if we force zero to din bit level sel becoming high,so that reding value not matched with expected value</t>
+          <t>test_define.c: //80,94,98,9c,a0,a4,a8,ac,b0...SKIPPING VRRW registers. skip_array[] and skip_rst_array[] specify which registers to skip. Comment: when reading default values the din value is becoming 1 automatically if we don't force any value, but if we force zero to din bit level sel becoming high, so that reading value not matched with expected value.</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>test_case(): calls chk_rst_val(); then chk_rd_wr(); if(def_fail_cnt &gt; 0 || wr_fail_cnt &gt; 0) finish(1); else finish(0).
-chk_rst_val(): for i=0..CNT-1: addr=addr_array[i]; if(skip_rst_array[i]==1) continue; if(read_mask_array[i]==0x00000000) continue; data_rd=read_reg(addr); data=(data_rd &amp; 0xfffffffe); if(data==default_value_array[i]) pass else {def_fail_cnt++; print fail with addr and values}.
-chk_rd_wr(): patterns chk_val[6]={0xffffffff,0xaaaaaaaa,0x55555555,0xf5f5f5f5,0xA5A5A5A5,0xffff0000}; For each j pattern: data_wr=chk_val[j]; Write phase: i=0..CNT-1: addr=addr_array[i]; if(skip_array[i]==1) continue; if(write_mask_array[i]==0x00000000) continue; else write_reg(addr,(data_wr &amp; write_mask_array[i])). Read-back phase: i=0..CNT-1: addr=addr_array[i]; if(skip_array[i]==1) continue; if(write_mask_array[i]==0x00000000) continue; if(read_mask_array[i]==0x00000000) continue; else {data_rd=(read_reg(addr) &amp; read_mask_array[i]); wr_n=(write_mask_array[i] ^ 0xffffffff); exp_val=((data_wr &amp; read_mask_array[i] &amp; write_mask_array[i]) | (wr_n &amp; read_mask_array[i] &amp; default_value_array[i])); if(data_rd==exp_val) pass else {wr_fail_cnt++; print fail}}.</t>
+          <t>["int test_case(): calls chk_rst_val(); calls chk_rd_wr(); if (def_fail_cnt &gt; 0 || wr_fail_cnt &gt; 0) finish(1); else finish(0).", "void chk_rst_val(): for (i=0;i&lt;CNT;i++): addr=addr_array[i] (e.g., MIZAR_GPIO_GP0_GPIO_8..MIZAR_GPIO_GP0_GPIO_39, MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, MIZAR_GPIO_GP0_INTRx_xxx, GPIO_IO_CTRL_GROUPx, GPIO_DOUT_GROUPx, GPIO_DIN_GROUPx); if (skip_rst_array[i]==1) continue; if (read_mask_array[i]==0) continue; data_rd=read_reg(addr); data=(data_rd &amp; 0xFFFFFFFE); if (data==default_value_array[i]) pass; else { def_fail_cnt++; printf failure }. No waits/timeouts.", "void chk_rd_wr(): unsigned chk_val[6]={0xFFFFFFFF,0xAAAAAAAA,0x55555555,0xF5F5F5F5,0xA5A5A5A5,0xFFFF0000}; For each pattern j: data_wr=chk_val[j]; Write phase: for (i=0;i&lt;CNT;i++): addr=addr_array[i]; if (skip_array[i]==1) continue; if (write_mask_array[i]==0) continue; else write_reg(addr,(data_wr &amp; write_mask_array[i])). Read/verify phase: for (i=0;i&lt;CNT;i++): addr=addr_array[i]; if (skip_array[i]==1) continue; if (write_mask_array[i]==0) continue; if (read_mask_array[i]==0) continue; data_rd=(read_reg(addr) &amp; read_mask_array[i]); wr_n=(write_mask_array[i] ^ 0xFFFFFFFF); exp_val=((data_wr &amp; read_mask_array[i] &amp; write_mask_array[i]) | (wr_n &amp; read_mask_array[i] &amp; default_value_array[i])); if (data_rd==exp_val) pass; else { wr_fail_cnt++; printf failure }."]</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>MIZAR_GPIO_GP0_GPIO_8, MIZAR_GPIO_GP0_GPIO_9, MIZAR_GPIO_GP0_GPIO_10, MIZAR_GPIO_GP0_GPIO_11, MIZAR_GPIO_GP0_GPIO_12, MIZAR_GPIO_GP0_GPIO_13, MIZAR_GPIO_GP0_GPIO_14, MIZAR_GPIO_GP0_GPIO_15, MIZAR_GPIO_GP0_GPIO_16, MIZAR_GPIO_GP0_GPIO_17, MIZAR_GPIO_GP0_GPIO_18, MIZAR_GPIO_GP0_GPIO_19, MIZAR_GPIO_GP0_GPIO_20, MIZAR_GPIO_GP0_GPIO_21, MIZAR_GPIO_GP0_GPIO_22, MIZAR_GPIO_GP0_GPIO_23, MIZAR_GPIO_GP0_GPIO_24, MIZAR_GPIO_GP0_GPIO_25, MIZAR_GPIO_GP0_GPIO_26, MIZAR_GPIO_GP0_GPIO_27, MIZAR_GPIO_GP0_GPIO_28, MIZAR_GPIO_GP0_GPIO_29, MIZAR_GPIO_GP0_GPIO_30, MIZAR_GPIO_GP0_GPIO_31, MIZAR_GPIO_GP0_GPIO_32, MIZAR_GPIO_GP0_GPIO_33, MIZAR_GPIO_GP0_GPIO_34, MIZAR_GPIO_GP0_GPIO_35, MIZAR_GPIO_GP0_GPIO_36, MIZAR_GPIO_GP0_GPIO_37, MIZAR_GPIO_GP0_GPIO_38, MIZAR_GPIO_GP0_GPIO_39, MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, MIZAR_GPIO_GP0_INTR1_INTR_EN1, MIZAR_GPIO_GP0_INTR1_INTR_STS1, MIZAR_GPIO_GP0_INTR2_INTR_EN1, MIZAR_GPIO_GP0_INTR2_INTR_STS1, MIZAR_GPIO_GPIO_IO_CTRL_GROUP1, MIZAR_GPIO_GPIO_IO_CTRL_GROUP2, MIZAR_GPIO_GPIO_IO_CTRL_GROUP3, MIZAR_GPIO_GPIO_IO_CTRL_GROUP4, MIZAR_GPIO_GPIO_DOUT_GROUP1, MIZAR_GPIO_GPIO_DOUT_GROUP2, MIZAR_GPIO_GPIO_DOUT_GROUP3, MIZAR_GPIO_GPIO_DOUT_GROUP4, MIZAR_GPIO_GPIO_DIN_GROUP1, MIZAR_GPIO_GPIO_DIN_GROUP2, MIZAR_GPIO_GPIO_DIN_GROUP3, MIZAR_GPIO_GPIO_DIN_GROUP4</t>
+          <t>MIZAR_GPIO_GP0_GPIO_8,MIZAR_GPIO_GP0_GPIO_9,MIZAR_GPIO_GP0_GPIO_10,MIZAR_GPIO_GP0_GPIO_11,MIZAR_GPIO_GP0_GPIO_12,MIZAR_GPIO_GP0_GPIO_13,MIZAR_GPIO_GP0_GPIO_14,MIZAR_GPIO_GP0_GPIO_15,MIZAR_GPIO_GP0_GPIO_16,MIZAR_GPIO_GP0_GPIO_17,MIZAR_GPIO_GP0_GPIO_18,MIZAR_GPIO_GP0_GPIO_19,MIZAR_GPIO_GP0_GPIO_20,MIZAR_GPIO_GP0_GPIO_21,MIZAR_GPIO_GP0_GPIO_22,MIZAR_GPIO_GP0_GPIO_23,MIZAR_GPIO_GP0_GPIO_24,MIZAR_GPIO_GP0_GPIO_25,MIZAR_GPIO_GP0_GPIO_26,MIZAR_GPIO_GP0_GPIO_27,MIZAR_GPIO_GP0_GPIO_28,MIZAR_GPIO_GP0_GPIO_29,MIZAR_GPIO_GP0_GPIO_30,MIZAR_GPIO_GP0_GPIO_31,MIZAR_GPIO_GP0_GPIO_32,MIZAR_GPIO_GP0_GPIO_33,MIZAR_GPIO_GP0_GPIO_34,MIZAR_GPIO_GP0_GPIO_35,MIZAR_GPIO_GP0_GPIO_36,MIZAR_GPIO_GP0_GPIO_37,MIZAR_GPIO_GP0_GPIO_38,MIZAR_GPIO_GP0_GPIO_39,MIZAR_GPIO_GPIO_INTR_RAW_STCLR1,MIZAR_GPIO_GP0_INTR1_INTR_EN1,MIZAR_GPIO_GP0_INTR1_INTR_STS1,MIZAR_GPIO_GP0_INTR2_INTR_EN1,MIZAR_GPIO_GP0_INTR2_INTR_STS1,MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,MIZAR_GPIO_GPIO_IO_CTRL_GROUP2,MIZAR_GPIO_GPIO_IO_CTRL_GROUP3,MIZAR_GPIO_GPIO_IO_CTRL_GROUP4,MIZAR_GPIO_GPIO_DOUT_GROUP1,MIZAR_GPIO_GPIO_DOUT_GROUP2,MIZAR_GPIO_GPIO_DOUT_GROUP3,MIZAR_GPIO_GPIO_DOUT_GROUP4,MIZAR_GPIO_GPIO_DIN_GROUP1,MIZAR_GPIO_GPIO_DIN_GROUP2,MIZAR_GPIO_GPIO_DIN_GROUP3,MIZAR_GPIO_GPIO_DIN_GROUP4</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Default check: data = (read_reg(addr) &amp; 0xfffffffe) must equal default_value_array[i]; Write/Read check: data_rd = (read_reg(addr) &amp; read_mask_array[i]) must equal exp_val = ((data_wr &amp; read_mask_array[i] &amp; write_mask_array[i]) | ((~write_mask_array[i]) &amp; read_mask_array[i] &amp; default_value_array[i])). finish(0) only if def_fail_cnt==0 and wr_fail_cnt==0.</t>
+          <t>Default pass criterion: for all i where skip_rst_array[i]==0 and read_mask_array[i]!=0, (read_reg(addr_array[i]) &amp; 0xFFFFFFFE) == default_value_array[i]. Write/read pass criterion: for all i where skip_array[i]==0, write_mask_array[i]!=0, read_mask_array[i]!=0, and for each j in 0..5, (read_reg(addr_array[i]) &amp; read_mask_array[i]) == ((chk_val[j] &amp; read_mask_array[i] &amp; write_mask_array[i]) | ((write_mask_array[i]^0xFFFFFFFF) &amp; read_mask_array[i] &amp; default_value_array[i])). Overall finish(0) indicates PASS.</t>
         </is>
       </c>
     </row>
@@ -668,7 +658,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bits: 18 Name: neie Description: Negative edge interrupt enable; 1 - Enable interrupt when falling edge (neg edge) is detected on gpio pin; 0 - Disable interrupt on neg-edge detection;</t>
+          <t>Interrupts can be generated based on positive edge or negative edge or level high or level low detection at GPIO input</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -678,7 +668,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Configures negative-edge interrupts for GPIOs 8–39, generates a falling edge per pin using a pad driver, then validates per-pin raw status, group status, input level after the edge, and proper clearing of both GPIO and system interrupt status.</t>
+          <t>Validate that each GPIO input (pads 8–39) can generate a falling-edge interrupt, that per-pin and group status latch correctly, and that both per-pin and group status can be cleared while the system interrupt path propagates and is serviced.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -703,46 +693,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Arms the wait condition before generating the edge to avoid race; uses a bounded wait with timeout for robustness; initializes the pad driver to a known state (all high) before each edge.</t>
+          <t>Interrupt wait uses a bounded polling loop with timeout; edge generation is ordered to arm the wait before toggling to avoid race; pad driver is returned to a known all-high state inside the handler before status checks.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Entry and interrupt enable:
-1) Entry point: test_case(). Initialize the test error counter to zero.
-2) Enable the platform interrupt line in the interrupt controller for the selected GPIO instance.
-3) Enable the system-level interrupt output by writing to INTR_EN1 with the appropriate GPIO interrupt enable field.
-Pad driver initialization:
-4) Drive the external pad interface at 0xA0243ffc to all ones to set a known initial level (high) on all pins.
-Configure per-pin control and clear raw status:
-5) For each pin index from 0 to 31, compute the per-pin control register (GPIO_GP0_GPIO_8 + index*4) and WRITE to enable input mode and negative-edge interrupt detection, and clear any existing raw status. Include a short wait after each write.
-Per-pin test loop to generate a falling edge and wait for ISR:
-6) For each bit position i from 0 to 31, compute a one-hot mask for that bit.
-7) Pre-clear any latched raw group bit by WRITING the one-hot mask to GPIO_INTR_RAW_STCLR1.
-8) Enable only this pin’s group interrupt by WRITING the one-hot mask to INTR1_INTR_EN1. Wait briefly.
-9) Arm the ISR wait by setting the shared pending flag and then generate a falling edge on the target pin by first driving 0xFFFFFFFF to 0xA0243ffc, then driving the bitwise complement of the one-hot mask to 0xA0243ffc so that the selected pin transitions 1→0.
-10) Poll on the pending flag with a bounded loop (timeout 5000 iterations with a short wait per iteration); if the timeout expires, log an error and continue.
-ISR behavior (Default_IRQHandler) upon interrupt:
-11) Clear the pending flag and drive the pad back to all ones at 0xA0243ffc.
-12) READ the per-pin control/status register for the active index and verify the input level field indicates 0 after the falling edge.
-13) Verify the per-pin raw status indicates an interrupt event; READ the group status from INTR1_INTR_STS1 and confirm the bit for the active pin is set.
-14) Clear the per-pin raw status by WRITING the clear field in the per-pin control register and also clear the group raw by WRITING the one-hot mask to GPIO_INTR_RAW_STCLR1. Then READ INTR1_INTR_STS1 and confirm it is 0.
-15) Clear the system-level raw status for the selected GPIO instance by WRITING the corresponding bit in RAW_STCR1 and service/clear the interrupt controller line for the instance.
-Completion:
-16) After testing all pins, report pass if the test error counter is zero; otherwise report failure.</t>
+          <t>["Entry point initializes error counters and enables the appropriate CPU interrupt in the interrupt controller for the selected GPIO instance.", "Enable the system register output for the selected GPIO instance to route the group interrupt to the CPU.", "Drive the external pad driver register to all ones to establish a known-high state on all GPIO inputs.", "Configure each per-GPIO control register for pads 8 through 39 to input mode, enable negative-edge detection, and clear any pending per-pin raw status; insert a short wait after each configuration write.", "For each GPIO bit from 0 to 31 (corresponding to pads 8–39): pre-clear the corresponding group raw status bit, enable only that bit in the group interrupt-enable register, and wait briefly.", "Arm the interrupt-wait flag, then generate a falling edge on the selected pad by first driving all-high and then clearing only the target bit in the pad driver register.", "Poll the arm flag with a bounded timeout (initial count 5000) and periodic short waits until the interrupt handler indicates service completion or the timeout expires; on timeout, record an error.", "Interrupt handler actions upon entry: clear the wait flag and immediately return the pad driver to the all-high state.", "Read the per-GPIO control/status register for the active pad and confirm that the input data bit indicates low following the falling edge.", "Confirm that the per-pin raw interrupt indication is set, then read the group interrupt status register and verify that the corresponding bit is asserted.", "Clear the per-pin raw status by writing the clear bit while preserving input mode, and clear the group raw status by writing one to the corresponding group clear register.", "Verify that the group status register reads zero after clears, clear the system-level raw interrupt status for the selected instance, and clear the pending interrupt in the interrupt controller."]</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>GPIO_GP0_GPIO_8, GPIO_GP0_GPIO_9, GPIO_GP0_GPIO_10, GPIO_GP0_GPIO_11, GPIO_GP0_GPIO_12, GPIO_GP0_GPIO_13, GPIO_GP0_GPIO_14, GPIO_GP0_GPIO_15, GPIO_GP0_GPIO_16, GPIO_GP0_GPIO_17, GPIO_GP0_GPIO_18, GPIO_GP0_GPIO_19, GPIO_GP0_GPIO_20, GPIO_GP0_GPIO_21, GPIO_GP0_GPIO_22, GPIO_GP0_GPIO_23, GPIO_GP0_GPIO_24, GPIO_GP0_GPIO_25, GPIO_GP0_GPIO_26, GPIO_GP0_GPIO_27, GPIO_GP0_GPIO_28, GPIO_GP0_GPIO_29, GPIO_GP0_GPIO_30, GPIO_GP0_GPIO_31, GPIO_GP0_GPIO_32, GPIO_GP0_GPIO_33, GPIO_GP0_GPIO_34, GPIO_35, GPIO_36, GPIO_37, GPIO_38, GPIO_39, GPIO_INTR_RAW_STCLR1, INTR1_INTR_EN1, INTR1_INTR_STS1, INTR_EN1, RAW_STCR1</t>
+          <t>MIZAR_LSS_SYSREG_INTR_EN1,MIZAR_LSS_SYSREG_RAW_STCR1,MIZAR_GPIO_GP0_GPIO_8,MIZAR_GPIO_GP0_GPIO_9,MIZAR_GPIO_GP0_GPIO_10,MIZAR_GPIO_GP0_GPIO_11,MIZAR_GPIO_GP0_GPIO_12,MIZAR_GPIO_GP0_GPIO_13,MIZAR_GPIO_GP0_GPIO_14,MIZAR_GPIO_GP0_GPIO_15,MIZAR_GPIO_GP0_GPIO_16,MIZAR_GPIO_GP0_GPIO_17,MIZAR_GPIO_GP0_GPIO_18,MIZAR_GPIO_GP0_GPIO_19,MIZAR_GPIO_GP0_GPIO_20,MIZAR_GPIO_GP0_GPIO_21,MIZAR_GPIO_GP0_GPIO_22,MIZAR_GPIO_GP0_GPIO_23,MIZAR_GPIO_GP0_GPIO_24,MIZAR_GPIO_GP0_GPIO_25,MIZAR_GPIO_GP0_GPIO_26,MIZAR_GPIO_GP0_GPIO_27,MIZAR_GPIO_GP0_GPIO_28,MIZAR_GPIO_GP0_GPIO_29,MIZAR_GPIO_GP0_GPIO_30,MIZAR_GPIO_GP0_GPIO_31,MIZAR_GPIO_GP0_GPIO_32,MIZAR_GPIO_GP0_GPIO_33,MIZAR_GPIO_GP0_GPIO_34,MIZAR_GPIO_GP0_GPIO_35,MIZAR_GPIO_GP0_GPIO_36,MIZAR_GPIO_GP0_GPIO_37,MIZAR_GPIO_GP0_GPIO_38,MIZAR_GPIO_GP0_GPIO_39,MIZAR_GPIO_GP0_INTR1_INTR_EN1,MIZAR_GPIO_GP0_INTR1_INTR_STS1,MIZAR_GPIO_GPIO_INTR_RAW_STCLR1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Pass conditions per pin:
-- The input level in the per-pin status indicates 0 immediately after the falling edge is handled.
-- The per-pin raw interrupt indicator reflects an event, and the group status shows the corresponding bit set.
-- After issuing the clears, the group status reads 0 and the system-level raw status is cleared. Overall pass when the final error counter is zero.</t>
+          <t>["For each pad tested, the per-pin input data reflects low after the induced falling edge.", "Per-pin raw interrupt indication is set for the active pad and the corresponding group status bit is asserted.", "After issuing per-pin and group clears, the group status register reads zero.", "System-level raw interrupt status for the selected instance is cleared after service, and the interrupt controller is cleared.", "Overall test passes only if no timeouts occur and no verification steps report errors."]</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -753,31 +719,27 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Negative-edge interrupt enable/verify for GPIO[8..39]. Sets doe=1, neie=1, iclr=1 per pin; uses 0xA0243ffc to toggle pads high then to ~wr_val to create 1-&gt;0 edges. Enables MIZAR_LSS_SYSREG_INTR_EN1 with LSS_SYSREG_INTR_EN1_GPIO0_INTR or GPIO1, sets MIZAR_GPIO_GP0_INTR1_INTR_EN1 per bit, waits on int_pend with timeout, ISR checks (rdata &amp; 0x1)==0, (rdata &amp; 0x2)!=0, MIZAR_GPIO_GP0_INTR1_INTR_STS1 has bit set, clears via per-pin iclr and MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, verifies group==0, clears MIZAR_LSS_SYSREG_RAW_STCR1 and GIC line.</t>
+          <t>program.c sets up negedge interrupts. In test_case(): optionally GIC_EnableIRQ(87/88); write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR or LSS_SYSREG_INTR_EN1_GPIO1_INTR); write_reg(0xA0243ffc, 0xffffffff); for i=0..31: addr1 = MIZAR_GPIO_GP0_GPIO_8 + (i*4); write_reg(addr1, (1&lt;&lt;20)|(1&lt;&lt;18)|(1&lt;&lt;16)); wait_on(10). For each i: wr_val=1&lt;&lt;i; write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, wr_val); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, wr_val); wait_on(10); int_pend=1; write_reg(0xA0243ffc, 0xffffffff); wait_on(30); write_reg(0xA0243ffc, ~wr_val); timeout=5000; while (int_pend &amp;&amp; timeout--) wait_on(10); if timeout==0 error++. finish(test_err). Default_IRQHandler(): local_wr=1&lt;&lt;i; int_pend=0; write_reg(0xA0243ffc, 0xffffffff); raddr=MIZAR_GPIO_GP0_GPIO_8 + (i*4); rdata=read_reg(raddr); if ((rdata &amp; 0x1)!=0) error++; if ((rdata &amp; 0x2)!=0x0) { rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if ((rdata_grp &amp; local_wr)==0) error++; write_reg(MIZAR_GPIO_GP0_GPIO_8 + (i*4), (1&lt;&lt;20)|(1&lt;&lt;16)); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, local_wr); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if (rdata_grp!=0x0) error++; write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR/1_INTR); GIC_ClearIRQ(87/88); } else error++;</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Arms wait before generating edge; bounded wait with timeout=5000; drives 0xA0243ffc to known states around each edge generation.</t>
+          <t>Wait-before-edge arming to avoid race: comment indicates arming int_pend before generating the edge. Uses bounded wait: timeout=5000 with wait_on(10) per loop. Pad driver (0xA0243ffc) set to known state inside ISR.</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>test_case(): test_err=0; GIC_EnableIRQ(87/88) ifdef; write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR or GPIO1); write_reg(0xA0243ffc, 0xffffffff);
-for i=0..31: addr1=MIZAR_GPIO_GP0_GPIO_8 + (i*4); write_reg(addr1, (1u&lt;&lt;20)|(1u&lt;&lt;18)|(1u&lt;&lt;16)); wait_on(10);
-for i=0..31: wr_val=1u&lt;&lt;i; write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, wr_val); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, wr_val); wait_on(10); int_pend=1; write_reg(0xA0243ffc, 0xffffffff); wait_on(30); write_reg(0xA0243ffc, ~wr_val); timeout=5000; while(int_pend &amp;&amp; timeout--) wait_on(10); if(timeout==0){printf timeout; test_err++;}
-finish(test_err);
-Default_IRQHandler(): local_wr=1u&lt;&lt;i; int_pend=0; write_reg(0xA0243ffc, 0xffffffff); raddr=MIZAR_GPIO_GP0_GPIO_8 + (i*4); rdata=read_reg(raddr); if((rdata &amp; 0x1)!=0) test_err++; if((rdata &amp; 0x2)!=0x0){ rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if((rdata_grp &amp; local_wr)==0) test_err++; raddr2=MIZAR_GPIO_GP0_GPIO_8 + (i*4); write_reg(raddr2,(1u&lt;&lt;20)|(1u&lt;&lt;16)); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, local_wr); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if(rdata_grp!=0x0) test_err++; write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR or GPIO1); GIC_ClearIRQ(87/88);} else { test_err++; }</t>
+          <t>["int test_case(): test_err=0; #ifdef GPIO0 GIC_EnableIRQ(87) #endif; #ifdef GPIO1 GIC_EnableIRQ(88) #endif;", "#ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR) #endif; #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO1_INTR) #endif;", "write_reg(0xA0243ffc, 0xFFFFFFFF);", "for (i=0;i&lt;32;i++): addr1=MIZAR_GPIO_GP0_GPIO_8 + (i*4); write_reg(addr1, (1&lt;&lt;20)|(1&lt;&lt;18)|(1&lt;&lt;16)); wait_on(10);", "for (i=0;i&lt;32;i++): wr_val=1&lt;&lt;i; write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, wr_val); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, wr_val); wait_on(10); int_pend=1; write_reg(0xA0243ffc, 0xFFFFFFFF); wait_on(30); write_reg(0xA0243ffc, ~wr_val);", "unsigned int timeout=5000; while (int_pend &amp;&amp; timeout--) wait_on(10); if (timeout==0) { printf timeout; test_err++; }", "finish(test_err);", "void Default_IRQHandler(): unsigned int local_wr=1&lt;&lt;i; int_pend=0; write_reg(0xA0243ffc, 0xFFFFFFFF); raddr=MIZAR_GPIO_GP0_GPIO_8 + (i*4); rdata=read_reg(raddr);", "if ((rdata &amp; 0x1)!=0) test_err++;", "if ((rdata &amp; 0x2)!=0x0) { rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if ((rdata_grp &amp; local_wr)==0) test_err++; write_reg(MIZAR_GPIO_GP0_GPIO_8 + (i*4), (1&lt;&lt;20)|(1&lt;&lt;16)); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, local_wr); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if (rdata_grp!=0x0) test_err++; #ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); GIC_ClearIRQ(87); #endif #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO1_INTR); GIC_ClearIRQ(88); #endif } else { test_err++; }"]</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>MIZAR_GPIO_GP0_GPIO_8, MIZAR_GPIO_GP0_GPIO_9, MIZAR_GPIO_GP0_GPIO_10, MIZAR_GPIO_GP0_GPIO_11, MIZAR_GPIO_GP0_GPIO_12, MIZAR_GPIO_GP0_GPIO_13, MIZAR_GPIO_GP0_GPIO_14, MIZAR_GPIO_GP0_GPIO_15, MIZAR_GPIO_GP0_GPIO_16, MIZAR_GPIO_GP0_GPIO_17, MIZAR_GPIO_GP0_GPIO_18, MIZAR_GPIO_GP0_GPIO_19, MIZAR_GPIO_GP0_GPIO_20, MIZAR_GPIO_GP0_GPIO_21, MIZAR_GPIO_GP0_GPIO_22, MIZAR_GPIO_GP0_GPIO_23, MIZAR_GPIO_GP0_GPIO_24, MIZAR_GPIO_GP0_GPIO_25, MIZAR_GPIO_GP0_GPIO_26, MIZAR_GPIO_GP0_GPIO_27, MIZAR_GPIO_GP0_GPIO_28, MIZAR_GPIO_GP0_GPIO_29, MIZAR_GPIO_GP0_GPIO_30, MIZAR_GPIO_GP0_GPIO_31, MIZAR_GPIO_GP0_GPIO_32, MIZAR_GPIO_GP0_GPIO_33, MIZAR_GPIO_GP0_GPIO_34, MIZAR_GPIO_GP0_GPIO_35, MIZAR_GPIO_GP0_GPIO_36, MIZAR_GPIO_GP0_GPIO_37, MIZAR_GPIO_GP0_GPIO_38, MIZAR_GPIO_GP0_GPIO_39, MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, MIZAR_GPIO_GP0_INTR1_INTR_EN1, MIZAR_GPIO_GP0_INTR1_INTR_STS1, MIZAR_LSS_SYSREG_INTR_EN1, MIZAR_LSS_SYSREG_RAW_STCR1</t>
+          <t>MIZAR_LSS_SYSREG_INTR_EN1,MIZAR_LSS_SYSREG_RAW_STCR1,MIZAR_GPIO_GP0_GPIO_8,MIZAR_GPIO_GP0_GPIO_9,MIZAR_GPIO_GP0_GPIO_10,MIZAR_GPIO_GP0_GPIO_11,MIZAR_GPIO_GP0_GPIO_12,MIZAR_GPIO_GP0_GPIO_13,MIZAR_GPIO_GP0_GPIO_14,MIZAR_GPIO_GP0_GPIO_15,MIZAR_GPIO_GP0_GPIO_16,MIZAR_GPIO_GP0_GPIO_17,MIZAR_GPIO_GP0_GPIO_18,MIZAR_GPIO_GP0_GPIO_19,MIZAR_GPIO_GP0_GPIO_20,MIZAR_GPIO_GP0_GPIO_21,MIZAR_GPIO_GP0_GPIO_22,MIZAR_GPIO_GP0_GPIO_23,MIZAR_GPIO_GP0_GPIO_24,MIZAR_GPIO_GP0_GPIO_25,MIZAR_GPIO_GP0_GPIO_26,MIZAR_GPIO_GP0_GPIO_27,MIZAR_GPIO_GP0_GPIO_28,MIZAR_GPIO_GP0_GPIO_29,MIZAR_GPIO_GP0_GPIO_30,MIZAR_GPIO_GP0_GPIO_31,MIZAR_GPIO_GP0_GPIO_32,MIZAR_GPIO_GP0_GPIO_33,MIZAR_GPIO_GP0_GPIO_34,MIZAR_GPIO_GP0_GPIO_35,MIZAR_GPIO_GP0_GPIO_36,MIZAR_GPIO_GP0_GPIO_37,MIZAR_GPIO_GP0_GPIO_38,MIZAR_GPIO_GP0_GPIO_39,MIZAR_GPIO_GP0_INTR1_INTR_EN1,MIZAR_GPIO_GP0_INTR1_INTR_STS1,MIZAR_GPIO_GPIO_INTR_RAW_STCLR1</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Per-pin: In ISR, (rdata &amp; 0x1)==0 (DIN=0) and (rdata &amp; 0x2)!=0 (raw set). MIZAR_GPIO_GP0_INTR1_INTR_STS1 has (1u&lt;&lt;i) set; after write of iclr and MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, read of MIZAR_GPIO_GP0_INTR1_INTR_STS1 must be 0. MIZAR_LSS_SYSREG_RAW_STCR1 must be cleared after write. finish(test_err) with test_err==0 indicates PASS; any timeout or check failure increments test_err.</t>
+          <t>Pass per pin when: after falling edge, (read_reg(MIZAR_GPIO_GP0_GPIO_8 + i*4) &amp; 0x1) == 0; (read_reg(MIZAR_GPIO_GP0_GPIO_8 + i*4) &amp; 0x2) != 0; (read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1) &amp; (1&lt;&lt;i)) != 0; after write_reg(MIZAR_GPIO_GP0_GPIO_8 + i*4, (1&lt;&lt;20)|(1&lt;&lt;16)) and write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, 1&lt;&lt;i), then read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1) == 0. System status cleared via MIZAR_LSS_SYSREG_RAW_STCR1 and GIC cleared. No timeout in while(int_pend &amp;&amp; timeout--) loop.</t>
         </is>
       </c>
     </row>
@@ -792,7 +754,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bits: 17 Name: peie Description: Positive edge interrupt enable; 1 - Enable interrupt when rising edge (pos edge) is detected on gpio pin; 0 - Disable interrupt on pos-edge detection;</t>
+          <t>Interrupts can be generated based on positive edge or negative edge or level high or level low detection at GPIO input</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -802,7 +764,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Enables positive-edge interrupts for GPIOs 8–39, configures pins to input mode, raises a single rising edge per pin using a pad driver, and validates interrupt group status, per-pin raw clear, and system interrupt status clear for each iteration.</t>
+          <t>Validate that enabling positive-edge detection on all GPIO inputs (pads 8–39) produces an interrupt per rising transition, that group status asserts and can be cleared for all pads, and that the system interrupt path is properly cleared and re-enabled between events.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -827,46 +789,22 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Arms the wait condition prior to generating each rising edge; uses a bounded wait to avoid infinite loops; masks the group during service and re-enables it afterward.</t>
+          <t>Group interrupt is masked during service and re-enabled afterward; the wait loop for the handler is bounded by a timeout; input mode for pads is configured via group I/O control registers to ensure edge detection.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Entry and interrupt enable:
-1) Entry point: test_case(). Reset the test error counter to zero.
-2) Enable the interrupt controller line for the selected GPIO instance.
-3) Enable system-level interrupt output for the selected GPIO instance by WRITING to INTR_EN1 with the instance-specific enable field.
-Per-pin positive-edge configuration:
-4) For each pin index from 0 to 31, WRITE the per-pin control register (GPIO_GP0_GPIO_8 + index*4) with the positive-edge interrupt enable field set.
-Set IO mode via group control:
-5) WRITE GPIO_IO_CTRL_GROUP1 through GPIO_IO_CTRL_GROUP4 to configure pins 8–39 as inputs.
-Enable group interrupt output:
-6) WRITE INTR1_INTR_EN1 with all bits set to enable all per-pin interrupts at the group level.
-Per-pin test loop to generate a rising edge and wait for ISR:
-7) For each index i from 0 to 31: drive the pad interface at 0xA0243ffc to all zeros; wait briefly; arm the pending flag; then WRITE 0xFFFFFFFF to 0xA0243ffc to generate a single rising edge on the selected pin.
-8) Poll the pending flag with a bounded loop (timeout 2000 iterations, brief wait per iteration). On timeout, count an error and break the loop; otherwise, drive the pad back low and wait briefly for the next iteration.
-ISR behavior (Default_IRQHandler) upon interrupt:
-9) Clear the pending flag; READ the group status from INTR1_INTR_STS1 and temporarily mask group enables by WRITING zero to INTR1_INTR_EN1.
-10) If the group status is zero, record an error; otherwise continue.
-11) Clear per-pin raw status for all pins by WRITING the clear field in each per-pin control register (GPIO_GP0_GPIO_8 + j*4 for j=0..31) and wait briefly.
-12) READ INTR1_INTR_STS1 and confirm it is zero (group status cleared).
-13) Clear the system-level raw status by WRITING the instance-specific bit to RAW_STCR1; then READ RAW_STCR1 and confirm the bit is cleared.
-14) Re-enable group interrupt output by WRITING all ones to INTR1_INTR_EN1 and clear the interrupt controller line for the selected instance.
-Completion:
-15) Report pass if the final test error counter remains zero; otherwise report failure.</t>
+          <t>["Entry point enables the appropriate CPU interrupt for the selected GPIO instance in the interrupt controller.", "Enable the system register output for the selected GPIO instance to route the group interrupt.", "Configure per-GPIO control registers for pads 8 through 39 to enable positive-edge interrupt detection.", "Set pads 8–39 to input mode using the four group I/O control registers.", "Enable all bits in the group interrupt-enable register.", "For each pad index from 0 to 31: drive the external pad driver low, wait briefly, arm the wait flag, then drive the external pad driver high to generate a single rising edge.", "Poll the wait flag with a bounded timeout (initial count 2000) and periodic short waits to confirm the interrupt was serviced; on timeout, record an error and exit the loop.", "After each iteration, optionally return the pad driver low and wait briefly to prepare for the next edge.", "Interrupt handler actions: clear the wait flag; read the group interrupt status; mask the group enable during service; check that at least one group bit is asserted; clear per-pin raw status across all pads by writing the per-GPIO clear bit in each control register and wait briefly.", "Verify that the group status is zero following the clears; clear the system-level raw status for the selected instance; re-enable the group interrupt and clear the pending interrupt in the interrupt controller."]</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>GPIO_GP0_GPIO_8, GPIO_GP0_GPIO_9, GPIO_GP0_GPIO_10, GPIO_GP0_GPIO_11, GPIO_GP0_GPIO_12, GPIO_GP0_GPIO_13, GPIO_GP0_GPIO_14, GPIO_GP0_GPIO_15, GPIO_GP0_GPIO_16, GPIO_GP0_GPIO_17, GPIO_GP0_GPIO_18, GPIO_GP0_GPIO_19, GPIO_GP0_GPIO_20, GPIO_GP0_GPIO_21, GPIO_GP0_GPIO_22, GPIO_GP0_GPIO_23, GPIO_GP0_GPIO_24, GPIO_GP0_GPIO_25, GPIO_GP0_GPIO_26, GPIO_GP0_GPIO_27, GPIO_GP0_GPIO_28, GPIO_GP0_GPIO_29, GPIO_GP0_GPIO_30, GPIO_GP0_GPIO_31, GPIO_GP0_GPIO_32, GPIO_GP0_GPIO_33, GPIO_GP0_GPIO_34, GPIO_35, GPIO_36, GPIO_37, GPIO_38, GPIO_39, INTR1_INTR_EN1, INTR1_INTR_STS1, GPIO_IO_CTRL_GROUP1, GPIO_IO_CTRL_GROUP2, GPIO_IO_CTRL_GROUP3, GPIO_IO_CTRL_GROUP4, INTR_EN1, RAW_STCR1</t>
+          <t>MIZAR_LSS_SYSREG_INTR_EN1,MIZAR_LSS_SYSREG_RAW_STCR1,MIZAR_GPIO_GP0_GPIO_8,MIZAR_GPIO_GP0_GPIO_9,MIZAR_GPIO_GP0_GPIO_10,MIZAR_GPIO_GP0_GPIO_11,MIZAR_GPIO_GP0_GPIO_12,MIZAR_GPIO_GP0_GPIO_13,MIZAR_GPIO_GP0_GPIO_14,MIZAR_GPIO_GP0_GPIO_15,MIZAR_GPIO_GP0_GPIO_16,MIZAR_GPIO_GP0_GPIO_17,MIZAR_GPIO_GP0_GPIO_18,MIZAR_GPIO_GP0_GPIO_19,MIZAR_GPIO_GP0_GPIO_20,MIZAR_GPIO_GP0_GPIO_21,MIZAR_GPIO_GP0_GPIO_22,MIZAR_GPIO_GP0_GPIO_23,MIZAR_GPIO_GP0_GPIO_24,MIZAR_GPIO_GP0_GPIO_25,MIZAR_GPIO_GP0_GPIO_26,MIZAR_GPIO_GP0_GPIO_27,MIZAR_GPIO_GP0_GPIO_28,MIZAR_GPIO_GP0_GPIO_29,MIZAR_GPIO_GP0_GPIO_30,MIZAR_GPIO_GP0_GPIO_31,MIZAR_GPIO_GP0_GPIO_32,MIZAR_GPIO_GP0_GPIO_33,MIZAR_GPIO_GP0_GPIO_34,MIZAR_GPIO_GP0_GPIO_35,MIZAR_GPIO_GP0_GPIO_36,MIZAR_GPIO_GP0_GPIO_37,MIZAR_GPIO_GP0_GPIO_38,MIZAR_GPIO_GP0_GPIO_39,MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,MIZAR_GPIO_GPIO_IO_CTRL_GROUP2,MIZAR_GPIO_GPIO_IO_CTRL_GROUP3,MIZAR_GPIO_GPIO_IO_CTRL_GROUP4,MIZAR_GPIO_GP0_INTR1_INTR_EN1,MIZAR_GPIO_GP0_INTR1_INTR_STS1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Pass conditions per iteration:
-- Group status indicates that at least one interrupt occurred when the rising edge is generated.
-- After clearing per-pin raw status across all pins, the group status reads zero.
-- The system-level raw interrupt status bit for the instance is cleared after the write, as verified by a subsequent read. Overall pass when no errors are recorded.</t>
+          <t>["Per rising transition, the group interrupt status indicates an active bit and is subsequently cleared to zero after per-pin raw clears.", "System-level raw interrupt status for the selected instance is cleared during handler execution and the interrupt controller pending state is cleared.", "Overall test passes only if no timeouts occur and status checks and clears succeed across the tested iterations."]</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -877,18 +815,550 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Positive-edge interrupt test for all GPIO pads 8..39. test_case(): enables GIC(87/88); write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR or GPIO1); for i=0..31 write_reg(MIZAR_GPIO_GP0_GPIO_8+(i*4),0x00020000); set input via MIZAR_GPIO_GPIO_IO_CTRL_GROUP1..4=0x000000FF; write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1,0xFFFFFFFF); per-pin: drive 0xA0243ffc-&gt;0x00000000; int_pend=1; write 0xFFFFFFFF; wait with timeout; drive low; finish(test_err). ISR: wr_val=1&lt;&lt;i; int_pend=0; rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1,0x00000000); if((rdata_grp &amp; 0xffffffff)==0) error; for j=0..31 write_reg(MIZAR_GPIO_GP0_GPIO_8+(j*4),0x00010000); wait_on(2); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); expect 0; clear MIZAR_LSS_SYSREG_RAW_STCR1 bit for instance and verify; re-enable EN1=0xFFFFFFFF; clear GIC IRQ.</t>
+          <t>test_case(): #ifdef GPIO0 GIC_EnableIRQ(87) #endif; #ifdef GPIO1 GIC_EnableIRQ(88) #endif; write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR/1_INTR); for (i=0;i&lt;32;i++) write_reg(MIZAR_GPIO_GP0_GPIO_8 + i*4, 0x00020000); wait_on(10); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,0xFF); ... GROUP4,0xFF; wait_on(10); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF); For i=0..31: write_reg(0xA0243ffc,0x00000000); wait_on(10); int_pend=1; write_reg(0xA0243ffc,0xFFFFFFFF); int timeout=2000; while (int_pend==1 &amp;&amp; --timeout&gt;0) wait_on(10); if (timeout==0) { printf timeout; test_err++; break; } write_reg(0xA0243ffc,0x00000000); wait_on(10); finish(test_err). Default_IRQHandler(): wr_val=1&lt;&lt;i; int_pend=0; rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1,0x00000000); if ((rdata_grp &amp; 0xFFFFFFFF)!=0) pass else { printf error; test_err++; } for (j=0;j&lt;32;j++) write_reg(MIZAR_GPIO_GP0_GPIO_8 + j*4, 0x00010000); wait_on(2); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if (rdata_grp==0) pass else { printf error; test_err++; } #ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if ((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO0_INTR)!=0) test_err++; #endif #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO1_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if ((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO1_INTR)!=0) test_err++; #endif write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF); GIC_ClearIRQ(87/88).</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Arms the wait before toggling; bounded timeout=2000 with wait_on(10) per loop; masks group enables during service to avoid nested/overlapping events.</t>
+          <t>Group interrupt enable is masked during handler: write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0x00000000) and re-enabled later; bounded wait with timeout=2000 and wait_on(10) per loop.</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>test_case(): GIC_EnableIRQ(87/88) ifdef; write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR or GPIO1); for(i=0;i&lt;32;i++) write_reg(MIZAR_GPIO_GP0_GPIO_8+(i*4),0x00020000); wait_on(10); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP2,0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP3,0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP4,0x000000FF); wait_on(10); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1,0xFFFFFFFF); for(i=0;i&lt;32;i++){ write_reg(0xA0243ffc,0x00000000); wait_on(10); int_pend=1; write_reg(0xA0243ffc,0xFFFFFFFF); timeout=2000; while(int_pend &amp;&amp; --timeout&gt;0) wait_on(10); if(timeout==0){printf timeout; test_err++; break;} write_reg(0xA0243ffc,0x00000000); wait_on(10);} finish(test_err);
-Default_IRQHandler(): wr_val=1&lt;&lt;i; int_pend=0; rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1,0x00000000); if((rdata_grp &amp; 0xffffffff)!=0) ok else {printf error; test_err++;} for(j=0;j&lt;32;j++) write_reg(MIZAR_GPIO_GP0_GPIO_8+(j*4),0x00010000); wait_on(2); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if(rdata_grp==0) ok else {printf error; test_err++;} write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR or GPIO1); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIOx_INTR)!=0) {printf not cleared; test_err++;} write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1,0xFFFFFFFF); GIC_ClearIRQ(87/88);</t>
+          <t>["void test_case(): #ifdef GPIO0 GIC_EnableIRQ(87) #endif; #ifdef GPIO1 GIC_EnableIRQ(88) #endif; unsigned int rdata, wr_val; test_err=0;", "#ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR) #endif; #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO1_INTR) #endif;", "for (i=0;i&lt;32;i++) write_reg(MIZAR_GPIO_GP0_GPIO_8 + (i*4), 0x00020000);", "wait_on(10); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP2,0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP3,0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP4,0x000000FF);", "wait_on(10); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF);", "for (i=0;i&lt;32;i++): write_reg(0xA0243ffc,0x00000000); wait_on(10); int_pend=1; write_reg(0xA0243ffc,0xFFFFFFFF); int timeout=2000; while ((int_pend==1) &amp;&amp; (--timeout&gt;0)) wait_on(10); if (timeout==0) { printf timeout; test_err++; break; } write_reg(0xA0243ffc,0x00000000); wait_on(10); finish(test_err);", "void Default_IRQHandler(): wr_val=1&lt;&lt;i; int_pend=0; rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1,0x00000000); if ((rdata_grp &amp; 0xFFFFFFFF)!=0) { /* success */ } else { printf error; test_err++; } for (j=0;j&lt;32;j++) write_reg(MIZAR_GPIO_GP0_GPIO_8 + (j*4), 0x00010000); wait_on(2); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if (rdata_grp==0) { /* cleared */ } else { printf error; test_err++; } #ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if ((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO0_INTR)!=0) test_err++; #endif #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO1_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if ((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO1_INTR)!=0) test_err++; #endif write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1,0xFFFFFFFF); #ifdef GPIO0 GIC_ClearIRQ(87) #endif #ifdef GPIO1 GIC_ClearIRQ(88) #endif"]</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>MIZAR_LSS_SYSREG_INTR_EN1,MIZAR_LSS_SYSREG_RAW_STCR1,MIZAR_GPIO_GP0_GPIO_8,MIZAR_GPIO_GP0_GPIO_9,MIZAR_GPIO_GP0_GPIO_10,MIZAR_GPIO_GP0_GPIO_11,MIZAR_GPIO_GP0_GPIO_12,MIZAR_GPIO_GP0_GPIO_13,MIZAR_GPIO_GP0_GPIO_14,MIZAR_GPIO_GP0_GPIO_15,MIZAR_GPIO_GP0_GPIO_16,MIZAR_GPIO_GP0_GPIO_17,MIZAR_GPIO_GP0_GPIO_18,MIZAR_GPIO_GP0_GPIO_19,MIZAR_GPIO_GP0_GPIO_20,MIZAR_GPIO_GP0_GPIO_21,MIZAR_GPIO_GP0_GPIO_22,MIZAR_GPIO_GP0_GPIO_23,MIZAR_GPIO_GP0_GPIO_24,MIZAR_GPIO_GP0_GPIO_25,MIZAR_GPIO_GP0_GPIO_26,MIZAR_GPIO_GP0_GPIO_27,MIZAR_GPIO_GP0_GPIO_28,MIZAR_GPIO_GP0_GPIO_29,MIZAR_GPIO_GP0_GPIO_30,MIZAR_GPIO_GP0_GPIO_31,MIZAR_GPIO_GP0_GPIO_32,MIZAR_GPIO_GP0_GPIO_33,MIZAR_GPIO_GP0_GPIO_34,MIZAR_GPIO_GP0_GPIO_35,MIZAR_GPIO_GP0_GPIO_36,MIZAR_GPIO_GP0_GPIO_37,MIZAR_GPIO_GP0_GPIO_38,MIZAR_GPIO_GP0_GPIO_39,MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,MIZAR_GPIO_GPIO_IO_CTRL_GROUP2,MIZAR_GPIO_GPIO_IO_CTRL_GROUP3,MIZAR_GPIO_GPIO_IO_CTRL_GROUP4,MIZAR_GPIO_GP0_INTR1_INTR_EN1,MIZAR_GPIO_GP0_INTR1_INTR_STS1</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Handler sees non-zero read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); after for(j=0..31) write_reg(MIZAR_GPIO_GP0_GPIO_8 + j*4, 0x00010000) and wait_on(2), then read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1)==0; #ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); subsequent read_reg(MIZAR_LSS_SYSREG_RAW_STCR1) &amp; LSS_SYSREG_RAW_STCR1_GPIO0_INTR == 0. Same check for GPIO1 if defined. No timeout while (int_pend==1 &amp;&amp; --timeout&gt;0).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="82" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="82" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="82" customWidth="1" min="10" max="10"/>
+    <col width="82" customWidth="1" min="11" max="11"/>
+    <col width="82" customWidth="1" min="12" max="12"/>
+    <col width="82" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Mode</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Memory Start Offset</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Memory End Offset</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Impacted Registers</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Validation Criteria</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Dependencies</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Requirements</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>gpio_reg_wr_rd_test</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Verify that per-GPIO control and group registers power-on default values match the specification and that masked write/read operations behave correctly across the defined GPIO register set.</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>GPIO</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Independent control register for each GPIO</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Certain registers are intentionally skipped: VRRW-type and those marked non-readable/non-writable; default-read masks clear bit0; known caveat noted for DIN behavior affecting default reads.</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>1. Entry point begins the test and first performs a default reset-value verification over the configured list of GPIO-related registers.
+2. Iterate through the configured register list; for any entry flagged to skip default checking, continue without accessing the register.
+3. For entries not skipped and marked as readable, read the register and apply a mask that clears bit 0, then compare the result to the documented default value for that register.
+4. Record a failure if any masked default-value comparison does not match the expected default.
+5. Proceed to masked write/read verification using a fixed sequence of six data patterns applied to the same configured register list.
+6. For each data pattern, iterate over the register list: if an entry is flagged to skip or has a zero write mask, do not write; otherwise, write the data pattern masked by the register’s write mask.
+7. After completing writes for the current pattern, iterate again over the register list: skip entries with zero write or zero read masks; for others, read the register value and mask it with the register’s read mask.
+8. For each read, compute the expected value as: (written_data AND read_mask AND write_mask) OR ((bitwise NOT of write_mask) AND read_mask AND the register’s default value).
+9. Compare the masked read value with the computed expected value and record a failure on any mismatch.
+10. Conclude the test and report pass if no default-value or write/read mismatches were recorded; otherwise report fail.</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>MIZAR_GPIO_GP0_GPIO_8,MIZAR_GPIO_GP0_GPIO_9,MIZAR_GPIO_GP0_GPIO_10,MIZAR_GPIO_GP0_GPIO_11,MIZAR_GPIO_GP0_GPIO_12,MIZAR_GPIO_GP0_GPIO_13,MIZAR_GPIO_GP0_GPIO_14,MIZAR_GPIO_GP0_GPIO_15,MIZAR_GPIO_GP0_GPIO_16,MIZAR_GPIO_GP0_GPIO_17,MIZAR_GPIO_GP0_GPIO_18,MIZAR_GPIO_GP0_GPIO_19,MIZAR_GPIO_GP0_GPIO_20,MIZAR_GPIO_GP0_GPIO_21,MIZAR_GPIO_GP0_GPIO_22,MIZAR_GPIO_GP0_GPIO_23,MIZAR_GPIO_GP0_GPIO_24,MIZAR_GPIO_GP0_GPIO_25,MIZAR_GPIO_GP0_GPIO_26,MIZAR_GPIO_GP0_GPIO_27,MIZAR_GPIO_GP0_GPIO_28,MIZAR_GPIO_GP0_GPIO_29,MIZAR_GPIO_GP0_GPIO_30,MIZAR_GPIO_GP0_GPIO_31,MIZAR_GPIO_GP0_GPIO_32,MIZAR_GPIO_GP0_GPIO_33,MIZAR_GPIO_GP0_GPIO_34,MIZAR_GPIO_GP0_GPIO_35,MIZAR_GPIO_GP0_GPIO_36,MIZAR_GPIO_GP0_GPIO_37,MIZAR_GPIO_GP0_GPIO_38,MIZAR_GPIO_GP0_GPIO_39,MIZAR_GPIO_GPIO_INTR_RAW_STCLR1,MIZAR_GPIO_GP0_INTR1_INTR_EN1,MIZAR_GPIO_GP0_INTR1_INTR_STS1,MIZAR_GPIO_GP0_INTR2_INTR_EN1,MIZAR_GPIO_GP0_INTR2_INTR_STS1,MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,MIZAR_GPIO_GPIO_IO_CTRL_GROUP2,MIZAR_GPIO_GPIO_IO_CTRL_GROUP3,MIZAR_GPIO_GPIO_IO_CTRL_GROUP4,MIZAR_GPIO_GPIO_DOUT_GROUP1,MIZAR_GPIO_GPIO_DOUT_GROUP2,MIZAR_GPIO_GPIO_DOUT_GROUP3,MIZAR_GPIO_GPIO_DOUT_GROUP4,MIZAR_GPIO_GPIO_DIN_GROUP1,MIZAR_GPIO_GPIO_DIN_GROUP2,MIZAR_GPIO_GPIO_DIN_GROUP3,MIZAR_GPIO_GPIO_DIN_GROUP4</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>1. Default reset-value check passes only if, for every non-skipped readable register, (read_value AND 0xFFFFFFFE) equals the documented default value.
+2. Write/read check passes only if, for every non-skipped entry and for each test pattern, the masked read value equals: (written_data AND read_mask AND write_mask) OR ((bitwise NOT of write_mask) AND read_mask AND default_value).
+3. Overall test status is PASS when no default or write/read mismatches are recorded; otherwise FAIL.</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>test_gpio_negedge_intr_en</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Validate that each GPIO input (pads 8–39) can generate a falling-edge interrupt, that per-pin and group status latch correctly, and that both per-pin and group status can be cleared while the system interrupt path propagates and is serviced.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>GPIO</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Interrupts can be generated based on positive edge or negative edge or level high or level low detection at GPIO input</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Interrupt</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>0xA0243ffc</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>0xA0243ffc</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Interrupt wait uses a bounded polling loop with timeout; edge generation is ordered to arm the wait before toggling to avoid race; pad driver is returned to a known all-high state inside the handler before status checks.</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>1. Entry point initializes error counters and enables the appropriate CPU interrupt in the interrupt controller for the selected GPIO instance.
+2. Enable the system register output for the selected GPIO instance to route the group interrupt to the CPU.
+3. Drive the external pad driver register to all ones to establish a known-high state on all GPIO inputs.
+4. Configure each per-GPIO control register for pads 8 through 39 to input mode, enable negative-edge detection, and clear any pending per-pin raw status; insert a short wait after each configuration write.
+5. For each GPIO bit from 0 to 31 (corresponding to pads 8–39): pre-clear the corresponding group raw status bit, enable only that bit in the group interrupt-enable register, and wait briefly.
+6. Arm the interrupt-wait flag, then generate a falling edge on the selected pad by first driving all-high and then clearing only the target bit in the pad driver register.
+7. Poll the arm flag with a bounded timeout (initial count 5000) and periodic short waits until the interrupt handler indicates service completion or the timeout expires; on timeout, record an error.
+8. Interrupt handler actions upon entry: clear the wait flag and immediately return the pad driver to the all-high state.
+9. Read the per-GPIO control/status register for the active pad and confirm that the input data bit indicates low following the falling edge.
+10. Confirm that the per-pin raw interrupt indication is set, then read the group interrupt status register and verify that the corresponding bit is asserted.
+11. Clear the per-pin raw status by writing the clear bit while preserving input mode, and clear the group raw status by writing one to the corresponding group clear register.
+12. Verify that the group status register reads zero after clears, clear the system-level raw interrupt status for the selected instance, and clear the pending interrupt in the interrupt controller.</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>MIZAR_LSS_SYSREG_INTR_EN1,MIZAR_LSS_SYSREG_RAW_STCR1,MIZAR_GPIO_GP0_GPIO_8,MIZAR_GPIO_GP0_GPIO_9,MIZAR_GPIO_GP0_GPIO_10,MIZAR_GPIO_GP0_GPIO_11,MIZAR_GPIO_GP0_GPIO_12,MIZAR_GPIO_GP0_GPIO_13,MIZAR_GPIO_GP0_GPIO_14,MIZAR_GPIO_GP0_GPIO_15,MIZAR_GPIO_GP0_GPIO_16,MIZAR_GPIO_GP0_GPIO_17,MIZAR_GPIO_GP0_GPIO_18,MIZAR_GPIO_GP0_GPIO_19,MIZAR_GPIO_GP0_GPIO_20,MIZAR_GPIO_GP0_GPIO_21,MIZAR_GPIO_GP0_GPIO_22,MIZAR_GPIO_GP0_GPIO_23,MIZAR_GPIO_GP0_GPIO_24,MIZAR_GPIO_GP0_GPIO_25,MIZAR_GPIO_GP0_GPIO_26,MIZAR_GPIO_GP0_GPIO_27,MIZAR_GPIO_GP0_GPIO_28,MIZAR_GPIO_GP0_GPIO_29,MIZAR_GPIO_GP0_GPIO_30,MIZAR_GPIO_GP0_GPIO_31,MIZAR_GPIO_GP0_GPIO_32,MIZAR_GPIO_GP0_GPIO_33,MIZAR_GPIO_GP0_GPIO_34,MIZAR_GPIO_GP0_GPIO_35,MIZAR_GPIO_GP0_GPIO_36,MIZAR_GPIO_GP0_GPIO_37,MIZAR_GPIO_GP0_GPIO_38,MIZAR_GPIO_GP0_GPIO_39,MIZAR_GPIO_GP0_INTR1_INTR_EN1,MIZAR_GPIO_GP0_INTR1_INTR_STS1,MIZAR_GPIO_GPIO_INTR_RAW_STCLR1</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>1. For each pad tested, the per-pin input data reflects low after the induced falling edge.
+2. Per-pin raw interrupt indication is set for the active pad and the corresponding group status bit is asserted.
+3. After issuing per-pin and group clears, the group status register reads zero.
+4. System-level raw interrupt status for the selected instance is cleared after service, and the interrupt controller is cleared.
+5. Overall test passes only if no timeouts occur and no verification steps report errors.</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>test_gpio_pedge_all_pads_en</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Validate that enabling positive-edge detection on all GPIO inputs (pads 8–39) produces an interrupt per rising transition, that group status asserts and can be cleared for all pads, and that the system interrupt path is properly cleared and re-enabled between events.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>GPIO</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Interrupts can be generated based on positive edge or negative edge or level high or level low detection at GPIO input</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Interrupt</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0xA0243ffc</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0xA0243ffc</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Group interrupt is masked during service and re-enabled afterward; the wait loop for the handler is bounded by a timeout; input mode for pads is configured via group I/O control registers to ensure edge detection.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1. Entry point enables the appropriate CPU interrupt for the selected GPIO instance in the interrupt controller.
+2. Enable the system register output for the selected GPIO instance to route the group interrupt.
+3. Configure per-GPIO control registers for pads 8 through 39 to enable positive-edge interrupt detection.
+4. Set pads 8–39 to input mode using the four group I/O control registers.
+5. Enable all bits in the group interrupt-enable register.
+6. For each pad index from 0 to 31: drive the external pad driver low, wait briefly, arm the wait flag, then drive the external pad driver high to generate a single rising edge.
+7. Poll the wait flag with a bounded timeout (initial count 2000) and periodic short waits to confirm the interrupt was serviced; on timeout, record an error and exit the loop.
+8. After each iteration, optionally return the pad driver low and wait briefly to prepare for the next edge.
+9. Interrupt handler actions: clear the wait flag; read the group interrupt status; mask the group enable during service; check that at least one group bit is asserted; clear per-pin raw status across all pads by writing the per-GPIO clear bit in each control register and wait briefly.
+10. Verify that the group status is zero following the clears; clear the system-level raw status for the selected instance; re-enable the group interrupt and clear the pending interrupt in the interrupt controller.</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>MIZAR_LSS_SYSREG_INTR_EN1,MIZAR_LSS_SYSREG_RAW_STCR1,MIZAR_GPIO_GP0_GPIO_8,MIZAR_GPIO_GP0_GPIO_9,MIZAR_GPIO_GP0_GPIO_10,MIZAR_GPIO_GP0_GPIO_11,MIZAR_GPIO_GP0_GPIO_12,MIZAR_GPIO_GP0_GPIO_13,MIZAR_GPIO_GP0_GPIO_14,MIZAR_GPIO_GP0_GPIO_15,MIZAR_GPIO_GP0_GPIO_16,MIZAR_GPIO_GP0_GPIO_17,MIZAR_GPIO_GP0_GPIO_18,MIZAR_GPIO_GP0_GPIO_19,MIZAR_GPIO_GP0_GPIO_20,MIZAR_GPIO_GP0_GPIO_21,MIZAR_GPIO_GP0_GPIO_22,MIZAR_GPIO_GP0_GPIO_23,MIZAR_GPIO_GP0_GPIO_24,MIZAR_GPIO_GP0_GPIO_25,MIZAR_GPIO_GP0_GPIO_26,MIZAR_GPIO_GP0_GPIO_27,MIZAR_GPIO_GP0_GPIO_28,MIZAR_GPIO_GP0_GPIO_29,MIZAR_GPIO_GP0_GPIO_30,MIZAR_GPIO_GP0_GPIO_31,MIZAR_GPIO_GP0_GPIO_32,MIZAR_GPIO_GP0_GPIO_33,MIZAR_GPIO_GP0_GPIO_34,MIZAR_GPIO_GP0_GPIO_35,MIZAR_GPIO_GP0_GPIO_36,MIZAR_GPIO_GP0_GPIO_37,MIZAR_GPIO_GP0_GPIO_38,MIZAR_GPIO_GP0_GPIO_39,MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,MIZAR_GPIO_GPIO_IO_CTRL_GROUP2,MIZAR_GPIO_GPIO_IO_CTRL_GROUP3,MIZAR_GPIO_GPIO_IO_CTRL_GROUP4,MIZAR_GPIO_GP0_INTR1_INTR_EN1,MIZAR_GPIO_GP0_INTR1_INTR_STS1</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1. Per rising transition, the group interrupt status indicates an active bit and is subsequently cleared to zero after per-pin raw clears.
+2. System-level raw interrupt status for the selected instance is cleared during handler execution and the interrupt controller pending state is cleared.
+3. Overall test passes only if no timeouts occur and status checks and clears succeed across the tested iterations.</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="82" customWidth="1" min="2" max="2"/>
+    <col width="82" customWidth="1" min="3" max="3"/>
+    <col width="82" customWidth="1" min="4" max="4"/>
+    <col width="82" customWidth="1" min="5" max="5"/>
+    <col width="82" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hidden_Test_Case_Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Hidden_Test_Description</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Hidden_Remarks</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Hidden_Test_Steps_Procedure</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Hidden_Impacted_Registers</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Hidden_Validation_Acceptance_Criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>gpio_reg_wr_rd_test</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>program.c invokes chk_rst_val() then chk_rd_wr(), and finishes with pass/fail based on def_fail_cnt and wr_fail_cnt. chk_rst_val() loops i=0..CNT-1 using addr=addr_array[i] (macros like MIZAR_GPIO_GP0_GPIO_8..GPIO_39, group regs, intr regs). It skips entries where skip_rst_array[i]==1 or read_mask_array[i]==0, reads via read_reg(addr), masks data_rd with 0xFFFFFFFE, and compares to default_value_array[i]. chk_rd_wr() tries six patterns (0xFFFFFFFF,0xAAAAAAAA,0x55555555,0xF5F5F5F5,0xA5A5A5A5,0xFFFF0000). For each i: if skip_array[i]==1 or write_mask_array[i]==0, it skips; else it write_reg(addr,(data_wr &amp; write_mask_array[i])). Then it reads back masked by read_mask_array[i], computes wr_n=(write_mask_array[i]^0xFFFFFFFF), and expected=((data_wr &amp; read_mask_array[i] &amp; write_mask_array[i]) | (wr_n &amp; read_mask_array[i] &amp; default_value_array[i])). Mismatch increments wr_fail_cnt. finish(1) if any failures, else finish(0).</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>test_define.c: //80,94,98,9c,a0,a4,a8,ac,b0...SKIPPING VRRW registers. skip_array[] and skip_rst_array[] specify which registers to skip. Comment: when reading default values the din value is becoming 1 automatically if we don't force any value, but if we force zero to din bit level sel becoming high, so that reading value not matched with expected value.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>["int test_case(): calls chk_rst_val(); calls chk_rd_wr(); if (def_fail_cnt &gt; 0 || wr_fail_cnt &gt; 0) finish(1); else finish(0).", "void chk_rst_val(): for (i=0;i&lt;CNT;i++): addr=addr_array[i] (e.g., MIZAR_GPIO_GP0_GPIO_8..MIZAR_GPIO_GP0_GPIO_39, MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, MIZAR_GPIO_GP0_INTRx_xxx, GPIO_IO_CTRL_GROUPx, GPIO_DOUT_GROUPx, GPIO_DIN_GROUPx); if (skip_rst_array[i]==1) continue; if (read_mask_array[i]==0) continue; data_rd=read_reg(addr); data=(data_rd &amp; 0xFFFFFFFE); if (data==default_value_array[i]) pass; else { def_fail_cnt++; printf failure }. No waits/timeouts.", "void chk_rd_wr(): unsigned chk_val[6]={0xFFFFFFFF,0xAAAAAAAA,0x55555555,0xF5F5F5F5,0xA5A5A5A5,0xFFFF0000}; For each pattern j: data_wr=chk_val[j]; Write phase: for (i=0;i&lt;CNT;i++): addr=addr_array[i]; if (skip_array[i]==1) continue; if (write_mask_array[i]==0) continue; else write_reg(addr,(data_wr &amp; write_mask_array[i])). Read/verify phase: for (i=0;i&lt;CNT;i++): addr=addr_array[i]; if (skip_array[i]==1) continue; if (write_mask_array[i]==0) continue; if (read_mask_array[i]==0) continue; data_rd=(read_reg(addr) &amp; read_mask_array[i]); wr_n=(write_mask_array[i] ^ 0xFFFFFFFF); exp_val=((data_wr &amp; read_mask_array[i] &amp; write_mask_array[i]) | (wr_n &amp; read_mask_array[i] &amp; default_value_array[i])); if (data_rd==exp_val) pass; else { wr_fail_cnt++; printf failure }."]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>MIZAR_GPIO_GP0_GPIO_8,MIZAR_GPIO_GP0_GPIO_9,MIZAR_GPIO_GP0_GPIO_10,MIZAR_GPIO_GP0_GPIO_11,MIZAR_GPIO_GP0_GPIO_12,MIZAR_GPIO_GP0_GPIO_13,MIZAR_GPIO_GP0_GPIO_14,MIZAR_GPIO_GP0_GPIO_15,MIZAR_GPIO_GP0_GPIO_16,MIZAR_GPIO_GP0_GPIO_17,MIZAR_GPIO_GP0_GPIO_18,MIZAR_GPIO_GP0_GPIO_19,MIZAR_GPIO_GP0_GPIO_20,MIZAR_GPIO_GP0_GPIO_21,MIZAR_GPIO_GP0_GPIO_22,MIZAR_GPIO_GP0_GPIO_23,MIZAR_GPIO_GP0_GPIO_24,MIZAR_GPIO_GP0_GPIO_25,MIZAR_GPIO_GP0_GPIO_26,MIZAR_GPIO_GP0_GPIO_27,MIZAR_GPIO_GP0_GPIO_28,MIZAR_GPIO_GP0_GPIO_29,MIZAR_GPIO_GP0_GPIO_30,MIZAR_GPIO_GP0_GPIO_31,MIZAR_GPIO_GP0_GPIO_32,MIZAR_GPIO_GP0_GPIO_33,MIZAR_GPIO_GP0_GPIO_34,MIZAR_GPIO_GP0_GPIO_35,MIZAR_GPIO_GP0_GPIO_36,MIZAR_GPIO_GP0_GPIO_37,MIZAR_GPIO_GP0_GPIO_38,MIZAR_GPIO_GP0_GPIO_39,MIZAR_GPIO_GPIO_INTR_RAW_STCLR1,MIZAR_GPIO_GP0_INTR1_INTR_EN1,MIZAR_GPIO_GP0_INTR1_INTR_STS1,MIZAR_GPIO_GP0_INTR2_INTR_EN1,MIZAR_GPIO_GP0_INTR2_INTR_STS1,MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,MIZAR_GPIO_GPIO_IO_CTRL_GROUP2,MIZAR_GPIO_GPIO_IO_CTRL_GROUP3,MIZAR_GPIO_GPIO_IO_CTRL_GROUP4,MIZAR_GPIO_GPIO_DOUT_GROUP1,MIZAR_GPIO_GPIO_DOUT_GROUP2,MIZAR_GPIO_GPIO_DOUT_GROUP3,MIZAR_GPIO_GPIO_DOUT_GROUP4,MIZAR_GPIO_GPIO_DIN_GROUP1,MIZAR_GPIO_GPIO_DIN_GROUP2,MIZAR_GPIO_GPIO_DIN_GROUP3,MIZAR_GPIO_GPIO_DIN_GROUP4</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Default pass criterion: for all i where skip_rst_array[i]==0 and read_mask_array[i]!=0, (read_reg(addr_array[i]) &amp; 0xFFFFFFFE) == default_value_array[i]. Write/read pass criterion: for all i where skip_array[i]==0, write_mask_array[i]!=0, read_mask_array[i]!=0, and for each j in 0..5, (read_reg(addr_array[i]) &amp; read_mask_array[i]) == ((chk_val[j] &amp; read_mask_array[i] &amp; write_mask_array[i]) | ((write_mask_array[i]^0xFFFFFFFF) &amp; read_mask_array[i] &amp; default_value_array[i])). Overall finish(0) indicates PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>test_gpio_negedge_intr_en</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>program.c sets up negedge interrupts. In test_case(): optionally GIC_EnableIRQ(87/88); write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR or LSS_SYSREG_INTR_EN1_GPIO1_INTR); write_reg(0xA0243ffc, 0xffffffff); for i=0..31: addr1 = MIZAR_GPIO_GP0_GPIO_8 + (i*4); write_reg(addr1, (1&lt;&lt;20)|(1&lt;&lt;18)|(1&lt;&lt;16)); wait_on(10). For each i: wr_val=1&lt;&lt;i; write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, wr_val); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, wr_val); wait_on(10); int_pend=1; write_reg(0xA0243ffc, 0xffffffff); wait_on(30); write_reg(0xA0243ffc, ~wr_val); timeout=5000; while (int_pend &amp;&amp; timeout--) wait_on(10); if timeout==0 error++. finish(test_err). Default_IRQHandler(): local_wr=1&lt;&lt;i; int_pend=0; write_reg(0xA0243ffc, 0xffffffff); raddr=MIZAR_GPIO_GP0_GPIO_8 + (i*4); rdata=read_reg(raddr); if ((rdata &amp; 0x1)!=0) error++; if ((rdata &amp; 0x2)!=0x0) { rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if ((rdata_grp &amp; local_wr)==0) error++; write_reg(MIZAR_GPIO_GP0_GPIO_8 + (i*4), (1&lt;&lt;20)|(1&lt;&lt;16)); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, local_wr); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if (rdata_grp!=0x0) error++; write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR/1_INTR); GIC_ClearIRQ(87/88); } else error++;</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Wait-before-edge arming to avoid race: comment indicates arming int_pend before generating the edge. Uses bounded wait: timeout=5000 with wait_on(10) per loop. Pad driver (0xA0243ffc) set to known state inside ISR.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>["int test_case(): test_err=0; #ifdef GPIO0 GIC_EnableIRQ(87) #endif; #ifdef GPIO1 GIC_EnableIRQ(88) #endif;", "#ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR) #endif; #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO1_INTR) #endif;", "write_reg(0xA0243ffc, 0xFFFFFFFF);", "for (i=0;i&lt;32;i++): addr1=MIZAR_GPIO_GP0_GPIO_8 + (i*4); write_reg(addr1, (1&lt;&lt;20)|(1&lt;&lt;18)|(1&lt;&lt;16)); wait_on(10);", "for (i=0;i&lt;32;i++): wr_val=1&lt;&lt;i; write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, wr_val); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, wr_val); wait_on(10); int_pend=1; write_reg(0xA0243ffc, 0xFFFFFFFF); wait_on(30); write_reg(0xA0243ffc, ~wr_val);", "unsigned int timeout=5000; while (int_pend &amp;&amp; timeout--) wait_on(10); if (timeout==0) { printf timeout; test_err++; }", "finish(test_err);", "void Default_IRQHandler(): unsigned int local_wr=1&lt;&lt;i; int_pend=0; write_reg(0xA0243ffc, 0xFFFFFFFF); raddr=MIZAR_GPIO_GP0_GPIO_8 + (i*4); rdata=read_reg(raddr);", "if ((rdata &amp; 0x1)!=0) test_err++;", "if ((rdata &amp; 0x2)!=0x0) { rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if ((rdata_grp &amp; local_wr)==0) test_err++; write_reg(MIZAR_GPIO_GP0_GPIO_8 + (i*4), (1&lt;&lt;20)|(1&lt;&lt;16)); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, local_wr); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if (rdata_grp!=0x0) test_err++; #ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); GIC_ClearIRQ(87); #endif #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO1_INTR); GIC_ClearIRQ(88); #endif } else { test_err++; }"]</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>MIZAR_LSS_SYSREG_INTR_EN1,MIZAR_LSS_SYSREG_RAW_STCR1,MIZAR_GPIO_GP0_GPIO_8,MIZAR_GPIO_GP0_GPIO_9,MIZAR_GPIO_GP0_GPIO_10,MIZAR_GPIO_GP0_GPIO_11,MIZAR_GPIO_GP0_GPIO_12,MIZAR_GPIO_GP0_GPIO_13,MIZAR_GPIO_GP0_GPIO_14,MIZAR_GPIO_GP0_GPIO_15,MIZAR_GPIO_GP0_GPIO_16,MIZAR_GPIO_GP0_GPIO_17,MIZAR_GPIO_GP0_GPIO_18,MIZAR_GPIO_GP0_GPIO_19,MIZAR_GPIO_GP0_GPIO_20,MIZAR_GPIO_GP0_GPIO_21,MIZAR_GPIO_GP0_GPIO_22,MIZAR_GPIO_GP0_GPIO_23,MIZAR_GPIO_GP0_GPIO_24,MIZAR_GPIO_GP0_GPIO_25,MIZAR_GPIO_GP0_GPIO_26,MIZAR_GPIO_GP0_GPIO_27,MIZAR_GPIO_GP0_GPIO_28,MIZAR_GPIO_GP0_GPIO_29,MIZAR_GPIO_GP0_GPIO_30,MIZAR_GPIO_GP0_GPIO_31,MIZAR_GPIO_GP0_GPIO_32,MIZAR_GPIO_GP0_GPIO_33,MIZAR_GPIO_GP0_GPIO_34,MIZAR_GPIO_GP0_GPIO_35,MIZAR_GPIO_GP0_GPIO_36,MIZAR_GPIO_GP0_GPIO_37,MIZAR_GPIO_GP0_GPIO_38,MIZAR_GPIO_GP0_GPIO_39,MIZAR_GPIO_GP0_INTR1_INTR_EN1,MIZAR_GPIO_GP0_INTR1_INTR_STS1,MIZAR_GPIO_GPIO_INTR_RAW_STCLR1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pass per pin when: after falling edge, (read_reg(MIZAR_GPIO_GP0_GPIO_8 + i*4) &amp; 0x1) == 0; (read_reg(MIZAR_GPIO_GP0_GPIO_8 + i*4) &amp; 0x2) != 0; (read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1) &amp; (1&lt;&lt;i)) != 0; after write_reg(MIZAR_GPIO_GP0_GPIO_8 + i*4, (1&lt;&lt;20)|(1&lt;&lt;16)) and write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, 1&lt;&lt;i), then read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1) == 0. System status cleared via MIZAR_LSS_SYSREG_RAW_STCR1 and GIC cleared. No timeout in while(int_pend &amp;&amp; timeout--) loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>test_gpio_pedge_all_pads_en</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>test_case(): #ifdef GPIO0 GIC_EnableIRQ(87) #endif; #ifdef GPIO1 GIC_EnableIRQ(88) #endif; write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR/1_INTR); for (i=0;i&lt;32;i++) write_reg(MIZAR_GPIO_GP0_GPIO_8 + i*4, 0x00020000); wait_on(10); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,0xFF); ... GROUP4,0xFF; wait_on(10); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF); For i=0..31: write_reg(0xA0243ffc,0x00000000); wait_on(10); int_pend=1; write_reg(0xA0243ffc,0xFFFFFFFF); int timeout=2000; while (int_pend==1 &amp;&amp; --timeout&gt;0) wait_on(10); if (timeout==0) { printf timeout; test_err++; break; } write_reg(0xA0243ffc,0x00000000); wait_on(10); finish(test_err). Default_IRQHandler(): wr_val=1&lt;&lt;i; int_pend=0; rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1,0x00000000); if ((rdata_grp &amp; 0xFFFFFFFF)!=0) pass else { printf error; test_err++; } for (j=0;j&lt;32;j++) write_reg(MIZAR_GPIO_GP0_GPIO_8 + j*4, 0x00010000); wait_on(2); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if (rdata_grp==0) pass else { printf error; test_err++; } #ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if ((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO0_INTR)!=0) test_err++; #endif #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO1_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if ((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO1_INTR)!=0) test_err++; #endif write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF); GIC_ClearIRQ(87/88).</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Group interrupt enable is masked during handler: write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0x00000000) and re-enabled later; bounded wait with timeout=2000 and wait_on(10) per loop.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>["void test_case(): #ifdef GPIO0 GIC_EnableIRQ(87) #endif; #ifdef GPIO1 GIC_EnableIRQ(88) #endif; unsigned int rdata, wr_val; test_err=0;", "#ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR) #endif; #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO1_INTR) #endif;", "for (i=0;i&lt;32;i++) write_reg(MIZAR_GPIO_GP0_GPIO_8 + (i*4), 0x00020000);", "wait_on(10); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP2,0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP3,0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP4,0x000000FF);", "wait_on(10); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF);", "for (i=0;i&lt;32;i++): write_reg(0xA0243ffc,0x00000000); wait_on(10); int_pend=1; write_reg(0xA0243ffc,0xFFFFFFFF); int timeout=2000; while ((int_pend==1) &amp;&amp; (--timeout&gt;0)) wait_on(10); if (timeout==0) { printf timeout; test_err++; break; } write_reg(0xA0243ffc,0x00000000); wait_on(10); finish(test_err);", "void Default_IRQHandler(): wr_val=1&lt;&lt;i; int_pend=0; rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1,0x00000000); if ((rdata_grp &amp; 0xFFFFFFFF)!=0) { /* success */ } else { printf error; test_err++; } for (j=0;j&lt;32;j++) write_reg(MIZAR_GPIO_GP0_GPIO_8 + (j*4), 0x00010000); wait_on(2); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if (rdata_grp==0) { /* cleared */ } else { printf error; test_err++; } #ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if ((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO0_INTR)!=0) test_err++; #endif #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO1_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if ((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO1_INTR)!=0) test_err++; #endif write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1,0xFFFFFFFF); #ifdef GPIO0 GIC_ClearIRQ(87) #endif #ifdef GPIO1 GIC_ClearIRQ(88) #endif"]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MIZAR_LSS_SYSREG_INTR_EN1,MIZAR_LSS_SYSREG_RAW_STCR1,MIZAR_GPIO_GP0_GPIO_8,MIZAR_GPIO_GP0_GPIO_9,MIZAR_GPIO_GP0_GPIO_10,MIZAR_GPIO_GP0_GPIO_11,MIZAR_GPIO_GP0_GPIO_12,MIZAR_GPIO_GP0_GPIO_13,MIZAR_GPIO_GP0_GPIO_14,MIZAR_GPIO_GP0_GPIO_15,MIZAR_GPIO_GP0_GPIO_16,MIZAR_GPIO_GP0_GPIO_17,MIZAR_GPIO_GP0_GPIO_18,MIZAR_GPIO_GP0_GPIO_19,MIZAR_GPIO_GP0_GPIO_20,MIZAR_GPIO_GP0_GPIO_21,MIZAR_GPIO_GP0_GPIO_22,MIZAR_GPIO_GP0_GPIO_23,MIZAR_GPIO_GP0_GPIO_24,MIZAR_GPIO_GP0_GPIO_25,MIZAR_GPIO_GP0_GPIO_26,MIZAR_GPIO_GP0_GPIO_27,MIZAR_GPIO_GP0_GPIO_28,MIZAR_GPIO_GP0_GPIO_29,MIZAR_GPIO_GP0_GPIO_30,MIZAR_GPIO_GP0_GPIO_31,MIZAR_GPIO_GP0_GPIO_32,MIZAR_GPIO_GP0_GPIO_33,MIZAR_GPIO_GP0_GPIO_34,MIZAR_GPIO_GP0_GPIO_35,MIZAR_GPIO_GP0_GPIO_36,MIZAR_GPIO_GP0_GPIO_37,MIZAR_GPIO_GP0_GPIO_38,MIZAR_GPIO_GP0_GPIO_39,MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,MIZAR_GPIO_GPIO_IO_CTRL_GROUP2,MIZAR_GPIO_GPIO_IO_CTRL_GROUP3,MIZAR_GPIO_GPIO_IO_CTRL_GROUP4,MIZAR_GPIO_GP0_INTR1_INTR_EN1,MIZAR_GPIO_GP0_INTR1_INTR_STS1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Handler sees non-zero read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); after for(j=0..31) write_reg(MIZAR_GPIO_GP0_GPIO_8 + j*4, 0x00010000) and wait_on(2), then read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1)==0; #ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); subsequent read_reg(MIZAR_LSS_SYSREG_RAW_STCR1) &amp; LSS_SYSREG_RAW_STCR1_GPIO0_INTR == 0. Same check for GPIO1 if defined. No timeout while (int_pend==1 &amp;&amp; --timeout&gt;0).</t>
         </is>
       </c>
     </row>

--- a/Test_Output/GPIO/TestPlan/GPIO_TestPlan_1.xlsx
+++ b/Test_Output/GPIO/TestPlan/GPIO_TestPlan_1.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="GPIO_TestPlan" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Hidden_Details" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -51,14 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,29 +417,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="82" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="129" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="82" customWidth="1" min="5" max="5"/>
+    <col width="150" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="82" customWidth="1" min="10" max="10"/>
-    <col width="82" customWidth="1" min="11" max="11"/>
-    <col width="82" customWidth="1" min="12" max="12"/>
-    <col width="82" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="150" customWidth="1" min="10" max="10"/>
+    <col width="150" customWidth="1" min="11" max="11"/>
+    <col width="150" customWidth="1" min="12" max="12"/>
+    <col width="150" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="14" max="14"/>
     <col width="29" customWidth="1" min="15" max="15"/>
-    <col width="82" customWidth="1" min="16" max="16"/>
-    <col width="82" customWidth="1" min="17" max="17"/>
-    <col width="82" customWidth="1" min="18" max="18"/>
-    <col width="82" customWidth="1" min="19" max="19"/>
-    <col width="82" customWidth="1" min="20" max="20"/>
+    <col width="150" customWidth="1" min="16" max="16"/>
+    <col width="150" customWidth="1" min="17" max="17"/>
+    <col width="150" customWidth="1" min="18" max="18"/>
+    <col width="150" customWidth="1" min="19" max="19"/>
+    <col width="150" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -602,7 +595,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>["Entry point begins the test and first performs a default reset-value verification over the configured list of GPIO-related registers.", "Iterate through the configured register list; for any entry flagged to skip default checking, continue without accessing the register.", "For entries not skipped and marked as readable, read the register and apply a mask that clears bit 0, then compare the result to the documented default value for that register.", "Record a failure if any masked default-value comparison does not match the expected default.", "Proceed to masked write/read verification using a fixed sequence of six data patterns applied to the same configured register list.", "For each data pattern, iterate over the register list: if an entry is flagged to skip or has a zero write mask, do not write; otherwise, write the data pattern masked by the register’s write mask.", "After completing writes for the current pattern, iterate again over the register list: skip entries with zero write or zero read masks; for others, read the register value and mask it with the register’s read mask.", "For each read, compute the expected value as: (written_data AND read_mask AND write_mask) OR ((bitwise NOT of write_mask) AND read_mask AND the register’s default value).", "Compare the masked read value with the computed expected value and record a failure on any mismatch.", "Conclude the test and report pass if no default-value or write/read mismatches were recorded; otherwise report fail."]</t>
+          <t>["Entry point begins the test and first performs a default reset-value verification over the configured list of GPIO-related registers.","Iterate through the configured register list; for any entry flagged to skip default checking, continue without accessing the register.","For entries not skipped and marked as readable, read the register and apply a mask that clears bit 0, then compare the result to the documented default value for that register.","Record a failure if any masked default-value comparison does not match the expected default.","Proceed to masked write/read verification using a fixed sequence of six data patterns applied to the same configured register list.","For each data pattern, iterate over the register list: if an entry is flagged to skip or has a zero write mask, do not write; otherwise, write the data pattern masked by the register’s write mask.","After completing writes for the current pattern, iterate again over the register list: skip entries with zero write or zero read masks; for others, read the register value and mask it with the register’s read mask.","For each read, compute the expected value as: (written_data AND read_mask AND write_mask) OR ((bitwise NOT of write_mask) AND read_mask AND the register’s default value).","Compare the masked read value with the computed expected value and record a failure on any mismatch.","Conclude the test and report pass if no default-value or write/read mismatches were recorded; otherwise report fail."]</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -612,7 +605,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>["Default reset-value check passes only if, for every non-skipped readable register, (read_value AND 0xFFFFFFFE) equals the documented default value.", "Write/read check passes only if, for every non-skipped entry and for each test pattern, the masked read value equals: (written_data AND read_mask AND write_mask) OR ((bitwise NOT of write_mask) AND read_mask AND default_value).", "Overall test status is PASS when no default or write/read mismatches are recorded; otherwise FAIL."]</t>
+          <t>["Default reset-value check passes only if, for every non-skipped readable register, (read_value AND 0xFFFFFFFE) equals the documented default value.","Write/read check passes only if, for every non-skipped entry and for each test pattern, the masked read value equals: (written_data AND read_mask AND write_mask) OR ((bitwise NOT of write_mask) AND read_mask AND default_value).","Overall test status is PASS when no default or write/read mismatches are recorded; otherwise FAIL."]</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -633,7 +626,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>["int test_case(): calls chk_rst_val(); calls chk_rd_wr(); if (def_fail_cnt &gt; 0 || wr_fail_cnt &gt; 0) finish(1); else finish(0).", "void chk_rst_val(): for (i=0;i&lt;CNT;i++): addr=addr_array[i] (e.g., MIZAR_GPIO_GP0_GPIO_8..MIZAR_GPIO_GP0_GPIO_39, MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, MIZAR_GPIO_GP0_INTRx_xxx, GPIO_IO_CTRL_GROUPx, GPIO_DOUT_GROUPx, GPIO_DIN_GROUPx); if (skip_rst_array[i]==1) continue; if (read_mask_array[i]==0) continue; data_rd=read_reg(addr); data=(data_rd &amp; 0xFFFFFFFE); if (data==default_value_array[i]) pass; else { def_fail_cnt++; printf failure }. No waits/timeouts.", "void chk_rd_wr(): unsigned chk_val[6]={0xFFFFFFFF,0xAAAAAAAA,0x55555555,0xF5F5F5F5,0xA5A5A5A5,0xFFFF0000}; For each pattern j: data_wr=chk_val[j]; Write phase: for (i=0;i&lt;CNT;i++): addr=addr_array[i]; if (skip_array[i]==1) continue; if (write_mask_array[i]==0) continue; else write_reg(addr,(data_wr &amp; write_mask_array[i])). Read/verify phase: for (i=0;i&lt;CNT;i++): addr=addr_array[i]; if (skip_array[i]==1) continue; if (write_mask_array[i]==0) continue; if (read_mask_array[i]==0) continue; data_rd=(read_reg(addr) &amp; read_mask_array[i]); wr_n=(write_mask_array[i] ^ 0xFFFFFFFF); exp_val=((data_wr &amp; read_mask_array[i] &amp; write_mask_array[i]) | (wr_n &amp; read_mask_array[i] &amp; default_value_array[i])); if (data_rd==exp_val) pass; else { wr_fail_cnt++; printf failure }."]</t>
+          <t>["int test_case(): calls chk_rst_val(); calls chk_rd_wr(); if (def_fail_cnt &gt; 0 || wr_fail_cnt &gt; 0) finish(1); else finish(0).","void chk_rst_val(): for (i=0;i&lt;CNT;i++): addr=addr_array[i] (e.g., MIZAR_GPIO_GP0_GPIO_8..MIZAR_GPIO_GP0_GPIO_39, MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, MIZAR_GPIO_GP0_INTRx_xxx, GPIO_IO_CTRL_GROUPx, GPIO_DOUT_GROUPx, GPIO_DIN_GROUPx); if (skip_rst_array[i]==1) continue; if (read_mask_array[i]==0) continue; data_rd=read_reg(addr); data=(data_rd &amp; 0xFFFFFFFE); if (data==default_value_array[i]) pass; else { def_fail_cnt++; printf failure }. No waits/timeouts.","void chk_rd_wr(): unsigned chk_val[6]={0xFFFFFFFF,0xAAAAAAAA,0x55555555,0xF5F5F5F5,0xA5A5A5A5,0xFFFF0000}; For each pattern j: data_wr=chk_val[j]; Write phase: for (i=0;i&lt;CNT;i++): addr=addr_array[i]; if (skip_array[i]==1) continue; if (write_mask_array[i]==0) continue; else write_reg(addr,(data_wr &amp; write_mask_array[i])). Read/verify phase: for (i=0;i&lt;CNT;i++): addr=addr_array[i]; if (skip_array[i]==1) continue; if (write_mask_array[i]==0) continue; if (read_mask_array[i]==0) continue; data_rd=(read_reg(addr) &amp; read_mask_array[i]); wr_n=(write_mask_array[i] ^ 0xFFFFFFFF); exp_val=((data_wr &amp; read_mask_array[i] &amp; write_mask_array[i]) | (wr_n &amp; read_mask_array[i] &amp; default_value_array[i])); if (data_rd==exp_val) pass; else { wr_fail_cnt++; printf failure }."]</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -698,7 +691,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>["Entry point initializes error counters and enables the appropriate CPU interrupt in the interrupt controller for the selected GPIO instance.", "Enable the system register output for the selected GPIO instance to route the group interrupt to the CPU.", "Drive the external pad driver register to all ones to establish a known-high state on all GPIO inputs.", "Configure each per-GPIO control register for pads 8 through 39 to input mode, enable negative-edge detection, and clear any pending per-pin raw status; insert a short wait after each configuration write.", "For each GPIO bit from 0 to 31 (corresponding to pads 8–39): pre-clear the corresponding group raw status bit, enable only that bit in the group interrupt-enable register, and wait briefly.", "Arm the interrupt-wait flag, then generate a falling edge on the selected pad by first driving all-high and then clearing only the target bit in the pad driver register.", "Poll the arm flag with a bounded timeout (initial count 5000) and periodic short waits until the interrupt handler indicates service completion or the timeout expires; on timeout, record an error.", "Interrupt handler actions upon entry: clear the wait flag and immediately return the pad driver to the all-high state.", "Read the per-GPIO control/status register for the active pad and confirm that the input data bit indicates low following the falling edge.", "Confirm that the per-pin raw interrupt indication is set, then read the group interrupt status register and verify that the corresponding bit is asserted.", "Clear the per-pin raw status by writing the clear bit while preserving input mode, and clear the group raw status by writing one to the corresponding group clear register.", "Verify that the group status register reads zero after clears, clear the system-level raw interrupt status for the selected instance, and clear the pending interrupt in the interrupt controller."]</t>
+          <t>["Entry point initializes error counters and enables the appropriate CPU interrupt in the interrupt controller for the selected GPIO instance.","Enable the system register output for the selected GPIO instance to route the group interrupt to the CPU.","Drive the external pad driver register to all ones to establish a known-high state on all GPIO inputs.","Configure each per-GPIO control register for pads 8 through 39 to input mode, enable negative-edge detection, and clear any pending per-pin raw status; insert a short wait after each configuration write.","For each GPIO bit from 0 to 31 (corresponding to pads 8–39): pre-clear the corresponding group raw status bit, enable only that bit in the group interrupt-enable register, and wait briefly.","Arm the interrupt-wait flag, then generate a falling edge on the selected pad by first driving all-high and then clearing only the target bit in the pad driver register.","Poll the arm flag with a bounded timeout (initial count 5000) and periodic short waits until the interrupt handler indicates service completion or the timeout expires; on timeout, record an error.","Interrupt handler actions upon entry: clear the wait flag and immediately return the pad driver to the all-high state.","Read the per-GPIO control/status register for the active pad and confirm that the input data bit indicates low following the falling edge.","Confirm that the per-pin raw interrupt indication is set, then read the group interrupt status register and verify that the corresponding bit is asserted.","Clear the per-pin raw status by writing the clear bit while preserving input mode, and clear the group raw status by writing one to the corresponding group clear register.","Verify that the group status register reads zero after clears, clear the system-level raw interrupt status for the selected instance, and clear the pending interrupt in the interrupt controller."]</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -708,7 +701,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>["For each pad tested, the per-pin input data reflects low after the induced falling edge.", "Per-pin raw interrupt indication is set for the active pad and the corresponding group status bit is asserted.", "After issuing per-pin and group clears, the group status register reads zero.", "System-level raw interrupt status for the selected instance is cleared after service, and the interrupt controller is cleared.", "Overall test passes only if no timeouts occur and no verification steps report errors."]</t>
+          <t>["For each pad tested, the per-pin input data reflects low after the induced falling edge.","Per-pin raw interrupt indication is set for the active pad and the corresponding group status bit is asserted.","After issuing per-pin and group clears, the group status register reads zero.","System-level raw interrupt status for the selected instance is cleared after service, and the interrupt controller is cleared.","Overall test passes only if no timeouts occur and no verification steps report errors."]</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -719,7 +712,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>program.c sets up negedge interrupts. In test_case(): optionally GIC_EnableIRQ(87/88); write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR or LSS_SYSREG_INTR_EN1_GPIO1_INTR); write_reg(0xA0243ffc, 0xffffffff); for i=0..31: addr1 = MIZAR_GPIO_GP0_GPIO_8 + (i*4); write_reg(addr1, (1&lt;&lt;20)|(1&lt;&lt;18)|(1&lt;&lt;16)); wait_on(10). For each i: wr_val=1&lt;&lt;i; write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, wr_val); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, wr_val); wait_on(10); int_pend=1; write_reg(0xA0243ffc, 0xffffffff); wait_on(30); write_reg(0xA0243ffc, ~wr_val); timeout=5000; while (int_pend &amp;&amp; timeout--) wait_on(10); if timeout==0 error++. finish(test_err). Default_IRQHandler(): local_wr=1&lt;&lt;i; int_pend=0; write_reg(0xA0243ffc, 0xffffffff); raddr=MIZAR_GPIO_GP0_GPIO_8 + (i*4); rdata=read_reg(raddr); if ((rdata &amp; 0x1)!=0) error++; if ((rdata &amp; 0x2)!=0x0) { rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if ((rdata_grp &amp; local_wr)==0) error++; write_reg(MIZAR_GPIO_GP0_GPIO_8 + (i*4), (1&lt;&lt;20)|(1&lt;&lt;16)); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, local_wr); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if (rdata_grp!=0x0) error++; write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR/1_INTR); GIC_ClearIRQ(87/88); } else error++;</t>
+          <t>program.c sets up negedge interrupts. In test_case(): optionally GIC_EnableIRQ(87/88); write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR or LSS_SYSREG_INTR_EN1_GPIO1_INTR); write_reg(0xA0243ffc, 0xffffffff); for i=0..31: addr1 = MIZAR_GPIO_GP0_GPIO_8 + (i4); write_reg(addr1, (1&lt;&lt;20)|(1&lt;&lt;18)|(1&lt;&lt;16)); wait_on(10). For each i: wr_val=1&lt;&lt;i; write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, wr_val); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, wr_val); wait_on(10); int_pend=1; write_reg(0xA0243ffc, 0xffffffff); wait_on(30); write_reg(0xA0243ffc, ~wr_val); timeout=5000; while (int_pend &amp;&amp; timeout--) wait_on(10); if timeout==0 error++. finish(test_err). Default_IRQHandler(): local_wr=1&lt;&lt;i; int_pend=0; write_reg(0xA0243ffc, 0xffffffff); raddr=MIZAR_GPIO_GP0_GPIO_8 + (i4); rdata=read_reg(raddr); if ((rdata &amp; 0x1)!=0) error++; if ((rdata &amp; 0x2)!=0x0) { rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if ((rdata_grp &amp; local_wr)==0) error++; write_reg(MIZAR_GPIO_GP0_GPIO_8 + (i4), (1&lt;&lt;20)|(1&lt;&lt;16)); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, local_wr); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if (rdata_grp!=0x0) error++; write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR/1_INTR); GIC_ClearIRQ(87/88); } else error++;</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -729,7 +722,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>["int test_case(): test_err=0; #ifdef GPIO0 GIC_EnableIRQ(87) #endif; #ifdef GPIO1 GIC_EnableIRQ(88) #endif;", "#ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR) #endif; #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO1_INTR) #endif;", "write_reg(0xA0243ffc, 0xFFFFFFFF);", "for (i=0;i&lt;32;i++): addr1=MIZAR_GPIO_GP0_GPIO_8 + (i*4); write_reg(addr1, (1&lt;&lt;20)|(1&lt;&lt;18)|(1&lt;&lt;16)); wait_on(10);", "for (i=0;i&lt;32;i++): wr_val=1&lt;&lt;i; write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, wr_val); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, wr_val); wait_on(10); int_pend=1; write_reg(0xA0243ffc, 0xFFFFFFFF); wait_on(30); write_reg(0xA0243ffc, ~wr_val);", "unsigned int timeout=5000; while (int_pend &amp;&amp; timeout--) wait_on(10); if (timeout==0) { printf timeout; test_err++; }", "finish(test_err);", "void Default_IRQHandler(): unsigned int local_wr=1&lt;&lt;i; int_pend=0; write_reg(0xA0243ffc, 0xFFFFFFFF); raddr=MIZAR_GPIO_GP0_GPIO_8 + (i*4); rdata=read_reg(raddr);", "if ((rdata &amp; 0x1)!=0) test_err++;", "if ((rdata &amp; 0x2)!=0x0) { rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if ((rdata_grp &amp; local_wr)==0) test_err++; write_reg(MIZAR_GPIO_GP0_GPIO_8 + (i*4), (1&lt;&lt;20)|(1&lt;&lt;16)); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, local_wr); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if (rdata_grp!=0x0) test_err++; #ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); GIC_ClearIRQ(87); #endif #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO1_INTR); GIC_ClearIRQ(88); #endif } else { test_err++; }"]</t>
+          <t>["int test_case(): test_err=0; #ifdef GPIO0 GIC_EnableIRQ(87) #endif; #ifdef GPIO1 GIC_EnableIRQ(88) #endif;","#ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR) #endif; #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO1_INTR) #endif;","write_reg(0xA0243ffc, 0xFFFFFFFF);","for (i=0;i&lt;32;i++): addr1=MIZAR_GPIO_GP0_GPIO_8 + (i4); write_reg(addr1, (1&lt;&lt;20)|(1&lt;&lt;18)|(1&lt;&lt;16)); wait_on(10);","for (i=0;i&lt;32;i++): wr_val=1&lt;&lt;i; write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, wr_val); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, wr_val); wait_on(10); int_pend=1; write_reg(0xA0243ffc, 0xFFFFFFFF); wait_on(30); write_reg(0xA0243ffc, ~wr_val);","unsigned int timeout=5000; while (int_pend &amp;&amp; timeout--) wait_on(10); if (timeout==0) { printf timeout; test_err++; }","finish(test_err);","void Default_IRQHandler(): unsigned int local_wr=1&lt;&lt;i; int_pend=0; write_reg(0xA0243ffc, 0xFFFFFFFF); raddr=MIZAR_GPIO_GP0_GPIO_8 + (i4); rdata=read_reg(raddr);","if ((rdata &amp; 0x1)!=0) test_err++;","if ((rdata &amp; 0x2)!=0x0) { rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if ((rdata_grp &amp; local_wr)==0) test_err++; write_reg(MIZAR_GPIO_GP0_GPIO_8 + (i4), (1&lt;&lt;20)|(1&lt;&lt;16)); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, local_wr); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if (rdata_grp!=0x0) test_err++; #ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); GIC_ClearIRQ(87); #endif #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO1_INTR); GIC_ClearIRQ(88); #endif } else { test_err++; }"]</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -739,7 +732,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Pass per pin when: after falling edge, (read_reg(MIZAR_GPIO_GP0_GPIO_8 + i*4) &amp; 0x1) == 0; (read_reg(MIZAR_GPIO_GP0_GPIO_8 + i*4) &amp; 0x2) != 0; (read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1) &amp; (1&lt;&lt;i)) != 0; after write_reg(MIZAR_GPIO_GP0_GPIO_8 + i*4, (1&lt;&lt;20)|(1&lt;&lt;16)) and write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, 1&lt;&lt;i), then read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1) == 0. System status cleared via MIZAR_LSS_SYSREG_RAW_STCR1 and GIC cleared. No timeout in while(int_pend &amp;&amp; timeout--) loop.</t>
+          <t>Pass per pin when: after falling edge, (read_reg(MIZAR_GPIO_GP0_GPIO_8 + i4) &amp; 0x1) == 0; (read_reg(MIZAR_GPIO_GP0_GPIO_8 + i4) &amp; 0x2) != 0; (read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1) &amp; (1&lt;&lt;i)) != 0; after write_reg(MIZAR_GPIO_GP0_GPIO_8 + i4, (1&lt;&lt;20)|(1&lt;&lt;16)) and write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, 1&lt;&lt;i), then read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1) == 0. System status cleared via MIZAR_LSS_SYSREG_RAW_STCR1 and GIC cleared. No timeout in while(int_pend &amp;&amp; timeout--) loop.</t>
         </is>
       </c>
     </row>
@@ -794,7 +787,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>["Entry point enables the appropriate CPU interrupt for the selected GPIO instance in the interrupt controller.", "Enable the system register output for the selected GPIO instance to route the group interrupt.", "Configure per-GPIO control registers for pads 8 through 39 to enable positive-edge interrupt detection.", "Set pads 8–39 to input mode using the four group I/O control registers.", "Enable all bits in the group interrupt-enable register.", "For each pad index from 0 to 31: drive the external pad driver low, wait briefly, arm the wait flag, then drive the external pad driver high to generate a single rising edge.", "Poll the wait flag with a bounded timeout (initial count 2000) and periodic short waits to confirm the interrupt was serviced; on timeout, record an error and exit the loop.", "After each iteration, optionally return the pad driver low and wait briefly to prepare for the next edge.", "Interrupt handler actions: clear the wait flag; read the group interrupt status; mask the group enable during service; check that at least one group bit is asserted; clear per-pin raw status across all pads by writing the per-GPIO clear bit in each control register and wait briefly.", "Verify that the group status is zero following the clears; clear the system-level raw status for the selected instance; re-enable the group interrupt and clear the pending interrupt in the interrupt controller."]</t>
+          <t>["Entry point enables the appropriate CPU interrupt for the selected GPIO instance in the interrupt controller.","Enable the system register output for the selected GPIO instance to route the group interrupt.","Configure per-GPIO control registers for pads 8 through 39 to enable positive-edge interrupt detection.","Set pads 8–39 to input mode using the four group I/O control registers.","Enable all bits in the group interrupt-enable register.","For each pad index from 0 to 31: drive the external pad driver low, wait briefly, arm the wait flag, then drive the external pad driver high to generate a single rising edge.","Poll the wait flag with a bounded timeout (initial count 2000) and periodic short waits to confirm the interrupt was serviced; on timeout, record an error and exit the loop.","After each iteration, optionally return the pad driver low and wait briefly to prepare for the next edge.","Interrupt handler actions: clear the wait flag; read the group interrupt status; mask the group enable during service; check that at least one group bit is asserted; clear per-pin raw status across all pads by writing the per-GPIO clear bit in each control register and wait briefly.","Verify that the group status is zero following the clears; clear the system-level raw status for the selected instance; re-enable the group interrupt and clear the pending interrupt in the interrupt controller."]</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -804,7 +797,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>["Per rising transition, the group interrupt status indicates an active bit and is subsequently cleared to zero after per-pin raw clears.", "System-level raw interrupt status for the selected instance is cleared during handler execution and the interrupt controller pending state is cleared.", "Overall test passes only if no timeouts occur and status checks and clears succeed across the tested iterations."]</t>
+          <t>["Per rising transition, the group interrupt status indicates an active bit and is subsequently cleared to zero after per-pin raw clears.","System-level raw interrupt status for the selected instance is cleared during handler execution and the interrupt controller pending state is cleared.","Overall test passes only if no timeouts occur and status checks and clears succeed across the tested iterations."]</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -815,7 +808,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>test_case(): #ifdef GPIO0 GIC_EnableIRQ(87) #endif; #ifdef GPIO1 GIC_EnableIRQ(88) #endif; write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR/1_INTR); for (i=0;i&lt;32;i++) write_reg(MIZAR_GPIO_GP0_GPIO_8 + i*4, 0x00020000); wait_on(10); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,0xFF); ... GROUP4,0xFF; wait_on(10); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF); For i=0..31: write_reg(0xA0243ffc,0x00000000); wait_on(10); int_pend=1; write_reg(0xA0243ffc,0xFFFFFFFF); int timeout=2000; while (int_pend==1 &amp;&amp; --timeout&gt;0) wait_on(10); if (timeout==0) { printf timeout; test_err++; break; } write_reg(0xA0243ffc,0x00000000); wait_on(10); finish(test_err). Default_IRQHandler(): wr_val=1&lt;&lt;i; int_pend=0; rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1,0x00000000); if ((rdata_grp &amp; 0xFFFFFFFF)!=0) pass else { printf error; test_err++; } for (j=0;j&lt;32;j++) write_reg(MIZAR_GPIO_GP0_GPIO_8 + j*4, 0x00010000); wait_on(2); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if (rdata_grp==0) pass else { printf error; test_err++; } #ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if ((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO0_INTR)!=0) test_err++; #endif #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO1_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if ((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO1_INTR)!=0) test_err++; #endif write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF); GIC_ClearIRQ(87/88).</t>
+          <t>test_case(): #ifdef GPIO0 GIC_EnableIRQ(87) #endif; #ifdef GPIO1 GIC_EnableIRQ(88) #endif; write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR/1_INTR); for (i=0;i&lt;32;i++) write_reg(MIZAR_GPIO_GP0_GPIO_8 + i4, 0x00020000); wait_on(10); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,0xFF); ... GROUP4,0xFF; wait_on(10); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF); For i=0..31: write_reg(0xA0243ffc,0x00000000); wait_on(10); int_pend=1; write_reg(0xA0243ffc,0xFFFFFFFF); int timeout=2000; while (int_pend==1 &amp;&amp; --timeout&gt;0) wait_on(10); if (timeout==0) { printf timeout; test_err++; break; } write_reg(0xA0243ffc,0x00000000); wait_on(10); finish(test_err). Default_IRQHandler(): wr_val=1&lt;&lt;i; int_pend=0; rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1,0x00000000); if ((rdata_grp &amp; 0xFFFFFFFF)!=0) pass else { printf error; test_err++; } for (j=0;j&lt;32;j++) write_reg(MIZAR_GPIO_GP0_GPIO_8 + j4, 0x00010000); wait_on(2); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if (rdata_grp==0) pass else { printf error; test_err++; } #ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if ((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO0_INTR)!=0) test_err++; #endif #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO1_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if ((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO1_INTR)!=0) test_err++; #endif write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF); GIC_ClearIRQ(87/88).</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -825,7 +818,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>["void test_case(): #ifdef GPIO0 GIC_EnableIRQ(87) #endif; #ifdef GPIO1 GIC_EnableIRQ(88) #endif; unsigned int rdata, wr_val; test_err=0;", "#ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR) #endif; #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO1_INTR) #endif;", "for (i=0;i&lt;32;i++) write_reg(MIZAR_GPIO_GP0_GPIO_8 + (i*4), 0x00020000);", "wait_on(10); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP2,0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP3,0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP4,0x000000FF);", "wait_on(10); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF);", "for (i=0;i&lt;32;i++): write_reg(0xA0243ffc,0x00000000); wait_on(10); int_pend=1; write_reg(0xA0243ffc,0xFFFFFFFF); int timeout=2000; while ((int_pend==1) &amp;&amp; (--timeout&gt;0)) wait_on(10); if (timeout==0) { printf timeout; test_err++; break; } write_reg(0xA0243ffc,0x00000000); wait_on(10); finish(test_err);", "void Default_IRQHandler(): wr_val=1&lt;&lt;i; int_pend=0; rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1,0x00000000); if ((rdata_grp &amp; 0xFFFFFFFF)!=0) { /* success */ } else { printf error; test_err++; } for (j=0;j&lt;32;j++) write_reg(MIZAR_GPIO_GP0_GPIO_8 + (j*4), 0x00010000); wait_on(2); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if (rdata_grp==0) { /* cleared */ } else { printf error; test_err++; } #ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if ((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO0_INTR)!=0) test_err++; #endif #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO1_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if ((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO1_INTR)!=0) test_err++; #endif write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1,0xFFFFFFFF); #ifdef GPIO0 GIC_ClearIRQ(87) #endif #ifdef GPIO1 GIC_ClearIRQ(88) #endif"]</t>
+          <t>["void test_case(): #ifdef GPIO0 GIC_EnableIRQ(87) #endif; #ifdef GPIO1 GIC_EnableIRQ(88) #endif; unsigned int rdata, wr_val; test_err=0;","#ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR) #endif; #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO1_INTR) #endif;","for (i=0;i&lt;32;i++) write_reg(MIZAR_GPIO_GP0_GPIO_8 + (i4), 0x00020000);","wait_on(10); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP2,0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP3,0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP4,0x000000FF);","wait_on(10); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF);","for (i=0;i&lt;32;i++): write_reg(0xA0243ffc,0x00000000); wait_on(10); int_pend=1; write_reg(0xA0243ffc,0xFFFFFFFF); int timeout=2000; while ((int_pend==1) &amp;&amp; (--timeout&gt;0)) wait_on(10); if (timeout==0) { printf timeout; test_err++; break; } write_reg(0xA0243ffc,0x00000000); wait_on(10); finish(test_err);","void Default_IRQHandler(): wr_val=1&lt;&lt;i; int_pend=0; rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1,0x00000000); if ((rdata_grp &amp; 0xFFFFFFFF)!=0) { /* success / } else { printf error; test_err++; } for (j=0;j&lt;32;j++) write_reg(MIZAR_GPIO_GP0_GPIO_8 + (j4), 0x00010000); wait_on(2); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if (rdata_grp==0) { /* cleared / } else { printf error; test_err++; } #ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if ((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO0_INTR)!=0) test_err++; #endif #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO1_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if ((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO1_INTR)!=0) test_err++; #endif write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1,0xFFFFFFFF); #ifdef GPIO0 GIC_ClearIRQ(87) #endif #ifdef GPIO1 GIC_ClearIRQ(88) #endif"]</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -835,530 +828,295 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Handler sees non-zero read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); after for(j=0..31) write_reg(MIZAR_GPIO_GP0_GPIO_8 + j*4, 0x00010000) and wait_on(2), then read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1)==0; #ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); subsequent read_reg(MIZAR_LSS_SYSREG_RAW_STCR1) &amp; LSS_SYSREG_RAW_STCR1_GPIO0_INTR == 0. Same check for GPIO1 if defined. No timeout while (int_pend==1 &amp;&amp; --timeout&gt;0).</t>
+          <t>Handler sees non-zero read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); after for(j=0..31) write_reg(MIZAR_GPIO_GP0_GPIO_8 + j4, 0x00010000) and wait_on(2), then read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1)==0; #ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); subsequent read_reg(MIZAR_LSS_SYSREG_RAW_STCR1) &amp; LSS_SYSREG_RAW_STCR1_GPIO0_INTR == 0. Same check for GPIO1 if defined. No timeout while (int_pend==1 &amp;&amp; --timeout&gt;0).</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:R4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="82" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="82" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="82" customWidth="1" min="10" max="10"/>
-    <col width="82" customWidth="1" min="11" max="11"/>
-    <col width="82" customWidth="1" min="12" max="12"/>
-    <col width="82" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Index</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Test Case Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Test Description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Mode</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Memory Start Offset</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Memory End Offset</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Impacted Registers</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Validation Criteria</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Parameters</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Dependencies</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Requirements</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Tags</t>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GPIO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Independent control register for each GPIO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>gpio_reg_wr_rd_test</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Verify that per-GPIO control and group registers power-on default values match the specification and that masked write/read operations behave correctly across the defined GPIO register set.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Certain registers are intentionally skipped: VRRW-type and those marked non-readable/non-writable; default-read masks clear bit0; known caveat noted for DIN behavior affecting default reads.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>["Entry point begins the test and first performs a default reset-value verification over the configured list of GPIO-related registers.","Iterate through the configured register list; for any entry flagged to skip default checking, continue without accessing the register.","For entries not skipped and marked as readable, read the register and apply a mask that clears bit 0, then compare the result to the documented default value for that register.","Record a failure if any masked default-value comparison does not match the expected default.","Proceed to masked write/read verification using a fixed sequence of six data patterns applied to the same configured register list.","For each data pattern, iterate over the register list: if an entry is flagged to skip or has a zero write mask, do not write; otherwise, write the data pattern masked by the register’s write mask.","After completing writes for the current pattern, iterate again over the register list: skip entries with zero write or zero read masks; for others, read the register value and mask it with the register’s read mask.","For each read, compute the expected value as: (written_data AND read_mask AND write_mask) OR ((bitwise NOT of write_mask) AND read_mask AND the register’s default value).","Compare the masked read value with the computed expected value and record a failure on any mismatch.","Conclude the test and report pass if no default-value or write/read mismatches were recorded; otherwise report fail."]</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>GPIO_GP0_GPIO_8,GPIO_GP0_GPIO_9,GPIO_GP0_GPIO_10,GPIO_GP0_GPIO_11,GPIO_GP0_GPIO_12,GPIO_GP0_GPIO_13,GPIO_GP0_GPIO_14,GPIO_GP0_GPIO_15,GPIO_GP0_GPIO_16,GPIO_GP0_GPIO_17,GPIO_GP0_GPIO_18,GPIO_GP0_GPIO_19,GPIO_GP0_GPIO_20,GPIO_GP0_GPIO_21,GPIO_GP0_GPIO_22,GPIO_GP0_GPIO_23,GPIO_GP0_GPIO_24,GPIO_GP0_GPIO_25,GPIO_GP0_GPIO_26,GPIO_GP0_GPIO_27,GPIO_GP0_GPIO_28,GPIO_GP0_GPIO_29,GPIO_GP0_GPIO_30,GPIO_GP0_GPIO_31,GPIO_GP0_GPIO_32,GPIO_GP0_GPIO_33,GPIO_GP0_GPIO_34,GPIO_GP0_GPIO_35,GPIO_GP0_GPIO_36,GPIO_GP0_GPIO_37,GPIO_GP0_GPIO_38,GPIO_GP0_GPIO_39,GPIO_GPIO_INTR_RAW_STCLR1,GPIO_GP0_INTR1_INTR_EN1,GPIO_GP0_INTR1_INTR_STS1,GPIO_GP0_INTR2_INTR_EN1,GPIO_GP0_INTR2_INTR_STS1,GPIO_GPIO_IO_CTRL_GROUP1,GPIO_GPIO_IO_CTRL_GROUP2,GPIO_GPIO_IO_CTRL_GROUP3,GPIO_GPIO_IO_CTRL_GROUP4,GPIO_GPIO_DOUT_GROUP1,GPIO_GPIO_DOUT_GROUP2,GPIO_GPIO_DOUT_GROUP3,GPIO_GPIO_DOUT_GROUP4,GPIO_GPIO_DIN_GROUP1,GPIO_GPIO_DIN_GROUP2,GPIO_GPIO_DIN_GROUP3,GPIO_GPIO_DIN_GROUP4</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>["Default reset-value check passes only if, for every non-skipped readable register, (read_value AND 0xFFFFFFFE) equals the documented default value.","Write/read check passes only if, for every non-skipped entry and for each test pattern, the masked read value equals: (written_data AND read_mask AND write_mask) OR ((bitwise NOT of write_mask) AND read_mask AND default_value).","Overall test status is PASS when no default or write/read mismatches are recorded; otherwise FAIL."]</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>gpio_reg_wr_rd_test</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>program.c invokes chk_rst_val() then chk_rd_wr(), and finishes with pass/fail based on def_fail_cnt and wr_fail_cnt. chk_rst_val() loops i=0..CNT-1 using addr=addr_array[i] (macros like MIZAR_GPIO_GP0_GPIO_8..GPIO_39, group regs, intr regs). It skips entries where skip_rst_array[i]==1 or read_mask_array[i]==0, reads via read_reg(addr), masks data_rd with 0xFFFFFFFE, and compares to default_value_array[i]. chk_rd_wr() tries six patterns (0xFFFFFFFF,0xAAAAAAAA,0x55555555,0xF5F5F5F5,0xA5A5A5A5,0xFFFF0000). For each i: if skip_array[i]==1 or write_mask_array[i]==0, it skips; else it write_reg(addr,(data_wr &amp; write_mask_array[i])). Then it reads back masked by read_mask_array[i], computes wr_n=(write_mask_array[i]^0xFFFFFFFF), and expected=((data_wr &amp; read_mask_array[i] &amp; write_mask_array[i]) | (wr_n &amp; read_mask_array[i] &amp; default_value_array[i])). Mismatch increments wr_fail_cnt. finish(1) if any failures, else finish(0).</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>test_define.c: //80,94,98,9c,a0,a4,a8,ac,b0...SKIPPING VRRW registers. skip_array[] and skip_rst_array[] specify which registers to skip. Comment: when reading default values the din value is becoming 1 automatically if we don't force any value, but if we force zero to din bit level sel becoming high, so that reading value not matched with expected value.</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>["int test_case(): calls chk_rst_val(); calls chk_rd_wr(); if (def_fail_cnt &gt; 0 || wr_fail_cnt &gt; 0) finish(1); else finish(0).","void chk_rst_val(): for (i=0;i&lt;CNT;i++): addr=addr_array[i] (e.g., MIZAR_GPIO_GP0_GPIO_8..MIZAR_GPIO_GP0_GPIO_39, MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, MIZAR_GPIO_GP0_INTRx_xxx, GPIO_IO_CTRL_GROUPx, GPIO_DOUT_GROUPx, GPIO_DIN_GROUPx); if (skip_rst_array[i]==1) continue; if (read_mask_array[i]==0) continue; data_rd=read_reg(addr); data=(data_rd &amp; 0xFFFFFFFE); if (data==default_value_array[i]) pass; else { def_fail_cnt++; printf failure }. No waits/timeouts.","void chk_rd_wr(): unsigned chk_val[6]={0xFFFFFFFF,0xAAAAAAAA,0x55555555,0xF5F5F5F5,0xA5A5A5A5,0xFFFF0000}; For each pattern j: data_wr=chk_val[j]; Write phase: for (i=0;i&lt;CNT;i++): addr=addr_array[i]; if (skip_array[i]==1) continue; if (write_mask_array[i]==0) continue; else write_reg(addr,(data_wr &amp; write_mask_array[i])). Read/verify phase: for (i=0;i&lt;CNT;i++): addr=addr_array[i]; if (skip_array[i]==1) continue; if (write_mask_array[i]==0) continue; if (read_mask_array[i]==0) continue; data_rd=(read_reg(addr) &amp; read_mask_array[i]); wr_n=(write_mask_array[i] ^ 0xFFFFFFFF); exp_val=((data_wr &amp; read_mask_array[i] &amp; write_mask_array[i]) | (wr_n &amp; read_mask_array[i] &amp; default_value_array[i])); if (data_rd==exp_val) pass; else { wr_fail_cnt++; printf failure }."]</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>MIZAR_GPIO_GP0_GPIO_8,MIZAR_GPIO_GP0_GPIO_9,MIZAR_GPIO_GP0_GPIO_10,MIZAR_GPIO_GP0_GPIO_11,MIZAR_GPIO_GP0_GPIO_12,MIZAR_GPIO_GP0_GPIO_13,MIZAR_GPIO_GP0_GPIO_14,MIZAR_GPIO_GP0_GPIO_15,MIZAR_GPIO_GP0_GPIO_16,MIZAR_GPIO_GP0_GPIO_17,MIZAR_GPIO_GP0_GPIO_18,MIZAR_GPIO_GP0_GPIO_19,MIZAR_GPIO_GP0_GPIO_20,MIZAR_GPIO_GP0_GPIO_21,MIZAR_GPIO_GP0_GPIO_22,MIZAR_GPIO_GP0_GPIO_23,MIZAR_GPIO_GP0_GPIO_24,MIZAR_GPIO_GP0_GPIO_25,MIZAR_GPIO_GP0_GPIO_26,MIZAR_GPIO_GP0_GPIO_27,MIZAR_GPIO_GP0_GPIO_28,MIZAR_GPIO_GP0_GPIO_29,MIZAR_GPIO_GP0_GPIO_30,MIZAR_GPIO_GP0_GPIO_31,MIZAR_GPIO_GP0_GPIO_32,MIZAR_GPIO_GP0_GPIO_33,MIZAR_GPIO_GP0_GPIO_34,MIZAR_GPIO_GP0_GPIO_35,MIZAR_GPIO_GP0_GPIO_36,MIZAR_GPIO_GP0_GPIO_37,MIZAR_GPIO_GP0_GPIO_38,MIZAR_GPIO_GP0_GPIO_39,MIZAR_GPIO_GPIO_INTR_RAW_STCLR1,MIZAR_GPIO_GP0_INTR1_INTR_EN1,MIZAR_GPIO_GP0_INTR1_INTR_STS1,MIZAR_GPIO_GP0_INTR2_INTR_EN1,MIZAR_GPIO_GP0_INTR2_INTR_STS1,MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,MIZAR_GPIO_GPIO_IO_CTRL_GROUP2,MIZAR_GPIO_GPIO_IO_CTRL_GROUP3,MIZAR_GPIO_GPIO_IO_CTRL_GROUP4,MIZAR_GPIO_GPIO_DOUT_GROUP1,MIZAR_GPIO_GPIO_DOUT_GROUP2,MIZAR_GPIO_GPIO_DOUT_GROUP3,MIZAR_GPIO_GPIO_DOUT_GROUP4,MIZAR_GPIO_GPIO_DIN_GROUP1,MIZAR_GPIO_GPIO_DIN_GROUP2,MIZAR_GPIO_GPIO_DIN_GROUP3,MIZAR_GPIO_GPIO_DIN_GROUP4</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Default pass criterion: for all i where skip_rst_array[i]==0 and read_mask_array[i]!=0, (read_reg(addr_array[i]) &amp; 0xFFFFFFFE) == default_value_array[i]. Write/read pass criterion: for all i where skip_array[i]==0, write_mask_array[i]!=0, read_mask_array[i]!=0, and for each j in 0..5, (read_reg(addr_array[i]) &amp; read_mask_array[i]) == ((chk_val[j] &amp; read_mask_array[i] &amp; write_mask_array[i]) | ((write_mask_array[i]^0xFFFFFFFF) &amp; read_mask_array[i] &amp; default_value_array[i])). Overall finish(0) indicates PASS.</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>gpio_reg_wr_rd_test</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Verify that per-GPIO control and group registers power-on default values match the specification and that masked write/read operations behave correctly across the defined GPIO register set.</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>GPIO</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Independent control register for each GPIO</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Interrupts can be generated based on positive edge or negative edge or level high or level low detection at GPIO input</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>test_gpio_negedge_intr_en</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Validate that each GPIO input (pads 8–39) can generate a falling-edge interrupt, that per-pin and group status latch correctly, and that both per-pin and group status can be cleared while the system interrupt path propagates and is serviced.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Interrupt</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0xA0243ffc</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0xA0243ffc</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Interrupt wait uses a bounded polling loop with timeout; edge generation is ordered to arm the wait before toggling to avoid race; pad driver is returned to a known all-high state inside the handler before status checks.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>["Entry point initializes error counters and enables the appropriate CPU interrupt in the interrupt controller for the selected GPIO instance.","Enable the system register output for the selected GPIO instance to route the group interrupt to the CPU.","Drive the external pad driver register to all ones to establish a known-high state on all GPIO inputs.","Configure each per-GPIO control register for pads 8 through 39 to input mode, enable negative-edge detection, and clear any pending per-pin raw status; insert a short wait after each configuration write.","For each GPIO bit from 0 to 31 (corresponding to pads 8–39): pre-clear the corresponding group raw status bit, enable only that bit in the group interrupt-enable register, and wait briefly.","Arm the interrupt-wait flag, then generate a falling edge on the selected pad by first driving all-high and then clearing only the target bit in the pad driver register.","Poll the arm flag with a bounded timeout (initial count 5000) and periodic short waits until the interrupt handler indicates service completion or the timeout expires; on timeout, record an error.","Interrupt handler actions upon entry: clear the wait flag and immediately return the pad driver to the all-high state.","Read the per-GPIO control/status register for the active pad and confirm that the input data bit indicates low following the falling edge.","Confirm that the per-pin raw interrupt indication is set, then read the group interrupt status register and verify that the corresponding bit is asserted.","Clear the per-pin raw status by writing the clear bit while preserving input mode, and clear the group raw status by writing one to the corresponding group clear register.","Verify that the group status register reads zero after clears, clear the system-level raw interrupt status for the selected instance, and clear the pending interrupt in the interrupt controller."]</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>INTR_EN1,RAW_STCR1,GPIO_GP0_GPIO_8,GPIO_GP0_GPIO_9,GPIO_GP0_GPIO_10,GPIO_GP0_GPIO_11,GPIO_GP0_GPIO_12,GPIO_GP0_GPIO_13,GPIO_GP0_GPIO_14,GPIO_GP0_GPIO_15,GPIO_GP0_GPIO_16,GPIO_GP0_GPIO_17,GPIO_GP0_GPIO_18,GPIO_GP0_GPIO_19,GPIO_GP0_GPIO_20,GPIO_GP0_GPIO_21,GPIO_GP0_GPIO_22,GPIO_GP0_GPIO_23,GPIO_GP0_GPIO_24,GPIO_GP0_GPIO_25,GPIO_GP0_GPIO_26,GPIO_GP0_GPIO_27,GPIO_GP0_GPIO_28,GPIO_GP0_GPIO_29,GPIO_GP0_GPIO_30,GPIO_GP0_GPIO_31,GPIO_GP0_GPIO_32,GPIO_GP0_GPIO_33,GPIO_GP0_GPIO_34,GPIO_GP0_GPIO_35,GPIO_GP0_GPIO_36,GPIO_GP0_GPIO_37,GPIO_GP0_GPIO_38,GPIO_GP0_GPIO_39,GPIO_GP0_INTR1_INTR_EN1,GPIO_GP0_INTR1_INTR_STS1,GPIO_GPIO_INTR_RAW_STCLR1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>["For each pad tested, the per-pin input data reflects low after the induced falling edge.","Per-pin raw interrupt indication is set for the active pad and the corresponding group status bit is asserted.","After issuing per-pin and group clears, the group status register reads zero.","System-level raw interrupt status for the selected instance is cleared after service, and the interrupt controller is cleared.","Overall test passes only if no timeouts occur and no verification steps report errors."]</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>test_gpio_negedge_intr_en</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>program.c sets up negedge interrupts. In test_case(): optionally GIC_EnableIRQ(87/88); write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR or LSS_SYSREG_INTR_EN1_GPIO1_INTR); write_reg(0xA0243ffc, 0xffffffff); for i=0..31: addr1 = MIZAR_GPIO_GP0_GPIO_8 + (i4); write_reg(addr1, (1&lt;&lt;20)|(1&lt;&lt;18)|(1&lt;&lt;16)); wait_on(10). For each i: wr_val=1&lt;&lt;i; write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, wr_val); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, wr_val); wait_on(10); int_pend=1; write_reg(0xA0243ffc, 0xffffffff); wait_on(30); write_reg(0xA0243ffc, ~wr_val); timeout=5000; while (int_pend &amp;&amp; timeout--) wait_on(10); if timeout==0 error++. finish(test_err). Default_IRQHandler(): local_wr=1&lt;&lt;i; int_pend=0; write_reg(0xA0243ffc, 0xffffffff); raddr=MIZAR_GPIO_GP0_GPIO_8 + (i4); rdata=read_reg(raddr); if ((rdata &amp; 0x1)!=0) error++; if ((rdata &amp; 0x2)!=0x0) { rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if ((rdata_grp &amp; local_wr)==0) error++; write_reg(MIZAR_GPIO_GP0_GPIO_8 + (i4), (1&lt;&lt;20)|(1&lt;&lt;16)); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, local_wr); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if (rdata_grp!=0x0) error++; write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR/1_INTR); GIC_ClearIRQ(87/88); } else error++;</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Wait-before-edge arming to avoid race: comment indicates arming int_pend before generating the edge. Uses bounded wait: timeout=5000 with wait_on(10) per loop. Pad driver (0xA0243ffc) set to known state inside ISR.</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>["int test_case(): test_err=0; #ifdef GPIO0 GIC_EnableIRQ(87) #endif; #ifdef GPIO1 GIC_EnableIRQ(88) #endif;","#ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR) #endif; #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO1_INTR) #endif;","write_reg(0xA0243ffc, 0xFFFFFFFF);","for (i=0;i&lt;32;i++): addr1=MIZAR_GPIO_GP0_GPIO_8 + (i4); write_reg(addr1, (1&lt;&lt;20)|(1&lt;&lt;18)|(1&lt;&lt;16)); wait_on(10);","for (i=0;i&lt;32;i++): wr_val=1&lt;&lt;i; write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, wr_val); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, wr_val); wait_on(10); int_pend=1; write_reg(0xA0243ffc, 0xFFFFFFFF); wait_on(30); write_reg(0xA0243ffc, ~wr_val);","unsigned int timeout=5000; while (int_pend &amp;&amp; timeout--) wait_on(10); if (timeout==0) { printf timeout; test_err++; }","finish(test_err);","void Default_IRQHandler(): unsigned int local_wr=1&lt;&lt;i; int_pend=0; write_reg(0xA0243ffc, 0xFFFFFFFF); raddr=MIZAR_GPIO_GP0_GPIO_8 + (i4); rdata=read_reg(raddr);","if ((rdata &amp; 0x1)!=0) test_err++;","if ((rdata &amp; 0x2)!=0x0) { rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if ((rdata_grp &amp; local_wr)==0) test_err++; write_reg(MIZAR_GPIO_GP0_GPIO_8 + (i4), (1&lt;&lt;20)|(1&lt;&lt;16)); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, local_wr); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if (rdata_grp!=0x0) test_err++; #ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); GIC_ClearIRQ(87); #endif #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO1_INTR); GIC_ClearIRQ(88); #endif } else { test_err++; }"]</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>MIZAR_LSS_SYSREG_INTR_EN1,MIZAR_LSS_SYSREG_RAW_STCR1,MIZAR_GPIO_GP0_GPIO_8,MIZAR_GPIO_GP0_GPIO_9,MIZAR_GPIO_GP0_GPIO_10,MIZAR_GPIO_GP0_GPIO_11,MIZAR_GPIO_GP0_GPIO_12,MIZAR_GPIO_GP0_GPIO_13,MIZAR_GPIO_GP0_GPIO_14,MIZAR_GPIO_GP0_GPIO_15,MIZAR_GPIO_GP0_GPIO_16,MIZAR_GPIO_GP0_GPIO_17,MIZAR_GPIO_GP0_GPIO_18,MIZAR_GPIO_GP0_GPIO_19,MIZAR_GPIO_GP0_GPIO_20,MIZAR_GPIO_GP0_GPIO_21,MIZAR_GPIO_GP0_GPIO_22,MIZAR_GPIO_GP0_GPIO_23,MIZAR_GPIO_GP0_GPIO_24,MIZAR_GPIO_GP0_GPIO_25,MIZAR_GPIO_GP0_GPIO_26,MIZAR_GPIO_GP0_GPIO_27,MIZAR_GPIO_GP0_GPIO_28,MIZAR_GPIO_GP0_GPIO_29,MIZAR_GPIO_GP0_GPIO_30,MIZAR_GPIO_GP0_GPIO_31,MIZAR_GPIO_GP0_GPIO_32,MIZAR_GPIO_GP0_GPIO_33,MIZAR_GPIO_GP0_GPIO_34,MIZAR_GPIO_GP0_GPIO_35,MIZAR_GPIO_GP0_GPIO_36,MIZAR_GPIO_GP0_GPIO_37,MIZAR_GPIO_GP0_GPIO_38,MIZAR_GPIO_GP0_GPIO_39,MIZAR_GPIO_GP0_INTR1_INTR_EN1,MIZAR_GPIO_GP0_INTR1_INTR_STS1,MIZAR_GPIO_GPIO_INTR_RAW_STCLR1</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Pass per pin when: after falling edge, (read_reg(MIZAR_GPIO_GP0_GPIO_8 + i4) &amp; 0x1) == 0; (read_reg(MIZAR_GPIO_GP0_GPIO_8 + i4) &amp; 0x2) != 0; (read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1) &amp; (1&lt;&lt;i)) != 0; after write_reg(MIZAR_GPIO_GP0_GPIO_8 + i4, (1&lt;&lt;20)|(1&lt;&lt;16)) and write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, 1&lt;&lt;i), then read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1) == 0. System status cleared via MIZAR_LSS_SYSREG_RAW_STCR1 and GIC cleared. No timeout in while(int_pend &amp;&amp; timeout--) loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GPIO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Interrupts can be generated based on positive edge or negative edge or level high or level low detection at GPIO input</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>test_gpio_pedge_all_pads_en</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Validate that enabling positive-edge detection on all GPIO inputs (pads 8–39) produces an interrupt per rising transition, that group status asserts and can be cleared for all pads, and that the system interrupt path is properly cleared and re-enabled between events.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Certain registers are intentionally skipped: VRRW-type and those marked non-readable/non-writable; default-read masks clear bit0; known caveat noted for DIN behavior affecting default reads.</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>1. Entry point begins the test and first performs a default reset-value verification over the configured list of GPIO-related registers.
-2. Iterate through the configured register list; for any entry flagged to skip default checking, continue without accessing the register.
-3. For entries not skipped and marked as readable, read the register and apply a mask that clears bit 0, then compare the result to the documented default value for that register.
-4. Record a failure if any masked default-value comparison does not match the expected default.
-5. Proceed to masked write/read verification using a fixed sequence of six data patterns applied to the same configured register list.
-6. For each data pattern, iterate over the register list: if an entry is flagged to skip or has a zero write mask, do not write; otherwise, write the data pattern masked by the register’s write mask.
-7. After completing writes for the current pattern, iterate again over the register list: skip entries with zero write or zero read masks; for others, read the register value and mask it with the register’s read mask.
-8. For each read, compute the expected value as: (written_data AND read_mask AND write_mask) OR ((bitwise NOT of write_mask) AND read_mask AND the register’s default value).
-9. Compare the masked read value with the computed expected value and record a failure on any mismatch.
-10. Conclude the test and report pass if no default-value or write/read mismatches were recorded; otherwise report fail.</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>MIZAR_GPIO_GP0_GPIO_8,MIZAR_GPIO_GP0_GPIO_9,MIZAR_GPIO_GP0_GPIO_10,MIZAR_GPIO_GP0_GPIO_11,MIZAR_GPIO_GP0_GPIO_12,MIZAR_GPIO_GP0_GPIO_13,MIZAR_GPIO_GP0_GPIO_14,MIZAR_GPIO_GP0_GPIO_15,MIZAR_GPIO_GP0_GPIO_16,MIZAR_GPIO_GP0_GPIO_17,MIZAR_GPIO_GP0_GPIO_18,MIZAR_GPIO_GP0_GPIO_19,MIZAR_GPIO_GP0_GPIO_20,MIZAR_GPIO_GP0_GPIO_21,MIZAR_GPIO_GP0_GPIO_22,MIZAR_GPIO_GP0_GPIO_23,MIZAR_GPIO_GP0_GPIO_24,MIZAR_GPIO_GP0_GPIO_25,MIZAR_GPIO_GP0_GPIO_26,MIZAR_GPIO_GP0_GPIO_27,MIZAR_GPIO_GP0_GPIO_28,MIZAR_GPIO_GP0_GPIO_29,MIZAR_GPIO_GP0_GPIO_30,MIZAR_GPIO_GP0_GPIO_31,MIZAR_GPIO_GP0_GPIO_32,MIZAR_GPIO_GP0_GPIO_33,MIZAR_GPIO_GP0_GPIO_34,MIZAR_GPIO_GP0_GPIO_35,MIZAR_GPIO_GP0_GPIO_36,MIZAR_GPIO_GP0_GPIO_37,MIZAR_GPIO_GP0_GPIO_38,MIZAR_GPIO_GP0_GPIO_39,MIZAR_GPIO_GPIO_INTR_RAW_STCLR1,MIZAR_GPIO_GP0_INTR1_INTR_EN1,MIZAR_GPIO_GP0_INTR1_INTR_STS1,MIZAR_GPIO_GP0_INTR2_INTR_EN1,MIZAR_GPIO_GP0_INTR2_INTR_STS1,MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,MIZAR_GPIO_GPIO_IO_CTRL_GROUP2,MIZAR_GPIO_GPIO_IO_CTRL_GROUP3,MIZAR_GPIO_GPIO_IO_CTRL_GROUP4,MIZAR_GPIO_GPIO_DOUT_GROUP1,MIZAR_GPIO_GPIO_DOUT_GROUP2,MIZAR_GPIO_GPIO_DOUT_GROUP3,MIZAR_GPIO_GPIO_DOUT_GROUP4,MIZAR_GPIO_GPIO_DIN_GROUP1,MIZAR_GPIO_GPIO_DIN_GROUP2,MIZAR_GPIO_GPIO_DIN_GROUP3,MIZAR_GPIO_GPIO_DIN_GROUP4</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>1. Default reset-value check passes only if, for every non-skipped readable register, (read_value AND 0xFFFFFFFE) equals the documented default value.
-2. Write/read check passes only if, for every non-skipped entry and for each test pattern, the masked read value equals: (written_data AND read_mask AND write_mask) OR ((bitwise NOT of write_mask) AND read_mask AND default_value).
-3. Overall test status is PASS when no default or write/read mismatches are recorded; otherwise FAIL.</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>test_gpio_negedge_intr_en</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Validate that each GPIO input (pads 8–39) can generate a falling-edge interrupt, that per-pin and group status latch correctly, and that both per-pin and group status can be cleared while the system interrupt path propagates and is serviced.</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>GPIO</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Interrupts can be generated based on positive edge or negative edge or level high or level low detection at GPIO input</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Interrupt</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>0xA0243ffc</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>0xA0243ffc</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Interrupt wait uses a bounded polling loop with timeout; edge generation is ordered to arm the wait before toggling to avoid race; pad driver is returned to a known all-high state inside the handler before status checks.</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>1. Entry point initializes error counters and enables the appropriate CPU interrupt in the interrupt controller for the selected GPIO instance.
-2. Enable the system register output for the selected GPIO instance to route the group interrupt to the CPU.
-3. Drive the external pad driver register to all ones to establish a known-high state on all GPIO inputs.
-4. Configure each per-GPIO control register for pads 8 through 39 to input mode, enable negative-edge detection, and clear any pending per-pin raw status; insert a short wait after each configuration write.
-5. For each GPIO bit from 0 to 31 (corresponding to pads 8–39): pre-clear the corresponding group raw status bit, enable only that bit in the group interrupt-enable register, and wait briefly.
-6. Arm the interrupt-wait flag, then generate a falling edge on the selected pad by first driving all-high and then clearing only the target bit in the pad driver register.
-7. Poll the arm flag with a bounded timeout (initial count 5000) and periodic short waits until the interrupt handler indicates service completion or the timeout expires; on timeout, record an error.
-8. Interrupt handler actions upon entry: clear the wait flag and immediately return the pad driver to the all-high state.
-9. Read the per-GPIO control/status register for the active pad and confirm that the input data bit indicates low following the falling edge.
-10. Confirm that the per-pin raw interrupt indication is set, then read the group interrupt status register and verify that the corresponding bit is asserted.
-11. Clear the per-pin raw status by writing the clear bit while preserving input mode, and clear the group raw status by writing one to the corresponding group clear register.
-12. Verify that the group status register reads zero after clears, clear the system-level raw interrupt status for the selected instance, and clear the pending interrupt in the interrupt controller.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>MIZAR_LSS_SYSREG_INTR_EN1,MIZAR_LSS_SYSREG_RAW_STCR1,MIZAR_GPIO_GP0_GPIO_8,MIZAR_GPIO_GP0_GPIO_9,MIZAR_GPIO_GP0_GPIO_10,MIZAR_GPIO_GP0_GPIO_11,MIZAR_GPIO_GP0_GPIO_12,MIZAR_GPIO_GP0_GPIO_13,MIZAR_GPIO_GP0_GPIO_14,MIZAR_GPIO_GP0_GPIO_15,MIZAR_GPIO_GP0_GPIO_16,MIZAR_GPIO_GP0_GPIO_17,MIZAR_GPIO_GP0_GPIO_18,MIZAR_GPIO_GP0_GPIO_19,MIZAR_GPIO_GP0_GPIO_20,MIZAR_GPIO_GP0_GPIO_21,MIZAR_GPIO_GP0_GPIO_22,MIZAR_GPIO_GP0_GPIO_23,MIZAR_GPIO_GP0_GPIO_24,MIZAR_GPIO_GP0_GPIO_25,MIZAR_GPIO_GP0_GPIO_26,MIZAR_GPIO_GP0_GPIO_27,MIZAR_GPIO_GP0_GPIO_28,MIZAR_GPIO_GP0_GPIO_29,MIZAR_GPIO_GP0_GPIO_30,MIZAR_GPIO_GP0_GPIO_31,MIZAR_GPIO_GP0_GPIO_32,MIZAR_GPIO_GP0_GPIO_33,MIZAR_GPIO_GP0_GPIO_34,MIZAR_GPIO_GP0_GPIO_35,MIZAR_GPIO_GP0_GPIO_36,MIZAR_GPIO_GP0_GPIO_37,MIZAR_GPIO_GP0_GPIO_38,MIZAR_GPIO_GP0_GPIO_39,MIZAR_GPIO_GP0_INTR1_INTR_EN1,MIZAR_GPIO_GP0_INTR1_INTR_STS1,MIZAR_GPIO_GPIO_INTR_RAW_STCLR1</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>1. For each pad tested, the per-pin input data reflects low after the induced falling edge.
-2. Per-pin raw interrupt indication is set for the active pad and the corresponding group status bit is asserted.
-3. After issuing per-pin and group clears, the group status register reads zero.
-4. System-level raw interrupt status for the selected instance is cleared after service, and the interrupt controller is cleared.
-5. Overall test passes only if no timeouts occur and no verification steps report errors.</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Group interrupt is masked during service and re-enabled afterward; the wait loop for the handler is bounded by a timeout; input mode for pads is configured via group I/O control registers to ensure edge detection.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>["Entry point enables the appropriate CPU interrupt for the selected GPIO instance in the interrupt controller.","Enable the system register output for the selected GPIO instance to route the group interrupt.","Configure per-GPIO control registers for pads 8 through 39 to enable positive-edge interrupt detection.","Set pads 8–39 to input mode using the four group I/O control registers.","Enable all bits in the group interrupt-enable register.","For each pad index from 0 to 31: drive the external pad driver low, wait briefly, arm the wait flag, then drive the external pad driver high to generate a single rising edge.","Poll the wait flag with a bounded timeout (initial count 2000) and periodic short waits to confirm the interrupt was serviced; on timeout, record an error and exit the loop.","After each iteration, optionally return the pad driver low and wait briefly to prepare for the next edge.","Interrupt handler actions: clear the wait flag; read the group interrupt status; mask the group enable during service; check that at least one group bit is asserted; clear per-pin raw status across all pads by writing the per-GPIO clear bit in each control register and wait briefly.","Verify that the group status is zero following the clears; clear the system-level raw status for the selected instance; re-enable the group interrupt and clear the pending interrupt in the interrupt controller."]</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>INTR_EN1,RAW_STCR1,GPIO_GP0_GPIO_8,GPIO_GP0_GPIO_9,GPIO_GP0_GPIO_10,GPIO_GP0_GPIO_11,GPIO_GP0_GPIO_12,GPIO_GP0_GPIO_13,GPIO_GP0_GPIO_14,GPIO_GP0_GPIO_15,GPIO_GP0_GPIO_16,GPIO_GP0_GPIO_17,GPIO_GP0_GPIO_18,GPIO_GP0_GPIO_19,GPIO_GP0_GPIO_20,GPIO_GP0_GPIO_21,GPIO_GP0_GPIO_22,GPIO_GP0_GPIO_23,GPIO_GP0_GPIO_24,GPIO_GP0_GPIO_25,GPIO_GP0_GPIO_26,GPIO_GP0_GPIO_27,GPIO_GP0_GPIO_28,GPIO_GP0_GPIO_29,GPIO_GP0_GPIO_30,GPIO_GP0_GPIO_31,GPIO_GP0_GPIO_32,GPIO_GP0_GPIO_33,GPIO_GP0_GPIO_34,GPIO_GP0_GPIO_35,GPIO_GP0_GPIO_36,GPIO_GP0_GPIO_37,GPIO_GP0_GPIO_38,GPIO_GP0_GPIO_39,GPIO_GPIO_IO_CTRL_GROUP1,GPIO_GPIO_IO_CTRL_GROUP2,GPIO_GPIO_IO_CTRL_GROUP3,GPIO_GPIO_IO_CTRL_GROUP4,GPIO_GP0_INTR1_INTR_EN1,GPIO_GP0_INTR1_INTR_STS1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>["Per rising transition, the group interrupt status indicates an active bit and is subsequently cleared to zero after per-pin raw clears.","System-level raw interrupt status for the selected instance is cleared during handler execution and the interrupt controller pending state is cleared.","Overall test passes only if no timeouts occur and status checks and clears succeed across the tested iterations."]</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
         <is>
           <t>test_gpio_pedge_all_pads_en</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Validate that enabling positive-edge detection on all GPIO inputs (pads 8–39) produces an interrupt per rising transition, that group status asserts and can be cleared for all pads, and that the system interrupt path is properly cleared and re-enabled between events.</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>GPIO</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Interrupts can be generated based on positive edge or negative edge or level high or level low detection at GPIO input</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Interrupt</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0xA0243ffc</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0xA0243ffc</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Group interrupt is masked during service and re-enabled afterward; the wait loop for the handler is bounded by a timeout; input mode for pads is configured via group I/O control registers to ensure edge detection.</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1. Entry point enables the appropriate CPU interrupt for the selected GPIO instance in the interrupt controller.
-2. Enable the system register output for the selected GPIO instance to route the group interrupt.
-3. Configure per-GPIO control registers for pads 8 through 39 to enable positive-edge interrupt detection.
-4. Set pads 8–39 to input mode using the four group I/O control registers.
-5. Enable all bits in the group interrupt-enable register.
-6. For each pad index from 0 to 31: drive the external pad driver low, wait briefly, arm the wait flag, then drive the external pad driver high to generate a single rising edge.
-7. Poll the wait flag with a bounded timeout (initial count 2000) and periodic short waits to confirm the interrupt was serviced; on timeout, record an error and exit the loop.
-8. After each iteration, optionally return the pad driver low and wait briefly to prepare for the next edge.
-9. Interrupt handler actions: clear the wait flag; read the group interrupt status; mask the group enable during service; check that at least one group bit is asserted; clear per-pin raw status across all pads by writing the per-GPIO clear bit in each control register and wait briefly.
-10. Verify that the group status is zero following the clears; clear the system-level raw status for the selected instance; re-enable the group interrupt and clear the pending interrupt in the interrupt controller.</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>MIZAR_LSS_SYSREG_INTR_EN1,MIZAR_LSS_SYSREG_RAW_STCR1,MIZAR_GPIO_GP0_GPIO_8,MIZAR_GPIO_GP0_GPIO_9,MIZAR_GPIO_GP0_GPIO_10,MIZAR_GPIO_GP0_GPIO_11,MIZAR_GPIO_GP0_GPIO_12,MIZAR_GPIO_GP0_GPIO_13,MIZAR_GPIO_GP0_GPIO_14,MIZAR_GPIO_GP0_GPIO_15,MIZAR_GPIO_GP0_GPIO_16,MIZAR_GPIO_GP0_GPIO_17,MIZAR_GPIO_GP0_GPIO_18,MIZAR_GPIO_GP0_GPIO_19,MIZAR_GPIO_GP0_GPIO_20,MIZAR_GPIO_GP0_GPIO_21,MIZAR_GPIO_GP0_GPIO_22,MIZAR_GPIO_GP0_GPIO_23,MIZAR_GPIO_GP0_GPIO_24,MIZAR_GPIO_GP0_GPIO_25,MIZAR_GPIO_GP0_GPIO_26,MIZAR_GPIO_GP0_GPIO_27,MIZAR_GPIO_GP0_GPIO_28,MIZAR_GPIO_GP0_GPIO_29,MIZAR_GPIO_GP0_GPIO_30,MIZAR_GPIO_GP0_GPIO_31,MIZAR_GPIO_GP0_GPIO_32,MIZAR_GPIO_GP0_GPIO_33,MIZAR_GPIO_GP0_GPIO_34,MIZAR_GPIO_GP0_GPIO_35,MIZAR_GPIO_GP0_GPIO_36,MIZAR_GPIO_GP0_GPIO_37,MIZAR_GPIO_GP0_GPIO_38,MIZAR_GPIO_GP0_GPIO_39,MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,MIZAR_GPIO_GPIO_IO_CTRL_GROUP2,MIZAR_GPIO_GPIO_IO_CTRL_GROUP3,MIZAR_GPIO_GPIO_IO_CTRL_GROUP4,MIZAR_GPIO_GP0_INTR1_INTR_EN1,MIZAR_GPIO_GP0_INTR1_INTR_STS1</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1. Per rising transition, the group interrupt status indicates an active bit and is subsequently cleared to zero after per-pin raw clears.
-2. System-level raw interrupt status for the selected instance is cleared during handler execution and the interrupt controller pending state is cleared.
-3. Overall test passes only if no timeouts occur and status checks and clears succeed across the tested iterations.</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="82" customWidth="1" min="2" max="2"/>
-    <col width="82" customWidth="1" min="3" max="3"/>
-    <col width="82" customWidth="1" min="4" max="4"/>
-    <col width="82" customWidth="1" min="5" max="5"/>
-    <col width="82" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Hidden_Test_Case_Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Hidden_Test_Description</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Hidden_Remarks</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Hidden_Test_Steps_Procedure</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Hidden_Impacted_Registers</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Hidden_Validation_Acceptance_Criteria</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>gpio_reg_wr_rd_test</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>program.c invokes chk_rst_val() then chk_rd_wr(), and finishes with pass/fail based on def_fail_cnt and wr_fail_cnt. chk_rst_val() loops i=0..CNT-1 using addr=addr_array[i] (macros like MIZAR_GPIO_GP0_GPIO_8..GPIO_39, group regs, intr regs). It skips entries where skip_rst_array[i]==1 or read_mask_array[i]==0, reads via read_reg(addr), masks data_rd with 0xFFFFFFFE, and compares to default_value_array[i]. chk_rd_wr() tries six patterns (0xFFFFFFFF,0xAAAAAAAA,0x55555555,0xF5F5F5F5,0xA5A5A5A5,0xFFFF0000). For each i: if skip_array[i]==1 or write_mask_array[i]==0, it skips; else it write_reg(addr,(data_wr &amp; write_mask_array[i])). Then it reads back masked by read_mask_array[i], computes wr_n=(write_mask_array[i]^0xFFFFFFFF), and expected=((data_wr &amp; read_mask_array[i] &amp; write_mask_array[i]) | (wr_n &amp; read_mask_array[i] &amp; default_value_array[i])). Mismatch increments wr_fail_cnt. finish(1) if any failures, else finish(0).</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>test_define.c: //80,94,98,9c,a0,a4,a8,ac,b0...SKIPPING VRRW registers. skip_array[] and skip_rst_array[] specify which registers to skip. Comment: when reading default values the din value is becoming 1 automatically if we don't force any value, but if we force zero to din bit level sel becoming high, so that reading value not matched with expected value.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>["int test_case(): calls chk_rst_val(); calls chk_rd_wr(); if (def_fail_cnt &gt; 0 || wr_fail_cnt &gt; 0) finish(1); else finish(0).", "void chk_rst_val(): for (i=0;i&lt;CNT;i++): addr=addr_array[i] (e.g., MIZAR_GPIO_GP0_GPIO_8..MIZAR_GPIO_GP0_GPIO_39, MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, MIZAR_GPIO_GP0_INTRx_xxx, GPIO_IO_CTRL_GROUPx, GPIO_DOUT_GROUPx, GPIO_DIN_GROUPx); if (skip_rst_array[i]==1) continue; if (read_mask_array[i]==0) continue; data_rd=read_reg(addr); data=(data_rd &amp; 0xFFFFFFFE); if (data==default_value_array[i]) pass; else { def_fail_cnt++; printf failure }. No waits/timeouts.", "void chk_rd_wr(): unsigned chk_val[6]={0xFFFFFFFF,0xAAAAAAAA,0x55555555,0xF5F5F5F5,0xA5A5A5A5,0xFFFF0000}; For each pattern j: data_wr=chk_val[j]; Write phase: for (i=0;i&lt;CNT;i++): addr=addr_array[i]; if (skip_array[i]==1) continue; if (write_mask_array[i]==0) continue; else write_reg(addr,(data_wr &amp; write_mask_array[i])). Read/verify phase: for (i=0;i&lt;CNT;i++): addr=addr_array[i]; if (skip_array[i]==1) continue; if (write_mask_array[i]==0) continue; if (read_mask_array[i]==0) continue; data_rd=(read_reg(addr) &amp; read_mask_array[i]); wr_n=(write_mask_array[i] ^ 0xFFFFFFFF); exp_val=((data_wr &amp; read_mask_array[i] &amp; write_mask_array[i]) | (wr_n &amp; read_mask_array[i] &amp; default_value_array[i])); if (data_rd==exp_val) pass; else { wr_fail_cnt++; printf failure }."]</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>MIZAR_GPIO_GP0_GPIO_8,MIZAR_GPIO_GP0_GPIO_9,MIZAR_GPIO_GP0_GPIO_10,MIZAR_GPIO_GP0_GPIO_11,MIZAR_GPIO_GP0_GPIO_12,MIZAR_GPIO_GP0_GPIO_13,MIZAR_GPIO_GP0_GPIO_14,MIZAR_GPIO_GP0_GPIO_15,MIZAR_GPIO_GP0_GPIO_16,MIZAR_GPIO_GP0_GPIO_17,MIZAR_GPIO_GP0_GPIO_18,MIZAR_GPIO_GP0_GPIO_19,MIZAR_GPIO_GP0_GPIO_20,MIZAR_GPIO_GP0_GPIO_21,MIZAR_GPIO_GP0_GPIO_22,MIZAR_GPIO_GP0_GPIO_23,MIZAR_GPIO_GP0_GPIO_24,MIZAR_GPIO_GP0_GPIO_25,MIZAR_GPIO_GP0_GPIO_26,MIZAR_GPIO_GP0_GPIO_27,MIZAR_GPIO_GP0_GPIO_28,MIZAR_GPIO_GP0_GPIO_29,MIZAR_GPIO_GP0_GPIO_30,MIZAR_GPIO_GP0_GPIO_31,MIZAR_GPIO_GP0_GPIO_32,MIZAR_GPIO_GP0_GPIO_33,MIZAR_GPIO_GP0_GPIO_34,MIZAR_GPIO_GP0_GPIO_35,MIZAR_GPIO_GP0_GPIO_36,MIZAR_GPIO_GP0_GPIO_37,MIZAR_GPIO_GP0_GPIO_38,MIZAR_GPIO_GP0_GPIO_39,MIZAR_GPIO_GPIO_INTR_RAW_STCLR1,MIZAR_GPIO_GP0_INTR1_INTR_EN1,MIZAR_GPIO_GP0_INTR1_INTR_STS1,MIZAR_GPIO_GP0_INTR2_INTR_EN1,MIZAR_GPIO_GP0_INTR2_INTR_STS1,MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,MIZAR_GPIO_GPIO_IO_CTRL_GROUP2,MIZAR_GPIO_GPIO_IO_CTRL_GROUP3,MIZAR_GPIO_GPIO_IO_CTRL_GROUP4,MIZAR_GPIO_GPIO_DOUT_GROUP1,MIZAR_GPIO_GPIO_DOUT_GROUP2,MIZAR_GPIO_GPIO_DOUT_GROUP3,MIZAR_GPIO_GPIO_DOUT_GROUP4,MIZAR_GPIO_GPIO_DIN_GROUP1,MIZAR_GPIO_GPIO_DIN_GROUP2,MIZAR_GPIO_GPIO_DIN_GROUP3,MIZAR_GPIO_GPIO_DIN_GROUP4</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Default pass criterion: for all i where skip_rst_array[i]==0 and read_mask_array[i]!=0, (read_reg(addr_array[i]) &amp; 0xFFFFFFFE) == default_value_array[i]. Write/read pass criterion: for all i where skip_array[i]==0, write_mask_array[i]!=0, read_mask_array[i]!=0, and for each j in 0..5, (read_reg(addr_array[i]) &amp; read_mask_array[i]) == ((chk_val[j] &amp; read_mask_array[i] &amp; write_mask_array[i]) | ((write_mask_array[i]^0xFFFFFFFF) &amp; read_mask_array[i] &amp; default_value_array[i])). Overall finish(0) indicates PASS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>test_gpio_negedge_intr_en</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>program.c sets up negedge interrupts. In test_case(): optionally GIC_EnableIRQ(87/88); write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR or LSS_SYSREG_INTR_EN1_GPIO1_INTR); write_reg(0xA0243ffc, 0xffffffff); for i=0..31: addr1 = MIZAR_GPIO_GP0_GPIO_8 + (i*4); write_reg(addr1, (1&lt;&lt;20)|(1&lt;&lt;18)|(1&lt;&lt;16)); wait_on(10). For each i: wr_val=1&lt;&lt;i; write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, wr_val); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, wr_val); wait_on(10); int_pend=1; write_reg(0xA0243ffc, 0xffffffff); wait_on(30); write_reg(0xA0243ffc, ~wr_val); timeout=5000; while (int_pend &amp;&amp; timeout--) wait_on(10); if timeout==0 error++. finish(test_err). Default_IRQHandler(): local_wr=1&lt;&lt;i; int_pend=0; write_reg(0xA0243ffc, 0xffffffff); raddr=MIZAR_GPIO_GP0_GPIO_8 + (i*4); rdata=read_reg(raddr); if ((rdata &amp; 0x1)!=0) error++; if ((rdata &amp; 0x2)!=0x0) { rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if ((rdata_grp &amp; local_wr)==0) error++; write_reg(MIZAR_GPIO_GP0_GPIO_8 + (i*4), (1&lt;&lt;20)|(1&lt;&lt;16)); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, local_wr); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if (rdata_grp!=0x0) error++; write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR/1_INTR); GIC_ClearIRQ(87/88); } else error++;</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Wait-before-edge arming to avoid race: comment indicates arming int_pend before generating the edge. Uses bounded wait: timeout=5000 with wait_on(10) per loop. Pad driver (0xA0243ffc) set to known state inside ISR.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>["int test_case(): test_err=0; #ifdef GPIO0 GIC_EnableIRQ(87) #endif; #ifdef GPIO1 GIC_EnableIRQ(88) #endif;", "#ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR) #endif; #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO1_INTR) #endif;", "write_reg(0xA0243ffc, 0xFFFFFFFF);", "for (i=0;i&lt;32;i++): addr1=MIZAR_GPIO_GP0_GPIO_8 + (i*4); write_reg(addr1, (1&lt;&lt;20)|(1&lt;&lt;18)|(1&lt;&lt;16)); wait_on(10);", "for (i=0;i&lt;32;i++): wr_val=1&lt;&lt;i; write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, wr_val); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, wr_val); wait_on(10); int_pend=1; write_reg(0xA0243ffc, 0xFFFFFFFF); wait_on(30); write_reg(0xA0243ffc, ~wr_val);", "unsigned int timeout=5000; while (int_pend &amp;&amp; timeout--) wait_on(10); if (timeout==0) { printf timeout; test_err++; }", "finish(test_err);", "void Default_IRQHandler(): unsigned int local_wr=1&lt;&lt;i; int_pend=0; write_reg(0xA0243ffc, 0xFFFFFFFF); raddr=MIZAR_GPIO_GP0_GPIO_8 + (i*4); rdata=read_reg(raddr);", "if ((rdata &amp; 0x1)!=0) test_err++;", "if ((rdata &amp; 0x2)!=0x0) { rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if ((rdata_grp &amp; local_wr)==0) test_err++; write_reg(MIZAR_GPIO_GP0_GPIO_8 + (i*4), (1&lt;&lt;20)|(1&lt;&lt;16)); write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, local_wr); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if (rdata_grp!=0x0) test_err++; #ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); GIC_ClearIRQ(87); #endif #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO1_INTR); GIC_ClearIRQ(88); #endif } else { test_err++; }"]</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>MIZAR_LSS_SYSREG_INTR_EN1,MIZAR_LSS_SYSREG_RAW_STCR1,MIZAR_GPIO_GP0_GPIO_8,MIZAR_GPIO_GP0_GPIO_9,MIZAR_GPIO_GP0_GPIO_10,MIZAR_GPIO_GP0_GPIO_11,MIZAR_GPIO_GP0_GPIO_12,MIZAR_GPIO_GP0_GPIO_13,MIZAR_GPIO_GP0_GPIO_14,MIZAR_GPIO_GP0_GPIO_15,MIZAR_GPIO_GP0_GPIO_16,MIZAR_GPIO_GP0_GPIO_17,MIZAR_GPIO_GP0_GPIO_18,MIZAR_GPIO_GP0_GPIO_19,MIZAR_GPIO_GP0_GPIO_20,MIZAR_GPIO_GP0_GPIO_21,MIZAR_GPIO_GP0_GPIO_22,MIZAR_GPIO_GP0_GPIO_23,MIZAR_GPIO_GP0_GPIO_24,MIZAR_GPIO_GP0_GPIO_25,MIZAR_GPIO_GP0_GPIO_26,MIZAR_GPIO_GP0_GPIO_27,MIZAR_GPIO_GP0_GPIO_28,MIZAR_GPIO_GP0_GPIO_29,MIZAR_GPIO_GP0_GPIO_30,MIZAR_GPIO_GP0_GPIO_31,MIZAR_GPIO_GP0_GPIO_32,MIZAR_GPIO_GP0_GPIO_33,MIZAR_GPIO_GP0_GPIO_34,MIZAR_GPIO_GP0_GPIO_35,MIZAR_GPIO_GP0_GPIO_36,MIZAR_GPIO_GP0_GPIO_37,MIZAR_GPIO_GP0_GPIO_38,MIZAR_GPIO_GP0_GPIO_39,MIZAR_GPIO_GP0_INTR1_INTR_EN1,MIZAR_GPIO_GP0_INTR1_INTR_STS1,MIZAR_GPIO_GPIO_INTR_RAW_STCLR1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Pass per pin when: after falling edge, (read_reg(MIZAR_GPIO_GP0_GPIO_8 + i*4) &amp; 0x1) == 0; (read_reg(MIZAR_GPIO_GP0_GPIO_8 + i*4) &amp; 0x2) != 0; (read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1) &amp; (1&lt;&lt;i)) != 0; after write_reg(MIZAR_GPIO_GP0_GPIO_8 + i*4, (1&lt;&lt;20)|(1&lt;&lt;16)) and write_reg(MIZAR_GPIO_GPIO_INTR_RAW_STCLR1, 1&lt;&lt;i), then read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1) == 0. System status cleared via MIZAR_LSS_SYSREG_RAW_STCR1 and GIC cleared. No timeout in while(int_pend &amp;&amp; timeout--) loop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>test_gpio_pedge_all_pads_en</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>test_case(): #ifdef GPIO0 GIC_EnableIRQ(87) #endif; #ifdef GPIO1 GIC_EnableIRQ(88) #endif; write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR/1_INTR); for (i=0;i&lt;32;i++) write_reg(MIZAR_GPIO_GP0_GPIO_8 + i*4, 0x00020000); wait_on(10); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,0xFF); ... GROUP4,0xFF; wait_on(10); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF); For i=0..31: write_reg(0xA0243ffc,0x00000000); wait_on(10); int_pend=1; write_reg(0xA0243ffc,0xFFFFFFFF); int timeout=2000; while (int_pend==1 &amp;&amp; --timeout&gt;0) wait_on(10); if (timeout==0) { printf timeout; test_err++; break; } write_reg(0xA0243ffc,0x00000000); wait_on(10); finish(test_err). Default_IRQHandler(): wr_val=1&lt;&lt;i; int_pend=0; rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1,0x00000000); if ((rdata_grp &amp; 0xFFFFFFFF)!=0) pass else { printf error; test_err++; } for (j=0;j&lt;32;j++) write_reg(MIZAR_GPIO_GP0_GPIO_8 + j*4, 0x00010000); wait_on(2); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if (rdata_grp==0) pass else { printf error; test_err++; } #ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if ((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO0_INTR)!=0) test_err++; #endif #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO1_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if ((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO1_INTR)!=0) test_err++; #endif write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF); GIC_ClearIRQ(87/88).</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Group interrupt enable is masked during handler: write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0x00000000) and re-enabled later; bounded wait with timeout=2000 and wait_on(10) per loop.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>["void test_case(): #ifdef GPIO0 GIC_EnableIRQ(87) #endif; #ifdef GPIO1 GIC_EnableIRQ(88) #endif; unsigned int rdata, wr_val; test_err=0;", "#ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR) #endif; #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO1_INTR) #endif;", "for (i=0;i&lt;32;i++) write_reg(MIZAR_GPIO_GP0_GPIO_8 + (i*4), 0x00020000);", "wait_on(10); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP2,0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP3,0x000000FF); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP4,0x000000FF);", "wait_on(10); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF);", "for (i=0;i&lt;32;i++): write_reg(0xA0243ffc,0x00000000); wait_on(10); int_pend=1; write_reg(0xA0243ffc,0xFFFFFFFF); int timeout=2000; while ((int_pend==1) &amp;&amp; (--timeout&gt;0)) wait_on(10); if (timeout==0) { printf timeout; test_err++; break; } write_reg(0xA0243ffc,0x00000000); wait_on(10); finish(test_err);", "void Default_IRQHandler(): wr_val=1&lt;&lt;i; int_pend=0; rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1,0x00000000); if ((rdata_grp &amp; 0xFFFFFFFF)!=0) { /* success */ } else { printf error; test_err++; } for (j=0;j&lt;32;j++) write_reg(MIZAR_GPIO_GP0_GPIO_8 + (j*4), 0x00010000); wait_on(2); rdata_grp=read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); if (rdata_grp==0) { /* cleared */ } else { printf error; test_err++; } #ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if ((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO0_INTR)!=0) test_err++; #endif #ifdef GPIO1 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO1_INTR); rdata=read_reg(MIZAR_LSS_SYSREG_RAW_STCR1); if ((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO1_INTR)!=0) test_err++; #endif write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1,0xFFFFFFFF); #ifdef GPIO0 GIC_ClearIRQ(87) #endif #ifdef GPIO1 GIC_ClearIRQ(88) #endif"]</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MIZAR_LSS_SYSREG_INTR_EN1,MIZAR_LSS_SYSREG_RAW_STCR1,MIZAR_GPIO_GP0_GPIO_8,MIZAR_GPIO_GP0_GPIO_9,MIZAR_GPIO_GP0_GPIO_10,MIZAR_GPIO_GP0_GPIO_11,MIZAR_GPIO_GP0_GPIO_12,MIZAR_GPIO_GP0_GPIO_13,MIZAR_GPIO_GP0_GPIO_14,MIZAR_GPIO_GP0_GPIO_15,MIZAR_GPIO_GP0_GPIO_16,MIZAR_GPIO_GP0_GPIO_17,MIZAR_GPIO_GP0_GPIO_18,MIZAR_GPIO_GP0_GPIO_19,MIZAR_GPIO_GP0_GPIO_20,MIZAR_GPIO_GP0_GPIO_21,MIZAR_GPIO_GP0_GPIO_22,MIZAR_GPIO_GP0_GPIO_23,MIZAR_GPIO_GP0_GPIO_24,MIZAR_GPIO_GP0_GPIO_25,MIZAR_GPIO_GP0_GPIO_26,MIZAR_GPIO_GP0_GPIO_27,MIZAR_GPIO_GP0_GPIO_28,MIZAR_GPIO_GP0_GPIO_29,MIZAR_GPIO_GP0_GPIO_30,MIZAR_GPIO_GP0_GPIO_31,MIZAR_GPIO_GP0_GPIO_32,MIZAR_GPIO_GP0_GPIO_33,MIZAR_GPIO_GP0_GPIO_34,MIZAR_GPIO_GP0_GPIO_35,MIZAR_GPIO_GP0_GPIO_36,MIZAR_GPIO_GP0_GPIO_37,MIZAR_GPIO_GP0_GPIO_38,MIZAR_GPIO_GP0_GPIO_39,MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,MIZAR_GPIO_GPIO_IO_CTRL_GROUP2,MIZAR_GPIO_GPIO_IO_CTRL_GROUP3,MIZAR_GPIO_GPIO_IO_CTRL_GROUP4,MIZAR_GPIO_GP0_INTR1_INTR_EN1,MIZAR_GPIO_GP0_INTR1_INTR_STS1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Handler sees non-zero read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1); after for(j=0..31) write_reg(MIZAR_GPIO_GP0_GPIO_8 + j*4, 0x00010000) and wait_on(2), then read_reg(MIZAR_GPIO_GP0_INTR1_INTR_STS1)==0; #ifdef GPIO0 write_reg(MIZAR_LSS_SYSREG_RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); subsequent read_reg(MIZAR_LSS_SYSREG_RAW_STCR1) &amp; LSS_SYSREG_RAW_STCR1_GPIO0_INTR == 0. Same check for GPIO1 if defined. No timeout while (int_pend==1 &amp;&amp; --timeout&gt;0).</t>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>test_case(): #ifdef GPIO0 GIC_EnableIRQ(87) #endif; #ifdef GPIO1 GIC_EnableIRQ(88) #endif; write_reg(MIZAR_LSS_SYSREG_INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR/1_INTR); for (i=0;i&lt;32;i++) write_reg(MIZAR_GPIO_GP0_GPIO_8 + i4, 0x00020000); wait_on(10); write_reg(MIZAR_GPIO_GPIO_IO_CTRL_GROUP1,0xFF); ... GROUP4,0xFF; wait_on(10); write_reg(MIZAR_GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF); For i=0..31: write_reg(0xA0243ffc,0x00000000); wait_on(10); int_pend=1; write_reg(0xA0243ffc,0xFFFFFFFF); int timeout=2000; while (int_pend==1 &amp;&amp; --timeout&gt;0) wait_on(10); if (timeout==0) { printf timeout; test_err++; break; } write_reg(0xA0243ffc,0x00000000); wait_on(10); finish(test_err). Default_IRQHandler(): wr_val=1&lt;&lt;i; int_pend=0; rdata_grp=read_reg(GPIO_GP0_INTR1_INTR_STS1); write_reg(GPIO_GP0_INTR1_INTR_EN1,0x00000000); if ((rdata_grp &amp; 0xFFFFFFFF)!=0) pass else { printf error; test_err++; } for (j=0;j&lt;32;j++) write_reg(GPIO_GP0_GPIO_8 + j4, 0x00010000); wait_on(2); rdata_grp=read_reg(GPIO_GP0_INTR1_INTR_STS1); if (rdata_grp==0) pass else { printf error; test_err++; } #ifdef GPIO0 write_reg(RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); rdata=read_reg(RAW_STCR1); if ((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO0_INTR)!=0) test_err++; #endif #ifdef GPIO1 write_reg(RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO1_INTR); rdata=read_reg(RAW_STCR1); if ((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO1_INTR)!=0) test_err++; #endif write_reg(GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF); GIC_ClearIRQ(87/88).</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Group interrupt enable is masked during handler: write_reg(GPIO_GP0_INTR1_INTR_EN1, 0x00000000) and re-enabled later; bounded wait with timeout=2000 and wait_on(10) per loop.</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>["void test_case(): #ifdef GPIO0 GIC_EnableIRQ(87) #endif; #ifdef GPIO1 GIC_EnableIRQ(88) #endif; unsigned int rdata, wr_val; test_err=0;","#ifdef GPIO0 write_reg(INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO0_INTR) #endif; #ifdef GPIO1 write_reg(INTR_EN1, LSS_SYSREG_INTR_EN1_GPIO1_INTR) #endif;","for (i=0;i&lt;32;i++) write_reg(GPIO_GP0_GPIO_8 + (i4), 0x00020000);","wait_on(10); write_reg(GPIO_GPIO_IO_CTRL_GROUP1,0x000000FF); write_reg(GPIO_GPIO_IO_CTRL_GROUP2,0x000000FF); write_reg(GPIO_GPIO_IO_CTRL_GROUP3,0x000000FF); write_reg(GPIO_GPIO_IO_CTRL_GROUP4,0x000000FF);","wait_on(10); write_reg(GPIO_GP0_INTR1_INTR_EN1, 0xFFFFFFFF);","for (i=0;i&lt;32;i++): write_reg(0xA0243ffc,0x00000000); wait_on(10); int_pend=1; write_reg(0xA0243ffc,0xFFFFFFFF); int timeout=2000; while ((int_pend==1) &amp;&amp; (--timeout&gt;0)) wait_on(10); if (timeout==0) { printf timeout; test_err++; break; } write_reg(0xA0243ffc,0x00000000); wait_on(10); finish(test_err);","void Default_IRQHandler(): wr_val=1&lt;&lt;i; int_pend=0; rdata_grp=read_reg(GPIO_GP0_INTR1_INTR_STS1); write_reg(GPIO_GP0_INTR1_INTR_EN1,0x00000000); if ((rdata_grp &amp; 0xFFFFFFFF)!=0) { /* success / } else { printf error; test_err++; } for (j=0;j&lt;32;j++) write_reg(GPIO_GP0_GPIO_8 + (j4), 0x00010000); wait_on(2); rdata_grp=read_reg(GPIO_GP0_INTR1_INTR_STS1); if (rdata_grp==0) { /* cleared / } else { printf error; test_err++; } #ifdef GPIO0 write_reg(RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); rdata=read_reg(RAW_STCR1); if ((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO0_INTR)!=0) test_err++; #endif #ifdef GPIO1 write_reg(RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO1_INTR); rdata=read_reg(RAW_STCR1); if ((rdata &amp; LSS_SYSREG_RAW_STCR1_GPIO1_INTR)!=0) test_err++; #endif write_reg(GPIO_GP0_INTR1_INTR_EN1,0xFFFFFFFF); #ifdef GPIO0 GIC_ClearIRQ(87) #endif #ifdef GPIO1 GIC_ClearIRQ(88) #endif"]</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>INTR_EN1,RAW_STCR1,GPIO_GP0_GPIO_8,GPIO_GP0_GPIO_9,GPIO_GP0_GPIO_10,GPIO_GP0_GPIO_11,GPIO_GP0_GPIO_12,GPIO_GP0_GPIO_13,GPIO_GP0_GPIO_14,GPIO_GP0_GPIO_15,GPIO_GP0_GPIO_16,GPIO_GP0_GPIO_17,GPIO_GP0_GPIO_18,GPIO_GP0_GPIO_19,GPIO_GP0_GPIO_20,GPIO_GP0_GPIO_21,GPIO_GP0_GPIO_22,GPIO_GP0_GPIO_23,GPIO_GP0_GPIO_24,GPIO_GP0_GPIO_25,GPIO_GP0_GPIO_26,GPIO_GP0_GPIO_27,GPIO_GP0_GPIO_28,GPIO_GP0_GPIO_29,GPIO_GP0_GPIO_30,GPIO_GP0_GPIO_31,GPIO_GP0_GPIO_32,GPIO_GP0_GPIO_33,GPIO_GP0_GPIO_34,GPIO_GP0_GPIO_35,GPIO_GP0_GPIO_36,GPIO_GP0_GPIO_37,GPIO_GP0_GPIO_38,GPIO_GP0_GPIO_39,GPIO_GPIO_IO_CTRL_GROUP1,GPIO_GPIO_IO_CTRL_GROUP2,GPIO_GPIO_IO_CTRL_GROUP3,GPIO_GPIO_IO_CTRL_GROUP4,GPIO_GP0_INTR1_INTR_EN1,GPIO_GP0_INTR1_INTR_STS1</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Handler sees non-zero read_reg(GPIO_GP0_INTR1_INTR_STS1); after for(j=0..31) write_reg(GPIO_GP0_GPIO_8 + j4, 0x00010000) and wait_on(2), then read_reg(GPIO_GP0_INTR1_INTR_STS1)==0; #ifdef GPIO0 write_reg(RAW_STCR1, LSS_SYSREG_RAW_STCR1_GPIO0_INTR); subsequent read_reg(RAW_STCR1) &amp; LSS_SYSREG_RAW_STCR1_GPIO0_INTR == 0. Same check for GPIO1 if defined. No timeout while (int_pend==1 &amp;&amp; --timeout&gt;0).</t>
         </is>
       </c>
     </row>
